--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3F96D50-107C-4D11-B063-BAE0F62B92A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAC93BC-6347-428B-852B-A4C29D95F341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="Optical" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="245">
   <si>
     <t>A</t>
   </si>
@@ -749,9 +748,6 @@
     <t>abs = 0.85; I_factor = 0.5 (186kW/m2)</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>higher temperature</t>
   </si>
   <si>
@@ -783,6 +779,24 @@
   </si>
   <si>
     <t>diffuse scattering</t>
+  </si>
+  <si>
+    <t>temperature didn't change much, but diff T8-T9 increased</t>
+  </si>
+  <si>
+    <t>specular</t>
+  </si>
+  <si>
+    <t>flux 5x</t>
+  </si>
+  <si>
+    <t>10x</t>
+  </si>
+  <si>
+    <t>20x</t>
+  </si>
+  <si>
+    <t>25x</t>
   </si>
 </sst>
 </file>
@@ -4772,7 +4786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B19FA9-A01B-4042-9995-5A31C36523E9}">
-  <dimension ref="A2:J96"/>
+  <dimension ref="A2:J99"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="4"/>
@@ -5739,7 +5753,7 @@
         <v>227</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
@@ -5747,7 +5761,7 @@
         <v>82</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
@@ -5755,10 +5769,10 @@
         <v>83</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -5766,13 +5780,13 @@
         <v>84</v>
       </c>
       <c r="F86" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
@@ -5780,7 +5794,7 @@
         <v>85</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
@@ -5788,35 +5802,73 @@
         <v>86</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" s="4">
+        <v>87</v>
+      </c>
       <c r="H89" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I89" s="4" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A90" s="4" t="s">
-        <v>228</v>
+      <c r="A90" s="4">
+        <v>88</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="H90" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" s="4">
+        <v>89</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" s="4">
+        <v>90</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" s="4">
+        <v>91</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H92" s="4" t="s">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G94" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H95" s="4" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C96" s="8">
+    <row r="99" spans="3:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C99" s="8">
         <v>7.8</v>
       </c>
-      <c r="H96" s="8" t="s">
+      <c r="H99" s="8" t="s">
         <v>208</v>
       </c>
     </row>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAC93BC-6347-428B-852B-A4C29D95F341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602887E7-87D4-4C96-8129-AB3A6ED8DE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="248">
   <si>
     <t>A</t>
   </si>
@@ -797,6 +797,15 @@
   </si>
   <si>
     <t>25x</t>
+  </si>
+  <si>
+    <t>R=1.7mm; t=0.2mm</t>
+  </si>
+  <si>
+    <t>profiles gets closer to experiments, temp higher</t>
+  </si>
+  <si>
+    <t>Ρ=1.3mm; t=0.6mm</t>
   </si>
 </sst>
 </file>
@@ -4786,7 +4795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B19FA9-A01B-4042-9995-5A31C36523E9}">
-  <dimension ref="A2:J99"/>
+  <dimension ref="A2:J101"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="4"/>
@@ -5855,20 +5864,42 @@
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" s="4">
+        <v>92</v>
+      </c>
       <c r="G94" s="4" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H95" s="4" t="s">
+      <c r="A95" s="4">
+        <v>93</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" s="4">
+        <v>94</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="97" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H97" s="4" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="99" spans="3:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C99" s="8">
+    <row r="101" spans="3:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C101" s="8">
         <v>7.8</v>
       </c>
-      <c r="H99" s="8" t="s">
+      <c r="H101" s="8" t="s">
         <v>208</v>
       </c>
     </row>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602887E7-87D4-4C96-8129-AB3A6ED8DE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1FF696-4EC5-424B-82CD-58BB310F9B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="18672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0D" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="540">
   <si>
     <t>A</t>
   </si>
@@ -155,18 +155,12 @@
     <t>no convergence</t>
   </si>
   <si>
-    <t>Input</t>
-  </si>
-  <si>
     <t>as close as possible to E67</t>
   </si>
   <si>
     <t>v7</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>temperature appeared too low</t>
   </si>
   <si>
@@ -186,9 +180,6 @@
   </si>
   <si>
     <t>no correction as original E67 without the 0.64</t>
-  </si>
-  <si>
-    <t>Heat</t>
   </si>
   <si>
     <t>Cps x 4</t>
@@ -687,12 +678,6 @@
     <t>256*0.8</t>
   </si>
   <si>
-    <t>Replaced Tracepro with COMSOL Raytracing</t>
-  </si>
-  <si>
-    <t>changed settings and duration of RayTracing</t>
-  </si>
-  <si>
     <t>ns scale for raytracing is wrong; total Q 164W for 0.1ns and 224W for 0.1μs
 temperatures are now to high, but length profile is great, time profile similar</t>
   </si>
@@ -739,9 +724,6 @@
     <t>abs = 0.625; I_factor = 0.7 (191kw/m2)</t>
   </si>
   <si>
-    <t>abs = 0.85; I_factor = 0.6 (223kW/m2)</t>
-  </si>
-  <si>
     <t>as was: abs = 0.85;  I_factor =1.0 (372kw/m2)</t>
   </si>
   <si>
@@ -806,6 +788,943 @@
   </si>
   <si>
     <t>Ρ=1.3mm; t=0.6mm</t>
+  </si>
+  <si>
+    <t>T_gas_in=17oC</t>
+  </si>
+  <si>
+    <t>lower temperature but smoother profile than #93, T9 is higher than T8</t>
+  </si>
+  <si>
+    <t>I_factor = 0.5</t>
+  </si>
+  <si>
+    <t>convectives losses T_ext -&gt;T_gas_in was insulation</t>
+  </si>
+  <si>
+    <t>changed settings and duration of RayTracing; max wall interactions 10k</t>
+  </si>
+  <si>
+    <t>lower temperature, length profile appears ok, T8 didn't change much but all others reduced</t>
+  </si>
+  <si>
+    <t>not much change if any</t>
+  </si>
+  <si>
+    <t>fine to extra fine for fluid dynamics -&gt; 320k</t>
+  </si>
+  <si>
+    <t>check mesh 40x smaller vs #7.7 (124k)</t>
+  </si>
+  <si>
+    <t>is 1.1M</t>
+  </si>
+  <si>
+    <t>still faster simulation, similar profiles</t>
+  </si>
+  <si>
+    <t>I_factor = 0.7</t>
+  </si>
+  <si>
+    <t>fast simulation; time profile higher but very nice with T8 &amp; T9 converging; but length too flat and not following expectation</t>
+  </si>
+  <si>
+    <t>bits=10</t>
+  </si>
+  <si>
+    <t>rays and source=1M</t>
+  </si>
+  <si>
+    <t>no obvious difference</t>
+  </si>
+  <si>
+    <t>final T are closer to experiments but profiles are not, light penetrates deeper; ALL T are very close to each other</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">comsol ray tracing; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I_factor =1.0, abs=0.85</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, bits=0; diffuse scattering</t>
+    </r>
+  </si>
+  <si>
+    <t>higher temperature but length profiles gets closer to preferred,</t>
+  </si>
+  <si>
+    <t>T8 and T9 behave correctly, final temperature not far away but as good for gas, length profile needs to drop faster, T10 too high</t>
+  </si>
+  <si>
+    <t>back to normal flux #84</t>
+  </si>
+  <si>
+    <t>need to change the specular for the front wall!!! T8 and T9 play as expected, although too much &amp; early. T3 is high but T10 even more, length profile needs to drop as in #103</t>
+  </si>
+  <si>
+    <t>temperature dropped; length profile flatter; T10 and T9 are both higher than T8!!! T3 is still higher but same as in #105</t>
+  </si>
+  <si>
+    <t>RH=0.42</t>
+  </si>
+  <si>
+    <t>temp increased but profile remains the same</t>
+  </si>
+  <si>
+    <t>Cp_s x4</t>
+  </si>
+  <si>
+    <t>bits=-10</t>
+  </si>
+  <si>
+    <t>should be the same with #104</t>
+  </si>
+  <si>
+    <t>Sim ID</t>
+  </si>
+  <si>
+    <t>Comsol Version</t>
+  </si>
+  <si>
+    <t>heat transfer model</t>
+  </si>
+  <si>
+    <t>Input general</t>
+  </si>
+  <si>
+    <t>Heat transfer specific</t>
+  </si>
+  <si>
+    <t>Comment (mostly compared to the previous Sim ID)</t>
+  </si>
+  <si>
+    <t>standard radiation</t>
+  </si>
+  <si>
+    <t>I_factor = 0.45</t>
+  </si>
+  <si>
+    <t>Cp_s normal</t>
+  </si>
+  <si>
+    <t>all temperatures increase slower, gas is close to what should have been but solid is also very slow</t>
+  </si>
+  <si>
+    <t>very flat profile compared to #109</t>
+  </si>
+  <si>
+    <t>almost no change vs #95</t>
+  </si>
+  <si>
+    <t>mesh fine to normal -&gt;569k</t>
+  </si>
+  <si>
+    <t>too low temperature</t>
+  </si>
+  <si>
+    <t>I_factor = 0.6</t>
+  </si>
+  <si>
+    <t>I_factor = 0.55</t>
+  </si>
+  <si>
+    <t>still high</t>
+  </si>
+  <si>
+    <t>RH=0.5</t>
+  </si>
+  <si>
+    <t>temperatures slightly lower but T8/T9 intersection a bit earlier as well, need to reduce more</t>
+  </si>
+  <si>
+    <t>RH=0.65</t>
+  </si>
+  <si>
+    <t>T8/T9 intersect earlier and are lower, T10/T3 are still higher</t>
+  </si>
+  <si>
+    <t>R=1.5mm; t=0.4mm</t>
+  </si>
+  <si>
+    <t>that was it!!! The temp profiles of gas and solid behave as they should; temp are lower but manageable
+still requires some manipulation on the properties and I_factor</t>
+  </si>
+  <si>
+    <t>lower temperature, no T8/T9 intersection, T3 great</t>
+  </si>
+  <si>
+    <t>add alumina piece, based on 7.7 #119</t>
+  </si>
+  <si>
+    <t>all temperature higher, no intersection</t>
+  </si>
+  <si>
+    <t>abs=0.85</t>
+  </si>
+  <si>
+    <t>R=1.6mm; t=0.3mm</t>
+  </si>
+  <si>
+    <t>still higher temperatures</t>
+  </si>
+  <si>
+    <t>Alumina diameter to 39mm</t>
+  </si>
+  <si>
+    <t>T8 higher, T9 slower/no intersection, T10/T3 slower but higher at the end</t>
+  </si>
+  <si>
+    <t>same behavior with #124 but higher temperatures</t>
+  </si>
+  <si>
+    <t>standard radiation with 0.99 emissivity</t>
+  </si>
+  <si>
+    <t>change to #104 radiation</t>
+  </si>
+  <si>
+    <t>same behavior with #125 but even higher temperatures, no steady state</t>
+  </si>
+  <si>
+    <t>slightly lower temperatures</t>
+  </si>
+  <si>
+    <t>T8 T9 are higher, rest are similar.</t>
+  </si>
+  <si>
+    <t>temperatures decreased compared to #128, but not sure if decreased more than needed</t>
+  </si>
+  <si>
+    <t>temp reduced, still no intersection</t>
+  </si>
+  <si>
+    <t>added metal end to Alumina</t>
+  </si>
+  <si>
+    <t>Alumina diameter to 29.4mm measured</t>
+  </si>
+  <si>
+    <t>T9, T10, T3 very good much, T8 slightly higher</t>
+  </si>
+  <si>
+    <t>add surface-ambient for back metal</t>
+  </si>
+  <si>
+    <t>RH=0.56</t>
+  </si>
+  <si>
+    <t>k(T) and Cp(T) for alumina</t>
+  </si>
+  <si>
+    <t>Metal: removed convective losses from back, changed side to heat transfer through insulation</t>
+  </si>
+  <si>
+    <t>T9 and T10 are ok, T8 higher, T3 okish, (T3 average was misdefined since #132)</t>
+  </si>
+  <si>
+    <t>very similar results, all good except for T8</t>
+  </si>
+  <si>
+    <t>abs=0.8</t>
+  </si>
+  <si>
+    <t>temperatures dropped a bit</t>
+  </si>
+  <si>
+    <t>seems better</t>
+  </si>
+  <si>
+    <t>RH=0.64</t>
+  </si>
+  <si>
+    <t>was specular reflection</t>
+  </si>
+  <si>
+    <t>temperatures dropped, can increase area or I_factor</t>
+  </si>
+  <si>
+    <t>T8 ok; T9 lower; T10 little lower; T3 almost ok</t>
+  </si>
+  <si>
+    <t>RH=0.55</t>
+  </si>
+  <si>
+    <t>T8 increased a bit</t>
+  </si>
+  <si>
+    <t>temperatures dropped but not that much, but length-profile changed drastically</t>
+  </si>
+  <si>
+    <t>abs_fr=0.625 abs_in=0.85</t>
+  </si>
+  <si>
+    <t>T3 gas ok but solid temperatures lower, length-profile as in #144</t>
+  </si>
+  <si>
+    <t>added a block for gas intake,
+got correct dimensions R=1.7, t=0.3, D=20</t>
+  </si>
+  <si>
+    <t>7.10</t>
+  </si>
+  <si>
+    <t>doesn't run at all - momentum issue</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>same with 7.9 just with the correct dimensions, change locations of thermocouples in the middle not corner of receiver</t>
+  </si>
+  <si>
+    <t>one abs for all, 0.85</t>
+  </si>
+  <si>
+    <t>lower middle temperatures, front and gas are ok</t>
+  </si>
+  <si>
+    <t>retry 7.10</t>
+  </si>
+  <si>
+    <t>visualize additional gas location</t>
+  </si>
+  <si>
+    <t>changed to COMSOL properties</t>
+  </si>
+  <si>
+    <t>small difference if any</t>
+  </si>
+  <si>
+    <t>lower temperatures but not drastic changes/improvement</t>
+  </si>
+  <si>
+    <t>back to Munro</t>
+  </si>
+  <si>
+    <t>Full Reflector as in 7.8</t>
+  </si>
+  <si>
+    <t>too high temperature, stopped</t>
+  </si>
+  <si>
+    <t>worked on mesh to refine the front wall but around 400k for receiver</t>
+  </si>
+  <si>
+    <t>irradiance decreased, come back to verify, temperature of solid tool low, of T3 not that low, time-profile very good</t>
+  </si>
+  <si>
+    <t>I_factor=0.7</t>
+  </si>
+  <si>
+    <t>I_factor=0.8</t>
+  </si>
+  <si>
+    <t>all temperature profiles increased, no intersection T8/T9 as before</t>
+  </si>
+  <si>
+    <t>temperature increased, profile better, but gas also higher, close to intersection</t>
+  </si>
+  <si>
+    <t>T8 and T9 very close to Exp (do not intersect) but T10 and T3 too high</t>
+  </si>
+  <si>
+    <t>lower temperature</t>
+  </si>
+  <si>
+    <t>RH=0.6, Cp_air ~ Cp_dry_air, used ASHRAE formula for vapor pressure</t>
+  </si>
+  <si>
+    <t>wrong estimation of Cp_g with RH</t>
+  </si>
+  <si>
+    <t>T8/T9 difference increased, all Temperatures still higher</t>
+  </si>
+  <si>
+    <t>bits=0; move light 0mm, smoothed source 0.2mm</t>
+  </si>
+  <si>
+    <t>400k primary + 400k secondary; I_factor=0.6, smoothed source 4mm</t>
+  </si>
+  <si>
+    <t>all temperatures are higher, profile not exactly what it would be ideally</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">reworked to smoothed accumulated boundary source, but solution of heat too slow, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>changed to normal</t>
+    </r>
+  </si>
+  <si>
+    <t>move light 10mm</t>
+  </si>
+  <si>
+    <t>Raytracing Qp=158kW/m2 but smoothed 54kW/m2, should be like 153</t>
+  </si>
+  <si>
+    <t>seems very close to #155</t>
+  </si>
+  <si>
+    <t>move light 30mm</t>
+  </si>
+  <si>
+    <t>temperature dropped but very little</t>
+  </si>
+  <si>
+    <t>move light -30mm</t>
+  </si>
+  <si>
+    <t>move light 0mm, bits=10</t>
+  </si>
+  <si>
+    <t>irradiance increased Qp=178kW/m2 but smoothed 63kW/m2, all temperatures increasd, but not that much</t>
+  </si>
+  <si>
+    <t>irradiance similar to bits=0  Qp=160kW/m2 but smoothed 54kW/m2</t>
+  </si>
+  <si>
+    <t>4*M_rho to mimic larger mass</t>
+  </si>
+  <si>
+    <t>not signficant change</t>
+  </si>
+  <si>
+    <t>metal radius 40mm</t>
+  </si>
+  <si>
+    <t>T8 ok but all other  too low</t>
+  </si>
+  <si>
+    <t>I_factor=1.0</t>
+  </si>
+  <si>
+    <t>T8/T9 higher T10/T3 lower</t>
+  </si>
+  <si>
+    <t>I_factor=0.9</t>
+  </si>
+  <si>
+    <t>decrease metal thickness=3mm</t>
+  </si>
+  <si>
+    <t>metal radius 30mm</t>
+  </si>
+  <si>
+    <t>T8 still higher, T9 almost ok, T10/T3 lowre</t>
+  </si>
+  <si>
+    <t>metal radius 20mm</t>
+  </si>
+  <si>
+    <t>I_factor=0.85</t>
+  </si>
+  <si>
+    <t>close but not ideal</t>
+  </si>
+  <si>
+    <t>change radius to Al and increase length for the same effect 6mm</t>
+  </si>
+  <si>
+    <t>9mm</t>
+  </si>
+  <si>
+    <t>not drastic change</t>
+  </si>
+  <si>
+    <t>back to 6mm</t>
+  </si>
+  <si>
+    <t>abs=0.9, to bring more energy at the front part</t>
+  </si>
+  <si>
+    <t>T8 T10 T3 very good but not T9</t>
+  </si>
+  <si>
+    <t>I_factor=0.5</t>
+  </si>
+  <si>
+    <t>bits=0</t>
+  </si>
+  <si>
+    <t>I_factor=0.65</t>
+  </si>
+  <si>
+    <t>Good enough but not T9 and without intersection</t>
+  </si>
+  <si>
+    <t>activated hnat=20</t>
+  </si>
+  <si>
+    <t>needs to be to high to make difference on the profile</t>
+  </si>
+  <si>
+    <t>I_factor=1.0, abs_front=0.5</t>
+  </si>
+  <si>
+    <t>abs_front=0.4</t>
+  </si>
+  <si>
+    <t>abs_front=0.3</t>
+  </si>
+  <si>
+    <t>it is not enough to fix T8 T9 intersection, when the temperatures get closer the profiles are becoming slower as well</t>
+  </si>
+  <si>
+    <t>hnat=40</t>
+  </si>
+  <si>
+    <t>not sufficient to alter the profile</t>
+  </si>
+  <si>
+    <t>abs_front=0.85</t>
+  </si>
+  <si>
+    <t>emis_factor5, hnat=10</t>
+  </si>
+  <si>
+    <t>emis_factor=2</t>
+  </si>
+  <si>
+    <t>abs_front=0.85, I_factor=1</t>
+  </si>
+  <si>
+    <t>massive impact</t>
+  </si>
+  <si>
+    <t>time profile is good except for the gas exit temperature, length profile is decent</t>
+  </si>
+  <si>
+    <t>conductive loss end of metal with water cooler -root.M_k*(T-root.T_amb)/(40[mm]) -- REMOVED</t>
+  </si>
+  <si>
+    <t>uncoupled</t>
+  </si>
+  <si>
+    <t>REMOVED</t>
+  </si>
+  <si>
+    <t>as #187</t>
+  </si>
+  <si>
+    <t>Tgas 550K</t>
+  </si>
+  <si>
+    <t>to test contribution of coupled flow, not that faster and noisy,
+back to coupled, v7.12</t>
+  </si>
+  <si>
+    <t>coupled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T8 T9 70-100K less than #189, profiles appear similar to #189, T10 T3 final very close to Exp, </t>
+  </si>
+  <si>
+    <t>had to fix 4 channels, added symetry at the end, but solution explodes</t>
+  </si>
+  <si>
+    <t>emis_factor=1</t>
+  </si>
+  <si>
+    <t>I_factor=1.0,</t>
+  </si>
+  <si>
+    <t>quite lower temperatures, flat length profile, T8 T9 wide gap</t>
+  </si>
+  <si>
+    <t>temperatures are still low, the gap between T8/T9 larger, and T10/T3 too small</t>
+  </si>
+  <si>
+    <t>change to TracePro</t>
+  </si>
+  <si>
+    <t>no sur-surf, Modest Appendix D eq27 (error in function)</t>
+  </si>
+  <si>
+    <t>fixed Modest function</t>
+  </si>
+  <si>
+    <t>CHANGED to TracePro, sec Rays 100k</t>
+  </si>
+  <si>
+    <t>quite high temperatures but profiles seem promising. T8/T9 do not intersect, I was expecting T9 to surpass T8 for such higher temperatures</t>
+  </si>
+  <si>
+    <t>lower but still high temperatures</t>
+  </si>
+  <si>
+    <t>use smoothed boundary source</t>
+  </si>
+  <si>
+    <t>removed A_tot/(A_tot-A_channel*100)</t>
+  </si>
+  <si>
+    <t>expected higher temperatures</t>
+  </si>
+  <si>
+    <t>with a small gap for air to sip in</t>
+  </si>
+  <si>
+    <t>still takes too much time to be solved, canceled</t>
+  </si>
+  <si>
+    <t>slow first flow field, not moving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gas_exit=0.5mm back of </t>
+  </si>
+  <si>
+    <t>length profile is high but close to the pattern; time profile is not, and all values are too high</t>
+  </si>
+  <si>
+    <t>no gap</t>
+  </si>
+  <si>
+    <t>I_factor=0.5, there was a mixup with the I_factor applied x2, in Ray Tracing and Heat Transfer</t>
+  </si>
+  <si>
+    <t>repeat</t>
+  </si>
+  <si>
+    <t>combined steps</t>
+  </si>
+  <si>
+    <t>I_factor=0.4</t>
+  </si>
+  <si>
+    <t>I_factor=0.3</t>
+  </si>
+  <si>
+    <t>emis=0.99</t>
+  </si>
+  <si>
+    <t>standard boundary source</t>
+  </si>
+  <si>
+    <t>added A_tot/(A_tot-A_channel*100)</t>
+  </si>
+  <si>
+    <t>wrong thermal insulation boundary conditions, not sure since what simulation</t>
+  </si>
+  <si>
+    <t>It seems that after the changes TRACEPRO cannot grab the profile and max temperature at the sime time; probably because of the wrong boundary condition</t>
+  </si>
+  <si>
+    <t>as expected now the temperatures are too low</t>
+  </si>
+  <si>
+    <t>I_factor=0.6</t>
+  </si>
+  <si>
+    <t>still lower</t>
+  </si>
+  <si>
+    <t>stopped early, still lower</t>
+  </si>
+  <si>
+    <t>removed A_tot/(A_tot-A_channel*100); emis=absorb=0.85;</t>
+  </si>
+  <si>
+    <t>T8 higher, no intersection, all other lower, the irradiance seems lower than usual</t>
+  </si>
+  <si>
+    <t>wall interactions 1k-&gt;10k, I_factor=0.8</t>
+  </si>
+  <si>
+    <t>irradiance increased 2x!!!; some double counting with I_factor; temperature two high and very large drop</t>
+  </si>
+  <si>
+    <t>stopped early, still higher, and large drop across length</t>
+  </si>
+  <si>
+    <t>metal radiation temp = T_ins(t); added A_tot/(A_tot-A_channel*100)</t>
+  </si>
+  <si>
+    <t>T10 T3 very good but T8 way off</t>
+  </si>
+  <si>
+    <t>emis_cav=0.85-&gt;0.99</t>
+  </si>
+  <si>
+    <t>all T very good except for T8</t>
+  </si>
+  <si>
+    <t>I_factor=0.55</t>
+  </si>
+  <si>
+    <t>qlpm=12.5</t>
+  </si>
+  <si>
+    <t>emis_factor=2x</t>
+  </si>
+  <si>
+    <t>? Bring it closer without T8 --&gt;needs a bit higher</t>
+  </si>
+  <si>
+    <t>?  #213 -&gt; I_factor=0.58</t>
+  </si>
+  <si>
+    <t>? To check whether the flows were ok, could not be solved because of stability, need to use different boundary conditions</t>
+  </si>
+  <si>
+    <t>emis_factor=4x</t>
+  </si>
+  <si>
+    <t>? To bring T8/T9 behavior -&gt; temperatures high, profiles ok, but  no intersection</t>
+  </si>
+  <si>
+    <t>emis_factor=6x</t>
+  </si>
+  <si>
+    <t>emis_factor=10x</t>
+  </si>
+  <si>
+    <t>T8/T9 intersected but still all higher</t>
+  </si>
+  <si>
+    <t>emis_factor=12x</t>
+  </si>
+  <si>
+    <t>length profile is excellent; time profile could have been better</t>
+  </si>
+  <si>
+    <t>so far E68</t>
+  </si>
+  <si>
+    <t>I_factor=0.9 * 256/456</t>
+  </si>
+  <si>
+    <t>all too high</t>
+  </si>
+  <si>
+    <t>x0.8</t>
+  </si>
+  <si>
+    <t>T10/T3 very good, T8/T9 kind of acceptable</t>
+  </si>
+  <si>
+    <t>change to Raytracing for lower irradiance</t>
+  </si>
+  <si>
+    <t>best could get</t>
+  </si>
+  <si>
+    <t>interesting result, T8/T9 intersect very early, T3/T10 increase faster but very close to steady state</t>
+  </si>
+  <si>
+    <t>change mass flow in, instead of lpm out, added a gap behind, and changed BC to front mass flow, qlpm_total</t>
+  </si>
+  <si>
+    <t>0.5 qlpm_t</t>
+  </si>
+  <si>
+    <t>not good but it gives the feeling that the changing the flow could lead to the actual solution</t>
+  </si>
+  <si>
+    <t>Ε68</t>
+  </si>
+  <si>
+    <t>0.75 qlpm_t</t>
+  </si>
+  <si>
+    <t>removed A_tot/(A_tot-A_channel*100);</t>
+  </si>
+  <si>
+    <t>qlpm_t</t>
+  </si>
+  <si>
+    <t>remove front convection</t>
+  </si>
+  <si>
+    <t>E68</t>
+  </si>
+  <si>
+    <t>ADD the full system, multiple modifications to run momentum (steady state, ambient temperature)</t>
+  </si>
+  <si>
+    <t>T8/T9 intersect but 300K higher, T3 lower 100K</t>
+  </si>
+  <si>
+    <t>steady-state velocity @Tamb</t>
+  </si>
+  <si>
+    <t>velocity x rho(Tamb)/rho(T)</t>
+  </si>
+  <si>
+    <t>T8 100K lower, T9 close steady state, T10 different profile, close steady state, T3 similar to T10</t>
+  </si>
+  <si>
+    <t>spf velocity field</t>
+  </si>
+  <si>
+    <t>back to qlpm</t>
+  </si>
+  <si>
+    <t>T8/T9 too high no intersection, T10/T3 too low</t>
+  </si>
+  <si>
+    <t>second laminar for steady state solution</t>
+  </si>
+  <si>
+    <t>transient with momentum coupled</t>
+  </si>
+  <si>
+    <t>quite lower temperatures</t>
+  </si>
+  <si>
+    <t>M_emis=0.8-&gt;0.6</t>
+  </si>
+  <si>
+    <t>seemed almost the same</t>
+  </si>
+  <si>
+    <t>no natural conversion alumina/metal</t>
+  </si>
+  <si>
+    <t>all temperatures slightly increased, mostly T3</t>
+  </si>
+  <si>
+    <t>natural convection metal, not alumina</t>
+  </si>
+  <si>
+    <t>need to decrease losses at the front and increase at the back</t>
+  </si>
+  <si>
+    <t>Al_emis=0.9; M_emis=0.05</t>
+  </si>
+  <si>
+    <t>Al_emis=0.6; M_emis=0.2</t>
+  </si>
+  <si>
+    <t>no radiation alumina, yes convection</t>
+  </si>
+  <si>
+    <t>alumina front insulation</t>
+  </si>
+  <si>
+    <t>re-radiation temp Tgas_in -&gt; Tamb</t>
+  </si>
+  <si>
+    <t>small increase on T9</t>
+  </si>
+  <si>
+    <t>T_amb at the small tube gas exit</t>
+  </si>
+  <si>
+    <t>T3 very close, T10 reduced significantly, T9 still highe than T8</t>
+  </si>
+  <si>
+    <t>change symbol insulation emissivity emis_ins, reradiation Metal back was forgotten</t>
+  </si>
+  <si>
+    <t>decrease insulation Cp 880-&gt;780</t>
+  </si>
+  <si>
+    <t>increase insulation k 0.078-&gt;0.08
+increase insulation Cp 780 -&gt; 1080</t>
+  </si>
+  <si>
+    <t>remove irradiance inside cavity</t>
+  </si>
+  <si>
+    <t>some change but probably not sufficient to ignore</t>
+  </si>
+  <si>
+    <t>not sure if there is any impact</t>
+  </si>
+  <si>
+    <t>reactivated irradiance inside cavity</t>
+  </si>
+  <si>
+    <t>allow irradiance front of insulation (too low but activated)</t>
+  </si>
+  <si>
+    <t>change to ray-tracing to increase the front heat</t>
+  </si>
+  <si>
+    <t>T2 insulation is 200K higher, side loss should be more or insulation stronger?</t>
+  </si>
+  <si>
+    <t>increase k_ins -&gt;0.15</t>
+  </si>
+  <si>
+    <t>all temperatures dropped, T8/T9 not so much, internal 50K, insulation temperature still, insulation still high</t>
+  </si>
+  <si>
+    <t>increase more -&gt; 0.3</t>
+  </si>
+  <si>
+    <t>all temperatures dropped</t>
+  </si>
+  <si>
+    <t>all temperatures dropped, Tinsulation still high</t>
+  </si>
+  <si>
+    <t>k_ins=0.08</t>
+  </si>
+  <si>
+    <t>enabled reradiation for insulation</t>
+  </si>
+  <si>
+    <t>add a round shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total powre is too high 650W for insulation eveything else &lt;150W, but effect is not massive, </t>
+  </si>
+  <si>
+    <t>Receiver abs=0.9</t>
+  </si>
+  <si>
+    <t>deactivate insulation convection</t>
+  </si>
+  <si>
+    <t>deactivate insulation reradiation, emis_cav=0.99-&gt;emis</t>
+  </si>
+  <si>
+    <t>very small increase on incoming power, small increase on temperatures</t>
+  </si>
+  <si>
+    <t>I_factor=1.05</t>
+  </si>
+  <si>
+    <t>increase insulation Cp 1280 -&gt; 1380</t>
+  </si>
+  <si>
+    <t>increase insulation Cp 1380 -&gt; 1480</t>
+  </si>
+  <si>
+    <t>increase insulation density 0.14-&gt;0.34</t>
+  </si>
+  <si>
+    <t>need to check the velocity simulation</t>
   </si>
 </sst>
 </file>
@@ -816,7 +1735,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -840,8 +1759,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -872,6 +1806,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -885,7 +1837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -916,6 +1868,27 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3645,6 +4618,135 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1610715</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>149520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1672950</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>33465</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FABABE3-794E-B610-149E-35563E1E3149}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="12964515" y="17418345"/>
+            <a:ext cx="54615" cy="49680"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FABABE3-794E-B610-149E-35563E1E3149}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12955532" y="17409345"/>
+              <a:ext cx="72221" cy="67320"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>268</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1390650</xdr:colOff>
+      <xdr:row>268</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{976FBD71-2E3D-C72F-238E-26AFB552FDCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="666750" y="81728310"/>
+          <a:ext cx="13959840" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -3794,6 +4896,34 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-07-03T10:50:40.107"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2 140 2292,'-2'-4'576,"4"-1"-180,1 0-396,1-8-600,2 0-1152</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="233.91">115 0 4424,'-3'11'8874,"-3"31"-4772,0 8-2336,-3-17-811,7-26-738,0-2-1,0 3 1,1-1-1,-1 0 1,1 0-1,-1 12 1,42-32-5010,-21-3 333,-1-8-2215</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4060,12 +5190,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:O40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="15" max="15" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="46.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4097,10 +5227,10 @@
         <v>27</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>7</v>
@@ -4109,7 +5239,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4156,7 +5286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4179,7 +5309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -4205,7 +5335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -4225,7 +5355,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -4248,7 +5378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -4268,7 +5398,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -4288,7 +5418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4311,7 +5441,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -4334,7 +5464,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -4357,7 +5487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -4368,7 +5498,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -4382,7 +5512,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -4405,21 +5535,21 @@
         <v>469</v>
       </c>
       <c r="O15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="N16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -4436,18 +5566,18 @@
         <v>465</v>
       </c>
       <c r="O17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="O18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -4458,18 +5588,18 @@
         <v>850</v>
       </c>
       <c r="O19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="O20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -4483,10 +5613,10 @@
         <v>573</v>
       </c>
       <c r="O21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -4497,10 +5627,10 @@
         <v>607</v>
       </c>
       <c r="O22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -4520,10 +5650,10 @@
         <v>502</v>
       </c>
       <c r="O23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -4543,10 +5673,10 @@
         <v>1641</v>
       </c>
       <c r="O24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -4566,10 +5696,10 @@
         <v>1071</v>
       </c>
       <c r="O25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -4580,10 +5710,10 @@
         <v>1892</v>
       </c>
       <c r="O26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -4603,7 +5733,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -4620,7 +5750,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -4631,10 +5761,10 @@
         <v>502</v>
       </c>
       <c r="O29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -4651,10 +5781,10 @@
         <v>502</v>
       </c>
       <c r="O30" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -4674,7 +5804,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -4682,10 +5812,10 @@
         <v>522</v>
       </c>
       <c r="O32" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -4705,7 +5835,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -4728,7 +5858,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -4742,13 +5872,13 @@
         <v>1.7341179006468701E-4</v>
       </c>
       <c r="K35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N35">
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -4762,7 +5892,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -4773,17 +5903,17 @@
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>37</v>
       </c>
@@ -4795,483 +5925,492 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B19FA9-A01B-4042-9995-5A31C36523E9}">
-  <dimension ref="A2:J101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:J274"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.109375" style="4"/>
-    <col min="3" max="3" width="31.88671875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="33.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="37.44140625" style="4" customWidth="1"/>
-    <col min="6" max="8" width="33.33203125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="55.109375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="29.88671875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="4"/>
+    <col min="1" max="2" width="9.140625" style="4"/>
+    <col min="3" max="3" width="9.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="37.42578125" style="4" customWidth="1"/>
+    <col min="6" max="8" width="33.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="55.140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="29.85546875" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>272</v>
+      </c>
       <c r="D2" s="4" t="s">
-        <v>31</v>
+        <v>273</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>42</v>
+        <v>274</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>7</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>10</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>11</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>12</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>13</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>14</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>16</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>24</v>
       </c>
       <c r="G26" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>26</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>29</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>32</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>34</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>37</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>40</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -5280,13 +6419,13 @@
       </c>
       <c r="E43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -5294,626 +6433,2583 @@
         <v>7.3</v>
       </c>
       <c r="F44" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I49" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>48</v>
       </c>
       <c r="F50" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J50" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="I50" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>49</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>50</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>51</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>52</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H54" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I54" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>53</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>54</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>55</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>56</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>57</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>58</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>59</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F61" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I61" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>60</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>61</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>62</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>63</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>64</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>65</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>66</v>
       </c>
       <c r="F68" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I68" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="I68" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>67</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>68</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>69</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>70</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>71</v>
       </c>
-      <c r="C73" s="8">
+      <c r="B73" s="8">
         <v>7.6</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>72</v>
       </c>
-      <c r="C74" s="9">
+      <c r="B74" s="9">
         <v>7.7</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>73</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>74</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>75</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>76</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>77</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>78</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>79</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>80</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>81</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>82</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>83</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>84</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>85</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>86</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>87</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>88</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>89</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>90</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>91</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>92</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>93</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>94</v>
       </c>
       <c r="D96" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A97" s="4">
+        <v>95</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
+        <v>96</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A99" s="4">
+        <v>97</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I99" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="I96" s="4" t="s">
+    </row>
+    <row r="100" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A100" s="4">
+        <v>98</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B101" s="14">
+        <v>7.8</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A102" s="4">
+        <v>99</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="4">
+        <v>100</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A104" s="4">
+        <v>101</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="4">
+        <v>102</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A106" s="4">
+        <v>103</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A107" s="4">
+        <v>104</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A108" s="4">
+        <v>105</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" s="4">
+        <v>106</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="4">
+        <v>107</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="4">
+        <v>108</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="4">
+        <v>109</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A113" s="4">
+        <v>110</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="4">
+        <v>111</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="4">
+        <v>112</v>
+      </c>
+      <c r="B116" s="9">
+        <v>7.7</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="4">
+        <v>113</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="4">
+        <v>114</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="4">
+        <v>115</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="4">
+        <v>116</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A121" s="4">
+        <v>117</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="4">
+        <v>118</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="4">
+        <v>119</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A125" s="4">
+        <v>120</v>
+      </c>
+      <c r="B125" s="9">
+        <v>7.9</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="I125" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="4">
+        <v>121</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="4">
+        <v>122</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="4">
+        <v>123</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I128" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A129" s="4">
+        <v>124</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="4">
+        <v>125</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="I130" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A131" s="4">
+        <v>126</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="4">
+        <v>127</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="4">
+        <v>128</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A134" s="4">
+        <v>129</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="4">
+        <v>130</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="4">
+        <v>131</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="4">
+        <v>132</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A138" s="4">
+        <v>133</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="I138" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="4">
+        <v>134</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="4">
+        <v>135</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="4">
+        <v>136</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A142" s="4">
+        <v>137</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A143" s="4">
+        <v>138</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="4">
+        <v>139</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="I144" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="4">
+        <v>140</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="4">
+        <v>141</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I146" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="4">
+        <v>142</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="4">
+        <v>143</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A149" s="4">
+        <v>144</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="I149" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A150" s="4">
+        <v>145</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I150" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B151" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I151" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A152" s="4">
+        <v>146</v>
+      </c>
+      <c r="B152" s="9">
+        <v>7.11</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="4">
+        <v>147</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D154" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B155" s="9">
+        <v>7.12</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A156" s="4">
+        <v>148</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="I156" s="16" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A157" s="4">
+        <v>149</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="I157" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A158" s="4">
+        <v>150</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I158" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A159" s="4">
+        <v>151</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="I159" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="4">
+        <v>152</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I160" s="17" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A161" s="4">
+        <v>153</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="I161" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="4">
+        <v>154</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I162" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A163" s="4">
+        <v>155</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="I163" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="4">
+        <v>156</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="I164" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="4">
+        <v>157</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="I165" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A166" s="4">
+        <v>158</v>
+      </c>
+      <c r="H166" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="I166" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A167" s="4">
+        <v>159</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="I167" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="4">
+        <v>160</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="I168" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="4">
+        <v>161</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="I169" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="4">
+        <v>162</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="4">
+        <v>163</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="I171" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="4">
+        <v>164</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="4">
+        <v>165</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="4">
+        <v>166</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A175" s="4">
+        <v>167</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="4">
+        <v>168</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="I176" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A177" s="4">
+        <v>169</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="4">
+        <v>170</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="4">
+        <v>171</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="4">
+        <v>172</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="4">
+        <v>173</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="I181" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="4">
+        <v>174</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="I182" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="4">
+        <v>175</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="4">
+        <v>176</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="4">
+        <v>177</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="4">
+        <v>178</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A187" s="4">
+        <v>179</v>
+      </c>
+      <c r="H187" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="4">
+        <v>180</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="4">
+        <v>181</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="4">
+        <v>182</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="4">
+        <v>183</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="4">
+        <v>184</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="4">
+        <v>185</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="4">
+        <v>186</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A195" s="4">
+        <v>187</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A196" s="4">
+        <v>188</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="H196" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="4">
+        <v>189</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="I197" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A198" s="4">
+        <v>190</v>
+      </c>
+      <c r="B198" s="9">
+        <v>7.13</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="I198" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A199" s="4">
+        <v>191</v>
+      </c>
+      <c r="B199" s="9">
+        <v>7.14</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="G199" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A201" s="4">
+        <v>192</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A202" s="4">
+        <v>193</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A203" s="4">
+        <v>194</v>
+      </c>
+      <c r="D203" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="G203" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="H203" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="4">
+        <v>195</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A205" s="4">
+        <v>196</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="I206" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B207" s="20"/>
+      <c r="D207" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="I207" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B208" s="12">
+        <v>7.14</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="H208" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A209" s="4">
+        <v>198</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="H209" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="I209" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="4">
+        <v>199</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="4">
+        <v>200</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="H211" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="4">
+        <v>201</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="4">
+        <v>202</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A214" s="4">
+        <v>203</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A215" s="4">
+        <v>204</v>
+      </c>
+      <c r="F215" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="H215" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="I215" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A216" s="4">
+        <v>205</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="I216" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="4">
+        <v>206</v>
+      </c>
+      <c r="H217" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I217" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="4">
+        <v>207</v>
+      </c>
+      <c r="H218" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="I218" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A219" s="4">
+        <v>208</v>
+      </c>
+      <c r="H219" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="I219" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A220" s="4">
+        <v>209</v>
+      </c>
+      <c r="H220" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="I220" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="4">
+        <v>210</v>
+      </c>
+      <c r="H221" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I221" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A222" s="4">
+        <v>211</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="H222" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="I222" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="4">
+        <v>212</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="H223" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I223" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="4">
+        <v>213</v>
+      </c>
+      <c r="H224" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="H225" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="I225" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A226" s="4">
+        <v>214</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="H226" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="I226" s="4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="4">
+        <v>215</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="4">
+        <v>216</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="4">
+        <v>217</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="I229" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="4">
+        <v>218</v>
+      </c>
+      <c r="H230" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A231" s="4">
+        <v>219</v>
+      </c>
+      <c r="H231" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="I231" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="4">
+        <v>220</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="H232" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="4">
+        <v>221</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="H233" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="I233" s="19" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="4">
+        <v>222</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H234" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="I234" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="4">
+        <v>223</v>
+      </c>
+      <c r="H235" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="I235" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="4">
+        <v>224</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I236" s="19" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A237" s="4">
+        <v>225</v>
+      </c>
+      <c r="B237" s="9">
+        <v>7.15</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="H237" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="I237" s="20" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A238" s="4">
+        <v>226</v>
+      </c>
+      <c r="B238" s="20"/>
+      <c r="F238" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="I238" s="20" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="4">
+        <v>227</v>
+      </c>
+      <c r="B239" s="20"/>
+      <c r="D239" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="I239" s="20"/>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="4">
+        <v>228</v>
+      </c>
+      <c r="B240" s="20"/>
+      <c r="D240" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="I240" s="20"/>
+    </row>
+    <row r="241" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A241" s="4">
+        <v>229</v>
+      </c>
+      <c r="B241" s="20"/>
+      <c r="F241" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="I241" s="20"/>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="4">
+        <v>230</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="4">
+        <v>231</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A244" s="4">
+        <v>232</v>
+      </c>
+      <c r="B244" s="9">
+        <v>7.16</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="H244" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="I244" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A245" s="4">
+        <v>233</v>
+      </c>
+      <c r="B245" s="20"/>
+      <c r="F245" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="I245" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="4">
+        <v>234</v>
+      </c>
+      <c r="B246" s="20"/>
+      <c r="D246" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="I246" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A247" s="4">
+        <v>235</v>
+      </c>
+      <c r="B247" s="20"/>
+      <c r="D247" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="H247" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="4">
+        <v>236</v>
+      </c>
+      <c r="B248" s="20"/>
+      <c r="H248" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="I248" s="4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="4">
+        <v>237</v>
+      </c>
+      <c r="B249" s="20"/>
+      <c r="H249" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="4">
+        <v>238</v>
+      </c>
+      <c r="B250" s="20"/>
+      <c r="F250" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="I250" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A251" s="4">
+        <v>239</v>
+      </c>
+      <c r="B251" s="20"/>
+      <c r="F251" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="I251" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A252" s="4">
+        <v>240</v>
+      </c>
+      <c r="B252" s="20"/>
+      <c r="G252" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="I252" s="4" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A253" s="4">
+        <v>241</v>
+      </c>
+      <c r="B253" s="20"/>
+      <c r="F253" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="G253" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A254" s="4">
+        <v>242</v>
+      </c>
+      <c r="B254" s="20"/>
+      <c r="F254" s="4" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B255" s="20"/>
+      <c r="F255" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="4">
+        <v>244</v>
+      </c>
+      <c r="B256" s="20"/>
+      <c r="G256" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="I256" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A257" s="4">
+        <v>245</v>
+      </c>
+      <c r="B257" s="20"/>
+      <c r="F257" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="I257" s="4" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A258" s="4">
         <v>246</v>
       </c>
-    </row>
-    <row r="97" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="H97" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="101" spans="3:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C101" s="8">
-        <v>7.8</v>
-      </c>
-      <c r="H101" s="8" t="s">
-        <v>208</v>
+      <c r="B258" s="20"/>
+      <c r="F258" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="G258" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A259" s="4">
+        <v>247</v>
+      </c>
+      <c r="B259" s="20"/>
+      <c r="F259" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="I259" s="4" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="4">
+        <v>248</v>
+      </c>
+      <c r="B260" s="20"/>
+      <c r="G260" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="I260" s="4" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A261" s="4">
+        <v>249</v>
+      </c>
+      <c r="B261" s="20"/>
+      <c r="G261" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="H261" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="I261" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A262" s="4">
+        <v>250</v>
+      </c>
+      <c r="B262" s="20"/>
+      <c r="F262" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="I262" s="4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="4">
+        <v>251</v>
+      </c>
+      <c r="B263" s="20"/>
+      <c r="F263" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="I263" s="4" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A264" s="4">
+        <v>252</v>
+      </c>
+      <c r="B264" s="20"/>
+      <c r="F264" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="G264" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="H264" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="I264" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A265" s="4">
+        <v>253</v>
+      </c>
+      <c r="B265" s="20"/>
+      <c r="F265" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="G265" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="H265" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="I265" s="4" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="4">
+        <v>254</v>
+      </c>
+      <c r="B266" s="20"/>
+      <c r="F266" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="H266" s="4" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B267" s="20"/>
+      <c r="F267" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="H267" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="I267" s="4" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B268" s="20"/>
+      <c r="F268" s="4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B269" s="20"/>
+      <c r="D269" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="H269" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B270" s="20"/>
+      <c r="H270" s="4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D272" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="274" spans="4:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="D274" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="I274" s="4" t="s">
+        <v>461</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57E4F1F-C950-4A27-AF75-D7439B97B581}">
   <dimension ref="A2:Q45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>1</v>
       </c>
@@ -5933,7 +9029,7 @@
         <v>0.38654923450307577</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1.57</v>
       </c>
@@ -5949,7 +9045,7 @@
         <v>411.95</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1.62</v>
       </c>
@@ -5965,7 +9061,7 @@
         <v>424.73</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1.6559999999999999</v>
       </c>
@@ -5981,7 +9077,7 @@
         <v>433.62</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="10">
         <v>1.7969999999999999</v>
       </c>
@@ -5997,7 +9093,7 @@
         <v>465.24</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1.84</v>
       </c>
@@ -6013,7 +9109,7 @@
         <v>474.38</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>3</v>
       </c>
@@ -6040,7 +9136,7 @@
         <v>599.08872447978786</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -6060,7 +9156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1.7820607373170305</v>
       </c>
@@ -6077,7 +9173,7 @@
         <v>456.00000740102411</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1.6557005420069286</v>
       </c>
@@ -6094,23 +9190,23 @@
         <v>456.03979015218101</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D23" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0</v>
       </c>
@@ -6129,7 +9225,7 @@
         <v>6.8841283483509805</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2</v>
       </c>
@@ -6148,7 +9244,7 @@
         <v>6.883196157481434</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -6167,7 +9263,7 @@
         <v>6.8840771516275598</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>8</v>
       </c>
@@ -6186,7 +9282,7 @@
         <v>6.8787589185405453</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>16</v>
       </c>
@@ -6205,7 +9301,7 @@
         <v>6.8377082806701024</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>32</v>
       </c>
@@ -6224,7 +9320,7 @@
         <v>6.5374739002084548</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>56</v>
       </c>
@@ -6243,7 +9339,7 @@
         <v>5.512460535664947</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>72</v>
       </c>
@@ -6262,7 +9358,7 @@
         <v>4.7502224576872303</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>128</v>
       </c>
@@ -6281,15 +9377,15 @@
         <v>1.4213718877325867</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>0.9</v>
       </c>
@@ -6304,7 +9400,7 @@
         <v>89.295627373824047</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0.7</v>
       </c>
@@ -6315,7 +9411,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>0.64700000000000002</v>
       </c>
@@ -6323,10 +9419,10 @@
         <v>503</v>
       </c>
       <c r="Q38" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0.63</v>
       </c>
@@ -6334,10 +9430,10 @@
         <v>477</v>
       </c>
       <c r="Q39" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0.62</v>
       </c>
@@ -6345,7 +9441,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>0.61499999999999999</v>
       </c>
@@ -6353,7 +9449,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0.42</v>
       </c>
@@ -6361,7 +9457,7 @@
         <v>212.19</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0.63935225868978396</v>
       </c>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1FF696-4EC5-424B-82CD-58BB310F9B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CD0387-233C-4F99-AFB0-FF632D723D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="18672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="555">
   <si>
     <t>A</t>
   </si>
@@ -1591,9 +1591,6 @@
     <t>T8/T9 too high no intersection, T10/T3 too low</t>
   </si>
   <si>
-    <t>second laminar for steady state solution</t>
-  </si>
-  <si>
     <t>transient with momentum coupled</t>
   </si>
   <si>
@@ -1725,6 +1722,54 @@
   </si>
   <si>
     <t>need to check the velocity simulation</t>
+  </si>
+  <si>
+    <t>decrease input Factor to capture insulation temperature, then alter properties for the rest</t>
+  </si>
+  <si>
+    <t>whatever RayTracing change since #235 e.g absorb couldn't be applied because it was locked on Study 2</t>
+  </si>
+  <si>
+    <t>all temperatures too low, bring properties to original values</t>
+  </si>
+  <si>
+    <t>abs=0.9</t>
+  </si>
+  <si>
+    <t>emis=0.9, emis_ins=0.6, M_emis=0.2</t>
+  </si>
+  <si>
+    <t>cp_ins=880; k_ins=0.08, rho_ins=0.16</t>
+  </si>
+  <si>
+    <t>ISSUE w Raytracing since #235 or #252</t>
+  </si>
+  <si>
+    <t>THE CROSSSECTION OF T8/T9 is a characteristic of the system</t>
+  </si>
+  <si>
+    <t>second laminar for steady state solution qlpm_t</t>
+  </si>
+  <si>
+    <t>qlpm</t>
+  </si>
+  <si>
+    <t>qlpm was qlpm_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> qlpm_t</t>
+  </si>
+  <si>
+    <t>very early intersection</t>
+  </si>
+  <si>
+    <t>no intersection or too far away</t>
+  </si>
+  <si>
+    <t>follow properties advised by GPT</t>
+  </si>
+  <si>
+    <t>same with #263 w/ qlpm</t>
   </si>
 </sst>
 </file>
@@ -4686,14 +4731,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>268</xdr:row>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>279</xdr:row>
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1390650</xdr:colOff>
-      <xdr:row>268</xdr:row>
+      <xdr:colOff>1402080</xdr:colOff>
+      <xdr:row>279</xdr:row>
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -4709,7 +4754,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="81728310"/>
+          <a:off x="678180" y="82299810"/>
           <a:ext cx="13959840" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -5925,7 +5970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B19FA9-A01B-4042-9995-5A31C36523E9}">
-  <dimension ref="A2:J274"/>
+  <dimension ref="A2:J286"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="4"/>
@@ -8711,11 +8756,11 @@
         <v>235</v>
       </c>
       <c r="B247" s="20"/>
-      <c r="D247" s="4" t="s">
+      <c r="D247" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="F247" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="F247" s="4" t="s">
-        <v>496</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>375</v>
@@ -8730,7 +8775,7 @@
         <v>347</v>
       </c>
       <c r="I248" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
@@ -8748,10 +8793,10 @@
       </c>
       <c r="B250" s="20"/>
       <c r="F250" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="I250" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="I250" s="4" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="251" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8760,10 +8805,10 @@
       </c>
       <c r="B251" s="20"/>
       <c r="F251" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="I251" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="I251" s="4" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="252" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8772,10 +8817,10 @@
       </c>
       <c r="B252" s="20"/>
       <c r="G252" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I252" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="253" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8784,10 +8829,10 @@
       </c>
       <c r="B253" s="20"/>
       <c r="F253" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="254" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8796,13 +8841,13 @@
       </c>
       <c r="B254" s="20"/>
       <c r="F254" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B255" s="20"/>
       <c r="F255" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
@@ -8811,10 +8856,10 @@
       </c>
       <c r="B256" s="20"/>
       <c r="G256" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="I256" s="4" t="s">
         <v>508</v>
-      </c>
-      <c r="I256" s="4" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8823,10 +8868,10 @@
       </c>
       <c r="B257" s="20"/>
       <c r="F257" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="I257" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="I257" s="4" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="258" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -8835,10 +8880,10 @@
       </c>
       <c r="B258" s="20"/>
       <c r="F258" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="259" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8847,10 +8892,10 @@
       </c>
       <c r="B259" s="20"/>
       <c r="F259" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I259" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -8859,10 +8904,10 @@
       </c>
       <c r="B260" s="20"/>
       <c r="G260" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="I260" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="I260" s="4" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="261" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8871,13 +8916,13 @@
       </c>
       <c r="B261" s="20"/>
       <c r="G261" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="H261" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="H261" s="4" t="s">
-        <v>519</v>
-      </c>
       <c r="I261" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="262" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8886,10 +8931,10 @@
       </c>
       <c r="B262" s="20"/>
       <c r="F262" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="I262" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="I262" s="4" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
@@ -8898,10 +8943,10 @@
       </c>
       <c r="B263" s="20"/>
       <c r="F263" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I263" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8910,16 +8955,16 @@
       </c>
       <c r="B264" s="20"/>
       <c r="F264" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G264" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="G264" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="H264" s="4" t="s">
-        <v>520</v>
+      <c r="H264" s="13" t="s">
+        <v>519</v>
       </c>
       <c r="I264" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="265" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8928,16 +8973,16 @@
       </c>
       <c r="B265" s="20"/>
       <c r="F265" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="G265" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="G265" s="4" t="s">
+      <c r="H265" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="I265" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="H265" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="I265" s="4" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
@@ -8946,55 +8991,175 @@
       </c>
       <c r="B266" s="20"/>
       <c r="F266" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="4">
+        <v>255</v>
+      </c>
       <c r="B267" s="20"/>
       <c r="F267" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H267" s="4" t="s">
         <v>373</v>
       </c>
       <c r="I267" s="4" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B268" s="20"/>
-      <c r="F268" s="4" t="s">
+    </row>
+    <row r="269" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A269" s="4">
+        <v>257</v>
+      </c>
+      <c r="B269" s="20"/>
+      <c r="F269" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B270" s="20"/>
+      <c r="I270" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B271" s="20"/>
+      <c r="H271" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="I271" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A272" s="4">
+        <v>258</v>
+      </c>
+      <c r="B272" s="20"/>
+      <c r="F272" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="G272" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="H272" s="20" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B273" s="20"/>
+      <c r="H273" s="20"/>
+      <c r="I273" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="4">
+        <v>259</v>
+      </c>
+      <c r="B274" s="20"/>
+      <c r="D274" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H274" s="20"/>
+      <c r="I274" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="4">
+        <v>260</v>
+      </c>
+      <c r="B275" s="20"/>
+      <c r="D275" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="H275" s="20"/>
+      <c r="I275" s="4" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="4">
+        <v>261</v>
+      </c>
+      <c r="B276" s="20"/>
+      <c r="D276" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="H276" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="I276" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="4">
+        <v>262</v>
+      </c>
+      <c r="B277" s="20"/>
+      <c r="D277" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="H277" s="20"/>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="4">
+        <v>263</v>
+      </c>
+      <c r="B278" s="20"/>
+      <c r="D278" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="H278" s="20"/>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B279" s="20"/>
+      <c r="D279" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="H279" s="20"/>
+    </row>
+    <row r="280" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B280" s="20"/>
+      <c r="D280" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B281" s="20"/>
+      <c r="D281" s="4" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="269" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B269" s="20"/>
-      <c r="D269" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="H269" s="4" t="s">
+      <c r="H281" s="4" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B270" s="20"/>
-      <c r="H270" s="4" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D272" s="4" t="s">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B282" s="20"/>
+      <c r="H282" s="4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D284" s="4" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="274" spans="4:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="D274" s="4" t="s">
+    <row r="286" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="D286" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="I274" s="4" t="s">
+      <c r="I286" s="4" t="s">
         <v>461</v>
       </c>
     </row>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CD0387-233C-4F99-AFB0-FF632D723D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF54DBE-6BF7-4250-A0BD-A9531A875905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="18672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0D" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Optical" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,6 +36,33 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={2C9673A5-534D-4FC2-A792-912F01D1091C}</author>
+    <author>tc={1195A4A6-AC02-43B0-9B61-6F9ADFAE84CE}</author>
+  </authors>
+  <commentList>
+    <comment ref="B39" authorId="0" shapeId="0" xr:uid="{2C9673A5-534D-4FC2-A792-912F01D1091C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    10^A</t>
+      </text>
+    </comment>
+    <comment ref="D40" authorId="1" shapeId="0" xr:uid="{1195A4A6-AC02-43B0-9B61-6F9ADFAE84CE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    10^</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="697">
   <si>
     <t>A</t>
   </si>
@@ -1771,6 +1799,432 @@
   <si>
     <t>same with #263 w/ qlpm</t>
   </si>
+  <si>
+    <t>T8 too high, rest too low</t>
+  </si>
+  <si>
+    <t>CHANGED dimensions of insulation according to measurements</t>
+  </si>
+  <si>
+    <t>all temperatures too low, T8/T9 intersect early as in the previous simulations, but T2 is 70-100K higher.</t>
+  </si>
+  <si>
+    <t>T2 moved to z=D_tot+40</t>
+  </si>
+  <si>
+    <t>I_factor=1.9 (Irradiance measured 456, absorbed 456*0.85, simulated 203)</t>
+  </si>
+  <si>
+    <t>T9 and T3 close enough to Exp, T8/T9 intersection still at the same time, T10 too high, T8 too low</t>
+  </si>
+  <si>
+    <t>T9 higher, T8 lower, T10 higher, T3 lower, T2 higher, T8/T9 intersect at the same place</t>
+  </si>
+  <si>
+    <t>qlpm_t*0.9</t>
+  </si>
+  <si>
+    <t>Returned to TRACEPRO; irradiance 456*0.85</t>
+  </si>
+  <si>
+    <t>T8 steady is ok, all others similar to #267</t>
+  </si>
+  <si>
+    <t>solid temperatures too high, gas too low</t>
+  </si>
+  <si>
+    <t>rearranged boundary conditions</t>
+  </si>
+  <si>
+    <t>T10 very good, T8/T9 very high no interesection, T3 very low</t>
+  </si>
+  <si>
+    <t>qlpm*2</t>
+  </si>
+  <si>
+    <t>stopped too high</t>
+  </si>
+  <si>
+    <t>qlpm*5</t>
+  </si>
+  <si>
+    <t>still high (1500K)</t>
+  </si>
+  <si>
+    <t>qlpm*10</t>
+  </si>
+  <si>
+    <t>higher velocity brings intersection earlier</t>
+  </si>
+  <si>
+    <t>fixed alumina diameter 29.4-&gt;38.8</t>
+  </si>
+  <si>
+    <t>cleaned up input/boundary conditions</t>
+  </si>
+  <si>
+    <t>remove Temperature from last part of the tube</t>
+  </si>
+  <si>
+    <t>need to decrease front losses</t>
+  </si>
+  <si>
+    <t>removed front and back losses</t>
+  </si>
+  <si>
+    <t>absorb0.85, I_factor1.1</t>
+  </si>
+  <si>
+    <t>reinstated losses</t>
+  </si>
+  <si>
+    <t>did not help to increase incoming radiation</t>
+  </si>
+  <si>
+    <t>Cps x2</t>
+  </si>
+  <si>
+    <t>some improvement</t>
+  </si>
+  <si>
+    <t>I_factor 1</t>
+  </si>
+  <si>
+    <t>Cps x4</t>
+  </si>
+  <si>
+    <t>getting better</t>
+  </si>
+  <si>
+    <t>no reradiation front</t>
+  </si>
+  <si>
+    <t>ks x2</t>
+  </si>
+  <si>
+    <t>intersection at the right point, temperatures lower, reduce losses</t>
+  </si>
+  <si>
+    <t>ins_k /3</t>
+  </si>
+  <si>
+    <t>length profile excellent, but time not that great</t>
+  </si>
+  <si>
+    <t>ins_k &amp; ins_cp *1.5</t>
+  </si>
+  <si>
+    <t>almost the same with #281</t>
+  </si>
+  <si>
+    <t>ins_properties back to normal</t>
+  </si>
+  <si>
+    <t>no good</t>
+  </si>
+  <si>
+    <t>I_factor 1.1</t>
+  </si>
+  <si>
+    <t>closer, but still not enough, T1 is surprisignly low</t>
+  </si>
+  <si>
+    <t>qlpm_t; move T1 from D_tot to very closer to the receiver</t>
+  </si>
+  <si>
+    <t>ins_k /10</t>
+  </si>
+  <si>
+    <t>slight increase of temperatures, cross section point moved earlier, Tinsulation at the expected levels</t>
+  </si>
+  <si>
+    <t>ins_cp /5</t>
+  </si>
+  <si>
+    <t>ins_cp normal; Cps normal; ks /4</t>
+  </si>
+  <si>
+    <t>cross section too early, temperatures not good</t>
+  </si>
+  <si>
+    <t>ks normal, Cps x4.5</t>
+  </si>
+  <si>
+    <t>ks /2, Cps x4</t>
+  </si>
+  <si>
+    <t>R_chan 1.65; t_chan 0.35</t>
+  </si>
+  <si>
+    <t>ks x2, Cps x4</t>
+  </si>
+  <si>
+    <t>I_factor 1.2</t>
+  </si>
+  <si>
+    <t>like #285 with higher I_factor; temperture higher, length profile ok, rest like before</t>
+  </si>
+  <si>
+    <t>Cps x3</t>
+  </si>
+  <si>
+    <t>ins_k=0.05 a bit higher than air</t>
+  </si>
+  <si>
+    <t>T3 to center of symmetry</t>
+  </si>
+  <si>
+    <t>all around insulation</t>
+  </si>
+  <si>
+    <t>temperatures (except T2) at the correct level but not steady state</t>
+  </si>
+  <si>
+    <t>add convective and radiative losses</t>
+  </si>
+  <si>
+    <t>ins_cp = 1360 [Wang 2024], ksx3</t>
+  </si>
+  <si>
+    <t>needs abs=0.99 for inner surface</t>
+  </si>
+  <si>
+    <t>no intersectoin, slight decrease of temperatures</t>
+  </si>
+  <si>
+    <t>ks, cps=normal</t>
+  </si>
+  <si>
+    <t>added thin layer 1mm of air around SiC inside alumina adaptor</t>
+  </si>
+  <si>
+    <t>interesting length profile, temporal not that great</t>
+  </si>
+  <si>
+    <t>added thin layer 1mm of air around the whole receiver</t>
+  </si>
+  <si>
+    <t>made it 0.5mm and added another around alumina adaptor</t>
+  </si>
+  <si>
+    <t>ks x2, Cps normal</t>
+  </si>
+  <si>
+    <t>thermal contact 1mm</t>
+  </si>
+  <si>
+    <t>receiver thermal contact 2mm</t>
+  </si>
+  <si>
+    <t>ks x3</t>
+  </si>
+  <si>
+    <t>ks x3  Cps x normal</t>
+  </si>
+  <si>
+    <t>final values kind of ok but not the profiles</t>
+  </si>
+  <si>
+    <t>receiver thermal contact 5mm</t>
+  </si>
+  <si>
+    <t>needs I_factor 1.15</t>
+  </si>
+  <si>
+    <t>lower temperatures</t>
+  </si>
+  <si>
+    <t>still lower temperatures</t>
+  </si>
+  <si>
+    <t>I_factor 1.15</t>
+  </si>
+  <si>
+    <t>perfect match T8/T9, all others only the steady state</t>
+  </si>
+  <si>
+    <t>for E78</t>
+  </si>
+  <si>
+    <t>T8/T9 too high, all others too low</t>
+  </si>
+  <si>
+    <t>kins = 0.0001</t>
+  </si>
+  <si>
+    <t>overall temperatures too low, intersection at the correct time</t>
+  </si>
+  <si>
+    <t>ks &amp;  Cps x normal</t>
+  </si>
+  <si>
+    <t>not a good approach</t>
+  </si>
+  <si>
+    <t>disabled thermal contact</t>
+  </si>
+  <si>
+    <t>kins = 0.001</t>
+  </si>
+  <si>
+    <t>317x</t>
+  </si>
+  <si>
+    <t>kins = 0.01</t>
+  </si>
+  <si>
+    <t>for E68</t>
+  </si>
+  <si>
+    <t>T2 at level, others kind of ok, but temporal profiles not; very low value</t>
+  </si>
+  <si>
+    <t>T8 high all others lower</t>
+  </si>
+  <si>
+    <t>emis_area</t>
+  </si>
+  <si>
+    <t>back to 1, removed cavity reradiation</t>
+  </si>
+  <si>
+    <t>T3 still lower</t>
+  </si>
+  <si>
+    <t>enabled thermal receiver thermal contact</t>
+  </si>
+  <si>
+    <t>T10 increased too high</t>
+  </si>
+  <si>
+    <t>ks*2</t>
+  </si>
+  <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>Cps x3 ks norm</t>
+  </si>
+  <si>
+    <t>time profile good for gas, higher temperatures for T9</t>
+  </si>
+  <si>
+    <t>MODIFIED to MATCH 3D #324</t>
+  </si>
+  <si>
+    <t>ks*1.5</t>
+  </si>
+  <si>
+    <t>kins = 0.05</t>
+  </si>
+  <si>
+    <t>kins = 0.078</t>
+  </si>
+  <si>
+    <t>Cps norm</t>
+  </si>
+  <si>
+    <t>T9 T10 T11 T12</t>
+  </si>
+  <si>
+    <t>kins = 0.1</t>
+  </si>
+  <si>
+    <t>enabled thermal contacts 1mm</t>
+  </si>
+  <si>
+    <t>Cps  x3</t>
+  </si>
+  <si>
+    <t>remove 40mm resistance with known temperature and added the whole cylinder with ambient temperature</t>
+  </si>
+  <si>
+    <t>ks*3</t>
+  </si>
+  <si>
+    <t>profile of h incorrect</t>
+  </si>
+  <si>
+    <t>thermal contact with fel 3mm</t>
+  </si>
+  <si>
+    <t>ks</t>
+  </si>
+  <si>
+    <t>k affects only Pr calculation</t>
+  </si>
+  <si>
+    <t>very small impact</t>
+  </si>
+  <si>
+    <t>added 3rd solid for insulation+metal, fixed error with boundary condition</t>
+  </si>
+  <si>
+    <t>added 50K on outer boundary</t>
+  </si>
+  <si>
+    <t>good match</t>
+  </si>
+  <si>
+    <t>Cps  x2</t>
+  </si>
+  <si>
+    <t>h betweeb solids to 500, removed</t>
+  </si>
+  <si>
+    <t>Cps -&gt; Munro 2x</t>
+  </si>
+  <si>
+    <t>1x</t>
+  </si>
+  <si>
+    <t>profiles are not good</t>
+  </si>
+  <si>
+    <t>2x</t>
+  </si>
+  <si>
+    <t>corrected rho and cp for insulation+metal</t>
+  </si>
+  <si>
+    <t>added losses from front and back</t>
+  </si>
+  <si>
+    <t>all T avg; failed</t>
+  </si>
+  <si>
+    <t>T9 &amp; T10</t>
+  </si>
+  <si>
+    <t>E78</t>
+  </si>
+  <si>
+    <t>I 0.7 * 0.7</t>
+  </si>
+  <si>
+    <t>T8 T9 T10</t>
+  </si>
+  <si>
+    <t>qlpm low</t>
+  </si>
+  <si>
+    <t>not good</t>
+  </si>
+  <si>
+    <t>E67</t>
+  </si>
+  <si>
+    <t>very good</t>
+  </si>
+  <si>
+    <t>not great profiles</t>
+  </si>
+  <si>
+    <t>fair enough</t>
+  </si>
+  <si>
+    <t>diameter instead of length on h, removed</t>
+  </si>
 </sst>
 </file>
 
@@ -1780,7 +2234,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1818,6 +2272,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1882,7 +2342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1936,6 +2396,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2284,6 +2745,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2291,7 +2753,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3507,6 +3968,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3514,7 +3976,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4730,16 +5191,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>279</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>605790</xdr:colOff>
+      <xdr:row>361</xdr:row>
+      <xdr:rowOff>1905</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1402080</xdr:colOff>
-      <xdr:row>279</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
+      <xdr:colOff>1314450</xdr:colOff>
+      <xdr:row>361</xdr:row>
+      <xdr:rowOff>1905</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4754,8 +5215,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="678180" y="82299810"/>
-          <a:ext cx="13959840" cy="0"/>
+          <a:off x="605790" y="89978865"/>
+          <a:ext cx="14333220" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -4966,9 +5427,15 @@
       <inkml:brushProperty name="height" value="0.05" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">2 140 2292,'-2'-4'576,"4"-1"-180,1 0-396,1-8-600,2 0-1152</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="233.91">115 0 4424,'-3'11'8874,"-3"31"-4772,0 8-2336,-3-17-811,7-26-738,0-2-1,0 3 1,1-1-1,-1 0 1,1 0-1,-1 12 1,42-32-5010,-21-3 333,-1-8-2215</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2 140 2292,'-2'-4'576,"4"-2"-180,1 2-396,3-10-600,0 2-1152</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="233.91">131 0 4424,'-3'11'8874,"-5"31"-4772,2 8-2336,-5-17-811,9-26-738,0-2-1,0 2 1,1 0-1,-1 2 1,1-2-1,-1 11 1,46-31-5010,-21-4 333,-3-6-2215</inkml:trace>
 </inkml:ink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Kakosimos, Konstantinos E" id="{276BCB23-7094-4A82-96C4-28630CE0F82D}" userId="S::k.kakosimos@tamu.edu::c3fdba53-c044-412b-a302-30eebab60827" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5232,15 +5699,26 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B39" dT="2025-07-23T05:22:20.02" personId="{276BCB23-7094-4A82-96C4-28630CE0F82D}" id="{2C9673A5-534D-4FC2-A792-912F01D1091C}">
+    <text>10^A</text>
+  </threadedComment>
+  <threadedComment ref="D40" dT="2025-07-23T05:38:31.92" personId="{276BCB23-7094-4A82-96C4-28630CE0F82D}" id="{1195A4A6-AC02-43B0-9B61-6F9ADFAE84CE}">
+    <text>10^</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:O40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:P68"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="15" max="15" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="46.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5275,16 +5753,19 @@
         <v>64</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5321,17 +5802,17 @@
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.4</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>499.47699999999998</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5347,14 +5828,14 @@
       <c r="E4">
         <v>0.66</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>528.26599999999996</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5373,14 +5854,14 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>473.34</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5396,11 +5877,11 @@
       <c r="G6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5416,14 +5897,14 @@
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>604.08600000000001</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5439,11 +5920,11 @@
       <c r="E8">
         <v>0.7</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5459,11 +5940,11 @@
       <c r="E9">
         <v>0.63</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5479,14 +5960,14 @@
       <c r="G10">
         <v>1.2</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>500</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -5502,14 +5983,14 @@
       <c r="E11">
         <v>0.64</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>480</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -5525,39 +6006,39 @@
       <c r="I12" t="s">
         <v>21</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>672</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="J13" t="s">
         <v>25</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="K14" t="s">
         <v>29</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>25612</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -5576,25 +6057,25 @@
       <c r="K15" t="s">
         <v>28</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>469</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>54</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -5607,44 +6088,44 @@
       <c r="D17">
         <v>25.984272299692599</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>465</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="E19">
         <v>0.84</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>850</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -5654,28 +6135,28 @@
       <c r="F21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>573</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="E22">
         <v>0.64</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>607</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -5691,14 +6172,14 @@
       <c r="E23">
         <v>0.7</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>502</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>21</v>
       </c>
@@ -5714,14 +6195,14 @@
       <c r="L24">
         <v>4.4000000000000004</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>1641</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>22</v>
       </c>
@@ -5737,28 +6218,28 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>1071</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="L26">
         <v>1</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>1892</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>24</v>
       </c>
@@ -5774,11 +6255,11 @@
       <c r="E27">
         <v>0.9</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>1354</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25</v>
       </c>
@@ -5795,21 +6276,21 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="E29">
         <v>0.7</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>502</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>27</v>
       </c>
@@ -5822,14 +6303,14 @@
       <c r="D30">
         <v>1.3738648256894E-4</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>502</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>28</v>
       </c>
@@ -5842,25 +6323,25 @@
       <c r="D31" s="2">
         <v>9.39537377217747E-5</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>0.6</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>522</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>30</v>
       </c>
@@ -5873,14 +6354,14 @@
       <c r="D33">
         <v>1.0263197679569199E-4</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>0</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>563</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>31</v>
       </c>
@@ -5899,11 +6380,11 @@
       <c r="G34">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>461</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>32</v>
       </c>
@@ -5919,11 +6400,11 @@
       <c r="K35" t="s">
         <v>73</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>33</v>
       </c>
@@ -5933,57 +6414,609 @@
       <c r="K36" t="s">
         <v>28</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>586</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="E37">
         <v>0.75</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="P38" s="21" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>35</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="B39">
+        <v>-1.5880535011177801</v>
+      </c>
+      <c r="C39">
+        <v>0.65091494933399197</v>
+      </c>
+      <c r="D39">
+        <v>3.6666969736259901E-2</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>0.7</v>
+      </c>
+      <c r="I39">
+        <v>7.8E-2</v>
+      </c>
+      <c r="O39">
+        <v>1140</v>
+      </c>
+      <c r="P39" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="B40">
+        <v>-1.62557011221157</v>
+      </c>
+      <c r="C40">
+        <v>0.64353970719628895</v>
+      </c>
+      <c r="D40">
+        <v>-5</v>
+      </c>
+      <c r="L40">
+        <v>3</v>
+      </c>
+      <c r="O40">
+        <v>975</v>
+      </c>
+      <c r="P40" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>37</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="O41">
+        <v>1140</v>
+      </c>
+      <c r="P41" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>38</v>
+      </c>
+      <c r="B42">
+        <v>-1.62633085814944</v>
+      </c>
+      <c r="C42">
+        <v>0.64384726379398405</v>
+      </c>
+      <c r="D42">
+        <v>-4.2152141852378398</v>
+      </c>
+      <c r="E42">
+        <v>1.2</v>
+      </c>
+      <c r="M42">
+        <v>3</v>
+      </c>
+      <c r="O42">
+        <v>975</v>
+      </c>
+      <c r="P42" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>39</v>
+      </c>
+      <c r="B43">
+        <v>-1.62557011221157</v>
+      </c>
+      <c r="C43">
+        <v>0.64353970719628895</v>
+      </c>
+      <c r="D43">
+        <v>-5</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>3</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>40</v>
+      </c>
+      <c r="B44">
+        <v>-0.21738961927643199</v>
+      </c>
+      <c r="C44">
+        <v>0.224136849475497</v>
+      </c>
+      <c r="D44">
+        <v>-4.38627582837346</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="O44">
+        <v>1496</v>
+      </c>
+      <c r="P44" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>41</v>
+      </c>
+      <c r="B45">
+        <v>-0.120453173998853</v>
+      </c>
+      <c r="C45">
+        <v>8.2527627411642504E-2</v>
+      </c>
+      <c r="D45">
+        <v>-5</v>
+      </c>
+      <c r="E45">
+        <v>0.7</v>
+      </c>
+      <c r="O45">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>42</v>
+      </c>
+      <c r="B46">
+        <v>-6.3694404355623402E-2</v>
+      </c>
+      <c r="C46">
+        <v>6.9338798965457998E-2</v>
+      </c>
+      <c r="D46">
+        <v>-3.66322327238499</v>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+      <c r="O46">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>43</v>
+      </c>
+      <c r="B47">
+        <v>-5.6187532274797197E-2</v>
+      </c>
+      <c r="C47">
+        <v>6.7192097637876202E-2</v>
+      </c>
+      <c r="D47">
+        <v>-3.85853069192695</v>
+      </c>
+      <c r="O47">
+        <v>999</v>
+      </c>
+      <c r="P47" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <v>-0.59913658322029595</v>
+      </c>
+      <c r="C48">
+        <v>0.23267951536977999</v>
+      </c>
+      <c r="D48">
+        <v>-4.54729113095385</v>
+      </c>
+      <c r="O48">
+        <v>1050</v>
+      </c>
+      <c r="P48" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>-3.0218416280894E-2</v>
+      </c>
+      <c r="C49">
+        <v>5.6553370855678999E-2</v>
+      </c>
+      <c r="D49">
+        <v>-5</v>
+      </c>
+      <c r="L49" t="s">
+        <v>679</v>
+      </c>
+      <c r="O49">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B50">
+        <v>2.32366143478863</v>
+      </c>
+      <c r="C50">
+        <v>5.2381129172708499E-2</v>
+      </c>
+      <c r="D50">
+        <v>1.15176621671389</v>
+      </c>
+      <c r="L50" t="s">
+        <v>680</v>
+      </c>
+      <c r="O50">
+        <v>1195</v>
+      </c>
+      <c r="P50" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <v>-0.11531413827813</v>
+      </c>
+      <c r="C51">
+        <v>0.110780162848843</v>
+      </c>
+      <c r="D51">
+        <v>-5</v>
+      </c>
+      <c r="F51">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L51" t="s">
+        <v>682</v>
+      </c>
+      <c r="O51">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B52">
+        <v>-5.9825795140801101E-2</v>
+      </c>
+      <c r="C52">
+        <v>8.3298389397967201E-2</v>
+      </c>
+      <c r="D52">
+        <v>-4.7822766948941098</v>
+      </c>
+      <c r="F52">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O52">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B53">
+        <v>0.163215104178386</v>
+      </c>
+      <c r="C53">
+        <v>0.110019492778361</v>
+      </c>
+      <c r="D53">
+        <v>-5</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <v>0.16620523432742201</v>
+      </c>
+      <c r="C54">
+        <v>0.10949611407786</v>
+      </c>
+      <c r="D54">
+        <v>-1.95188474207697</v>
+      </c>
+      <c r="O54">
+        <v>1880</v>
+      </c>
+      <c r="P54" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B55">
+        <v>0.113337590003834</v>
+      </c>
+      <c r="C55">
+        <v>0.113912815280584</v>
+      </c>
+      <c r="D55">
+        <v>-3.17711423761659</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="O55">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B56">
+        <v>0.115547627813837</v>
+      </c>
+      <c r="C56">
+        <v>0.113073002583607</v>
+      </c>
+      <c r="D56">
+        <v>-4.5277566109866303</v>
+      </c>
+      <c r="O56">
+        <v>1692</v>
+      </c>
+      <c r="P56" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <v>-3.3149389346669902E-2</v>
+      </c>
+      <c r="C57">
+        <v>5.74856315526577E-2</v>
+      </c>
+      <c r="D57">
+        <v>-5</v>
+      </c>
+      <c r="E57">
+        <v>0.7</v>
+      </c>
+      <c r="O57">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="P58" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B59">
+        <v>0.250054010925023</v>
+      </c>
+      <c r="C59">
+        <v>9.0017378931107103E-2</v>
+      </c>
+      <c r="D59">
+        <v>-3.5197283757326399</v>
+      </c>
+      <c r="O59">
+        <v>1746</v>
+      </c>
+      <c r="P59" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <v>-1.44059076725918</v>
+      </c>
+      <c r="C60">
+        <v>0.67522154899549303</v>
+      </c>
+      <c r="D60">
+        <v>-4.8807740743608301</v>
+      </c>
+      <c r="O60">
+        <v>1574</v>
+      </c>
+      <c r="P60" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B61">
+        <v>-1.21144890336943</v>
+      </c>
+      <c r="C61">
+        <v>0.594262978875436</v>
+      </c>
+      <c r="D61">
+        <v>-5</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="O61">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B62">
+        <v>-1.2070813277479999</v>
+      </c>
+      <c r="C62">
+        <v>0.49223109727618702</v>
+      </c>
+      <c r="D62">
+        <v>-5</v>
+      </c>
+      <c r="E62">
+        <v>0.7</v>
+      </c>
+      <c r="H62">
+        <v>0.7</v>
+      </c>
+      <c r="O62">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <v>-1.0012021396300801</v>
+      </c>
+      <c r="C63">
+        <v>0.40143186621960603</v>
+      </c>
+      <c r="D63">
+        <v>-5</v>
+      </c>
+      <c r="O63">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B64">
+        <v>-4.4248727373665302</v>
+      </c>
+      <c r="C64">
+        <v>2.0054297178263898</v>
+      </c>
+      <c r="D64">
+        <v>-0.92802622567503801</v>
+      </c>
+      <c r="O64">
+        <v>1528</v>
+      </c>
+      <c r="P64" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B65">
+        <v>-1.0608132419307801</v>
+      </c>
+      <c r="C65">
+        <v>0.415984490245218</v>
+      </c>
+      <c r="D65">
+        <v>-4.9695269901766101</v>
+      </c>
+      <c r="L65" t="s">
+        <v>682</v>
+      </c>
+      <c r="O65">
+        <v>1167</v>
+      </c>
+      <c r="P65" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <v>-1.1261289140861099</v>
+      </c>
+      <c r="C66">
+        <v>0.47186731215250699</v>
+      </c>
+      <c r="D66">
+        <v>-4.5038498068435002</v>
+      </c>
+      <c r="F66">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="O66">
+        <v>1002</v>
+      </c>
+      <c r="P66" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B67">
+        <v>-1.2035253749880399</v>
+      </c>
+      <c r="C67">
+        <v>0.49275278422355101</v>
+      </c>
+      <c r="D67">
+        <v>-4.83529833670908</v>
+      </c>
+      <c r="O67">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B68">
+        <v>-1.44395477402174</v>
+      </c>
+      <c r="C68">
+        <v>0.49278508137217503</v>
+      </c>
+      <c r="D68">
+        <v>-4.59924882828237</v>
+      </c>
+      <c r="O68">
+        <v>1121</v>
+      </c>
+      <c r="P68" t="s">
+        <v>696</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B19FA9-A01B-4042-9995-5A31C36523E9}">
-  <dimension ref="A2:J286"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:J370"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="4"/>
-    <col min="3" max="3" width="9.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="37.42578125" style="4" customWidth="1"/>
-    <col min="6" max="8" width="33.28515625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="55.140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="29.85546875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="2" width="9.109375" style="4"/>
+    <col min="3" max="3" width="9.6640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="33.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="37.44140625" style="4" customWidth="1"/>
+    <col min="6" max="8" width="33.33203125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="55.109375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="29.88671875" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>270</v>
       </c>
@@ -6012,7 +7045,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -6029,7 +7062,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -6040,7 +7073,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -6051,7 +7084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -6065,7 +7098,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -6076,7 +7109,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -6090,7 +7123,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -6101,7 +7134,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -6109,7 +7142,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -6123,7 +7156,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -6134,7 +7167,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -6142,7 +7175,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -6153,7 +7186,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -6164,7 +7197,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -6175,7 +7208,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -6186,7 +7219,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -6197,7 +7230,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -6208,7 +7241,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -6219,7 +7252,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -6233,7 +7266,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -6244,7 +7277,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -6255,7 +7288,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -6266,7 +7299,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -6277,7 +7310,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -6288,7 +7321,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -6299,7 +7332,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -6310,7 +7343,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -6321,7 +7354,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -6329,7 +7362,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -6337,7 +7370,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -6345,7 +7378,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -6356,7 +7389,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -6370,7 +7403,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -6378,7 +7411,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -6386,7 +7419,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -6397,7 +7430,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -6411,7 +7444,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -6425,7 +7458,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -6436,7 +7469,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -6447,7 +7480,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -6455,7 +7488,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -6470,7 +7503,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -6484,7 +7517,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -6495,7 +7528,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -6506,7 +7539,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -6517,7 +7550,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -6528,7 +7561,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -6542,7 +7575,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -6556,7 +7589,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -6573,7 +7606,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -6584,7 +7617,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>51</v>
       </c>
@@ -6595,7 +7628,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>52</v>
       </c>
@@ -6609,7 +7642,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>53</v>
       </c>
@@ -6620,7 +7653,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>54</v>
       </c>
@@ -6634,7 +7667,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>55</v>
       </c>
@@ -6648,7 +7681,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>56</v>
       </c>
@@ -6659,7 +7692,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>57</v>
       </c>
@@ -6667,7 +7700,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>58</v>
       </c>
@@ -6678,7 +7711,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>59</v>
       </c>
@@ -6692,7 +7725,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>60</v>
       </c>
@@ -6703,7 +7736,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>61</v>
       </c>
@@ -6714,7 +7747,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>62</v>
       </c>
@@ -6725,7 +7758,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>63</v>
       </c>
@@ -6736,7 +7769,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>64</v>
       </c>
@@ -6747,7 +7780,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>65</v>
       </c>
@@ -6758,7 +7791,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>66</v>
       </c>
@@ -6769,7 +7802,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>67</v>
       </c>
@@ -6780,7 +7813,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>68</v>
       </c>
@@ -6794,7 +7827,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>69</v>
       </c>
@@ -6808,7 +7841,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>70</v>
       </c>
@@ -6816,7 +7849,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>71</v>
       </c>
@@ -6830,7 +7863,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>72</v>
       </c>
@@ -6844,7 +7877,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>73</v>
       </c>
@@ -6855,7 +7888,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>74</v>
       </c>
@@ -6866,7 +7899,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>75</v>
       </c>
@@ -6877,7 +7910,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>76</v>
       </c>
@@ -6891,7 +7924,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>77</v>
       </c>
@@ -6902,7 +7935,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>78</v>
       </c>
@@ -6913,7 +7946,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>79</v>
       </c>
@@ -6924,7 +7957,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>80</v>
       </c>
@@ -6938,7 +7971,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>81</v>
       </c>
@@ -6949,7 +7982,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>82</v>
       </c>
@@ -6957,7 +7990,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>83</v>
       </c>
@@ -6968,7 +8001,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>84</v>
       </c>
@@ -6982,7 +8015,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>85</v>
       </c>
@@ -6990,7 +8023,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>86</v>
       </c>
@@ -7001,7 +8034,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>87</v>
       </c>
@@ -7012,7 +8045,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>88</v>
       </c>
@@ -7023,7 +8056,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>89</v>
       </c>
@@ -7031,7 +8064,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>90</v>
       </c>
@@ -7039,7 +8072,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>91</v>
       </c>
@@ -7047,7 +8080,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>92</v>
       </c>
@@ -7055,7 +8088,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>93</v>
       </c>
@@ -7066,7 +8099,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>94</v>
       </c>
@@ -7077,7 +8110,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>95</v>
       </c>
@@ -7091,7 +8124,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>96</v>
       </c>
@@ -7102,7 +8135,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>97</v>
       </c>
@@ -7116,7 +8149,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>98</v>
       </c>
@@ -7130,7 +8163,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="14">
         <v>7.8</v>
       </c>
@@ -7147,7 +8180,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>99</v>
       </c>
@@ -7158,7 +8191,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>100</v>
       </c>
@@ -7166,7 +8199,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>101</v>
       </c>
@@ -7177,7 +8210,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>102</v>
       </c>
@@ -7188,7 +8221,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>103</v>
       </c>
@@ -7199,7 +8232,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>104</v>
       </c>
@@ -7210,7 +8243,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>105</v>
       </c>
@@ -7221,7 +8254,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>106</v>
       </c>
@@ -7232,7 +8265,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>107</v>
       </c>
@@ -7243,7 +8276,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>108</v>
       </c>
@@ -7254,7 +8287,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>109</v>
       </c>
@@ -7265,7 +8298,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>110</v>
       </c>
@@ -7276,7 +8309,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>111</v>
       </c>
@@ -7290,7 +8323,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>112</v>
       </c>
@@ -7301,7 +8334,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>113</v>
       </c>
@@ -7315,7 +8348,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>114</v>
       </c>
@@ -7326,7 +8359,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>115</v>
       </c>
@@ -7337,7 +8370,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>116</v>
       </c>
@@ -7345,7 +8378,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>117</v>
       </c>
@@ -7356,7 +8389,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>118</v>
       </c>
@@ -7364,7 +8397,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>119</v>
       </c>
@@ -7375,7 +8408,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>120</v>
       </c>
@@ -7392,7 +8425,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>121</v>
       </c>
@@ -7403,7 +8436,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>122</v>
       </c>
@@ -7414,7 +8447,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>123</v>
       </c>
@@ -7425,7 +8458,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>124</v>
       </c>
@@ -7436,7 +8469,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>125</v>
       </c>
@@ -7447,7 +8480,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>126</v>
       </c>
@@ -7458,7 +8491,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>127</v>
       </c>
@@ -7469,7 +8502,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>128</v>
       </c>
@@ -7480,7 +8513,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>129</v>
       </c>
@@ -7491,7 +8524,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>130</v>
       </c>
@@ -7502,7 +8535,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>131</v>
       </c>
@@ -7510,7 +8543,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>132</v>
       </c>
@@ -7518,7 +8551,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>133</v>
       </c>
@@ -7529,7 +8562,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>134</v>
       </c>
@@ -7537,7 +8570,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>135</v>
       </c>
@@ -7545,7 +8578,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>136</v>
       </c>
@@ -7556,7 +8589,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>137</v>
       </c>
@@ -7567,7 +8600,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>138</v>
       </c>
@@ -7578,7 +8611,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>139</v>
       </c>
@@ -7589,7 +8622,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>140</v>
       </c>
@@ -7600,7 +8633,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>141</v>
       </c>
@@ -7611,7 +8644,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>142</v>
       </c>
@@ -7622,7 +8655,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>143</v>
       </c>
@@ -7633,7 +8666,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>144</v>
       </c>
@@ -7644,7 +8677,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>145</v>
       </c>
@@ -7655,7 +8688,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>333</v>
       </c>
@@ -7672,7 +8705,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>146</v>
       </c>
@@ -7689,7 +8722,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>147</v>
       </c>
@@ -7700,7 +8733,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D154" s="4" t="s">
         <v>338</v>
       </c>
@@ -7708,7 +8741,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B155" s="9">
         <v>7.12</v>
       </c>
@@ -7722,7 +8755,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>148</v>
       </c>
@@ -7736,7 +8769,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>149</v>
       </c>
@@ -7747,7 +8780,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>150</v>
       </c>
@@ -7758,7 +8791,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>151</v>
       </c>
@@ -7769,7 +8802,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>152</v>
       </c>
@@ -7780,7 +8813,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>153</v>
       </c>
@@ -7791,7 +8824,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>154</v>
       </c>
@@ -7802,7 +8835,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>155</v>
       </c>
@@ -7816,7 +8849,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>156</v>
       </c>
@@ -7827,7 +8860,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>157</v>
       </c>
@@ -7838,7 +8871,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>158</v>
       </c>
@@ -7849,7 +8882,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>159</v>
       </c>
@@ -7860,7 +8893,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>160</v>
       </c>
@@ -7871,7 +8904,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>161</v>
       </c>
@@ -7882,7 +8915,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>162</v>
       </c>
@@ -7893,7 +8926,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>163</v>
       </c>
@@ -7907,7 +8940,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>164</v>
       </c>
@@ -7915,7 +8948,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>165</v>
       </c>
@@ -7923,7 +8956,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>166</v>
       </c>
@@ -7934,7 +8967,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>167</v>
       </c>
@@ -7942,7 +8975,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>168</v>
       </c>
@@ -7953,7 +8986,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>169</v>
       </c>
@@ -7964,7 +8997,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>170</v>
       </c>
@@ -7972,7 +9005,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>171</v>
       </c>
@@ -7983,7 +9016,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>172</v>
       </c>
@@ -7991,7 +9024,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>173</v>
       </c>
@@ -8002,7 +9035,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>174</v>
       </c>
@@ -8013,7 +9046,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>175</v>
       </c>
@@ -8024,7 +9057,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>176</v>
       </c>
@@ -8032,7 +9065,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>177</v>
       </c>
@@ -8040,7 +9073,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>178</v>
       </c>
@@ -8048,7 +9081,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>179</v>
       </c>
@@ -8059,7 +9092,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>180</v>
       </c>
@@ -8070,7 +9103,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>181</v>
       </c>
@@ -8081,7 +9114,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>182</v>
       </c>
@@ -8089,7 +9122,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>183</v>
       </c>
@@ -8097,7 +9130,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>184</v>
       </c>
@@ -8108,7 +9141,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>185</v>
       </c>
@@ -8116,7 +9149,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>186</v>
       </c>
@@ -8124,7 +9157,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>187</v>
       </c>
@@ -8135,7 +9168,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>188</v>
       </c>
@@ -8149,7 +9182,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>189</v>
       </c>
@@ -8160,7 +9193,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>190</v>
       </c>
@@ -8177,7 +9210,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>191</v>
       </c>
@@ -8194,7 +9227,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
         <v>333</v>
       </c>
@@ -8202,7 +9235,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>192</v>
       </c>
@@ -8216,7 +9249,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>193</v>
       </c>
@@ -8227,7 +9260,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>194</v>
       </c>
@@ -8244,7 +9277,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>195</v>
       </c>
@@ -8255,7 +9288,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>196</v>
       </c>
@@ -8266,7 +9299,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>333</v>
       </c>
@@ -8277,11 +9310,10 @@
         <v>429</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B207" s="20"/>
       <c r="D207" s="4" t="s">
         <v>428</v>
       </c>
@@ -8292,7 +9324,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B208" s="12">
         <v>7.14</v>
       </c>
@@ -8303,7 +9335,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>198</v>
       </c>
@@ -8317,7 +9349,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>199</v>
       </c>
@@ -8325,7 +9357,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>200</v>
       </c>
@@ -8336,7 +9368,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>201</v>
       </c>
@@ -8347,7 +9379,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>202</v>
       </c>
@@ -8358,7 +9390,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>203</v>
       </c>
@@ -8366,7 +9398,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>204</v>
       </c>
@@ -8380,7 +9412,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>205</v>
       </c>
@@ -8391,7 +9423,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>206</v>
       </c>
@@ -8402,7 +9434,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>207</v>
       </c>
@@ -8413,7 +9445,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>208</v>
       </c>
@@ -8424,7 +9456,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>209</v>
       </c>
@@ -8435,7 +9467,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>210</v>
       </c>
@@ -8446,7 +9478,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>211</v>
       </c>
@@ -8460,7 +9492,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>212</v>
       </c>
@@ -8474,7 +9506,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>213</v>
       </c>
@@ -8485,7 +9517,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>333</v>
       </c>
@@ -8499,7 +9531,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>214</v>
       </c>
@@ -8513,7 +9545,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>215</v>
       </c>
@@ -8521,7 +9553,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>216</v>
       </c>
@@ -8529,7 +9561,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>217</v>
       </c>
@@ -8540,7 +9572,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
         <v>218</v>
       </c>
@@ -8548,7 +9580,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>219</v>
       </c>
@@ -8559,7 +9591,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>220</v>
       </c>
@@ -8570,7 +9602,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>221</v>
       </c>
@@ -8584,7 +9616,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>222</v>
       </c>
@@ -8598,7 +9630,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>223</v>
       </c>
@@ -8609,7 +9641,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>224</v>
       </c>
@@ -8620,7 +9652,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>225</v>
       </c>
@@ -8639,53 +9671,46 @@
       <c r="H237" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="I237" s="20" t="s">
+      <c r="I237" s="4" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>226</v>
       </c>
-      <c r="B238" s="20"/>
       <c r="F238" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="I238" s="20" t="s">
+      <c r="I238" s="4" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>227</v>
       </c>
-      <c r="B239" s="20"/>
       <c r="D239" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="I239" s="20"/>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>228</v>
       </c>
-      <c r="B240" s="20"/>
       <c r="D240" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="I240" s="20"/>
-    </row>
-    <row r="241" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>229</v>
       </c>
-      <c r="B241" s="20"/>
       <c r="F241" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="I241" s="20"/>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>230</v>
       </c>
@@ -8693,7 +9718,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>231</v>
       </c>
@@ -8701,7 +9726,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>232</v>
       </c>
@@ -8724,11 +9749,10 @@
         <v>488</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>233</v>
       </c>
-      <c r="B245" s="20"/>
       <c r="F245" s="4" t="s">
         <v>490</v>
       </c>
@@ -8736,11 +9760,10 @@
         <v>491</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>234</v>
       </c>
-      <c r="B246" s="20"/>
       <c r="D246" s="4" t="s">
         <v>493</v>
       </c>
@@ -8751,11 +9774,10 @@
         <v>494</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>235</v>
       </c>
-      <c r="B247" s="20"/>
       <c r="D247" s="13" t="s">
         <v>547</v>
       </c>
@@ -8766,11 +9788,10 @@
         <v>375</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>236</v>
       </c>
-      <c r="B248" s="20"/>
       <c r="H248" s="4" t="s">
         <v>347</v>
       </c>
@@ -8778,20 +9799,18 @@
         <v>496</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>237</v>
       </c>
-      <c r="B249" s="20"/>
       <c r="H249" s="4" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>238</v>
       </c>
-      <c r="B250" s="20"/>
       <c r="F250" s="4" t="s">
         <v>497</v>
       </c>
@@ -8799,11 +9818,10 @@
         <v>498</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>239</v>
       </c>
-      <c r="B251" s="20"/>
       <c r="F251" s="4" t="s">
         <v>499</v>
       </c>
@@ -8811,11 +9829,10 @@
         <v>500</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>240</v>
       </c>
-      <c r="B252" s="20"/>
       <c r="G252" s="4" t="s">
         <v>503</v>
       </c>
@@ -8823,11 +9840,10 @@
         <v>502</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>241</v>
       </c>
-      <c r="B253" s="20"/>
       <c r="F253" s="4" t="s">
         <v>501</v>
       </c>
@@ -8835,26 +9851,23 @@
         <v>504</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>242</v>
       </c>
-      <c r="B254" s="20"/>
       <c r="F254" s="4" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B255" s="20"/>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F255" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>244</v>
       </c>
-      <c r="B256" s="20"/>
       <c r="G256" s="4" t="s">
         <v>507</v>
       </c>
@@ -8862,11 +9875,10 @@
         <v>508</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>245</v>
       </c>
-      <c r="B257" s="20"/>
       <c r="F257" s="4" t="s">
         <v>509</v>
       </c>
@@ -8874,11 +9886,10 @@
         <v>510</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>246</v>
       </c>
-      <c r="B258" s="20"/>
       <c r="F258" s="4" t="s">
         <v>512</v>
       </c>
@@ -8886,11 +9897,10 @@
         <v>511</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>247</v>
       </c>
-      <c r="B259" s="20"/>
       <c r="F259" s="4" t="s">
         <v>513</v>
       </c>
@@ -8898,11 +9908,10 @@
         <v>516</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>248</v>
       </c>
-      <c r="B260" s="20"/>
       <c r="G260" s="5" t="s">
         <v>514</v>
       </c>
@@ -8910,11 +9919,10 @@
         <v>515</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>249</v>
       </c>
-      <c r="B261" s="20"/>
       <c r="G261" s="4" t="s">
         <v>517</v>
       </c>
@@ -8925,11 +9933,10 @@
         <v>520</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>250</v>
       </c>
-      <c r="B262" s="20"/>
       <c r="F262" s="4" t="s">
         <v>521</v>
       </c>
@@ -8937,11 +9944,10 @@
         <v>522</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>251</v>
       </c>
-      <c r="B263" s="20"/>
       <c r="F263" s="4" t="s">
         <v>523</v>
       </c>
@@ -8949,11 +9955,10 @@
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>252</v>
       </c>
-      <c r="B264" s="20"/>
       <c r="F264" s="4" t="s">
         <v>526</v>
       </c>
@@ -8967,11 +9972,10 @@
         <v>529</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>253</v>
       </c>
-      <c r="B265" s="20"/>
       <c r="F265" s="4" t="s">
         <v>531</v>
       </c>
@@ -8985,11 +9989,10 @@
         <v>533</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>254</v>
       </c>
-      <c r="B266" s="20"/>
       <c r="F266" s="4" t="s">
         <v>535</v>
       </c>
@@ -8997,11 +10000,10 @@
         <v>534</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>255</v>
       </c>
-      <c r="B267" s="20"/>
       <c r="F267" s="4" t="s">
         <v>536</v>
       </c>
@@ -9012,26 +10014,20 @@
         <v>524</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B268" s="20"/>
-    </row>
-    <row r="269" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>257</v>
       </c>
-      <c r="B269" s="20"/>
       <c r="F269" s="4" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B270" s="20"/>
+    <row r="270" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="I270" s="4" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B271" s="20"/>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H271" s="13" t="s">
         <v>545</v>
       </c>
@@ -9039,127 +10035,953 @@
         <v>541</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>258</v>
       </c>
-      <c r="B272" s="20"/>
       <c r="F272" s="4" t="s">
         <v>544</v>
       </c>
       <c r="G272" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="H272" s="20" t="s">
+      <c r="H272" s="4" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B273" s="20"/>
-      <c r="H273" s="20"/>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I273" s="4" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
         <v>259</v>
       </c>
-      <c r="B274" s="20"/>
       <c r="D274" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="H274" s="20"/>
       <c r="I274" s="4" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
         <v>260</v>
       </c>
-      <c r="B275" s="20"/>
       <c r="D275" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="H275" s="20"/>
       <c r="I275" s="4" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>261</v>
       </c>
-      <c r="B276" s="20"/>
       <c r="D276" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="H276" s="20" t="s">
+      <c r="H276" s="4" t="s">
         <v>347</v>
       </c>
       <c r="I276" s="4" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>262</v>
       </c>
-      <c r="B277" s="20"/>
       <c r="D277" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="H277" s="20"/>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>263</v>
       </c>
-      <c r="B278" s="20"/>
       <c r="D278" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="H278" s="20"/>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B279" s="20"/>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D279" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="H279" s="20"/>
-    </row>
-    <row r="280" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B280" s="20"/>
+    </row>
+    <row r="280" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A280" s="4">
+        <v>264</v>
+      </c>
       <c r="D280" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="E280" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="I280" s="4" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A281" s="4">
+        <v>265</v>
+      </c>
+      <c r="D281" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="I281" s="4" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A282" s="4">
+        <v>266</v>
+      </c>
+      <c r="H282" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="I282" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A283" s="4">
+        <v>267</v>
+      </c>
+      <c r="H283" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="I283" s="4" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A284" s="4">
+        <v>268</v>
+      </c>
+      <c r="D284" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="I284" s="4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A285" s="4">
+        <v>269</v>
+      </c>
+      <c r="D285" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="I285" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A286" s="4">
+        <v>270</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I286" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D287" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="I287" s="4" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A288" s="4">
+        <v>271</v>
+      </c>
+      <c r="D288" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="I288" s="4" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A289" s="4">
+        <v>272</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="I289" s="4" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A290" s="4">
+        <v>273</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="E290" s="12" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A291" s="4">
+        <v>274</v>
+      </c>
+      <c r="D291" s="4" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A292" s="4">
+        <v>275</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="I292" s="4" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A293" s="4">
+        <v>276</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A294" s="4">
+        <v>277</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="H294" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="I294" s="4" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A295" s="4">
+        <v>278</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="I295" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A296" s="4">
+        <v>279</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="I296" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A297" s="4">
+        <v>280</v>
+      </c>
+      <c r="G297" s="4" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A298" s="4">
+        <v>281</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="I298" s="4" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A299" s="4">
+        <v>282</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="I299" s="4" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A300" s="4">
+        <v>283</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="I300" s="4" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A301" s="4">
+        <v>284</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="I301" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A302" s="4">
+        <v>285</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="H302" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="I302" s="4" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A303" s="4">
+        <v>286</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="I303" s="4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A304" s="4">
+        <v>287</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="H304" s="4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A305" s="4">
+        <v>288</v>
+      </c>
+      <c r="F305" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="I305" s="4" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A306" s="4">
+        <v>289</v>
+      </c>
+      <c r="F306" s="4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A307" s="4">
+        <v>290</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A308" s="4">
+        <v>291</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="H308" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="I308" s="4" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A309" s="4">
+        <v>292</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I309" s="4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A310" s="4">
+        <v>293</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A311" s="4">
+        <v>294</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A312" s="4">
+        <v>295</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="I312" s="4" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A313" s="4">
+        <v>296</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A314" s="4">
+        <v>297</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="I314" s="4" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A315" s="4">
+        <v>298</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="G315" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="I315" s="4" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A316" s="4">
+        <v>299</v>
+      </c>
+      <c r="H316" s="4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A317" s="4">
+        <v>300</v>
+      </c>
+      <c r="G317" s="4" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A318" s="4">
+        <v>301</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="G318" s="4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A319" s="4">
+        <v>302</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A320" s="4">
+        <v>303</v>
+      </c>
+      <c r="G320" s="4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A321" s="4">
+        <v>304</v>
+      </c>
+      <c r="H321" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A322" s="4">
+        <v>305</v>
+      </c>
+      <c r="G322" s="4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A323" s="4">
+        <v>306</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A324" s="4">
+        <v>307</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A325" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A326" s="4">
+        <v>308</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A327" s="4">
+        <v>309</v>
+      </c>
+      <c r="H327" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="I327" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A328" s="4">
+        <v>310</v>
+      </c>
+      <c r="H328" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="I328" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A329" s="4">
+        <v>311</v>
+      </c>
+      <c r="G329" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="H329" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="I329" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A330" s="4">
+        <v>312</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="I330" s="4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A331" s="12">
+        <v>313</v>
+      </c>
+      <c r="H331" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="I331" s="12" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A332" s="20">
+        <v>314</v>
+      </c>
+      <c r="D332" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="I332" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A333" s="20">
+        <v>315</v>
+      </c>
+      <c r="D333" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="H333" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="I333" s="4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A334" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="I334" s="4" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A335" s="20">
+        <v>316</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A336" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="F336" s="4" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A337" s="20">
+        <v>318</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="I337" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A338" s="20">
+        <v>319</v>
+      </c>
+      <c r="D338" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="I338" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A339" s="20">
+        <v>320</v>
+      </c>
+      <c r="D339" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="G339" s="4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A340" s="20">
+        <v>321</v>
+      </c>
+      <c r="G340" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="I340" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A341" s="4">
+        <v>322</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="I341" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F342" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="I342" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A343" s="4">
+        <v>324</v>
+      </c>
+      <c r="F343" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="I343" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A344" s="4">
+        <v>325</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A345" s="4">
+        <v>326</v>
+      </c>
+      <c r="F345" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A346" s="4">
+        <v>327</v>
+      </c>
+      <c r="F346" s="4" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A347" s="4">
+        <v>328</v>
+      </c>
+      <c r="F347" s="4" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A348" s="4">
+        <v>329</v>
+      </c>
+      <c r="F348" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="G348" s="4" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A349" s="4">
+        <v>330</v>
+      </c>
+      <c r="F349" s="4" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A350" s="4">
+        <v>331</v>
+      </c>
+      <c r="F350" s="4" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A351" s="4">
+        <v>332</v>
+      </c>
+      <c r="F351" s="4" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A352" s="4">
+        <v>333</v>
+      </c>
+      <c r="G352" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="I352" s="4" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A353" s="4">
+        <v>334</v>
+      </c>
+      <c r="H353" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="I353" s="12" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A354" s="4">
+        <v>335</v>
+      </c>
+      <c r="F354" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="I354" s="12"/>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A355" s="4">
+        <v>336</v>
+      </c>
+      <c r="F355" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="I355" s="20"/>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A356" s="4">
+        <v>337</v>
+      </c>
+      <c r="H356" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="I356" s="20"/>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A357" s="4">
+        <v>338</v>
+      </c>
+      <c r="F357" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="I357" s="20"/>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A358" s="4">
+        <v>339</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="H358" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="I358" s="20" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I359" s="20"/>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A360" s="4">
+        <v>340</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="H360" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="I360" s="12" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F361" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="I361" s="12" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G363" s="4" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="D364" s="4" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B281" s="20"/>
-      <c r="D281" s="4" t="s">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D365" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="H281" s="4" t="s">
+      <c r="H365" s="4" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B282" s="20"/>
-      <c r="H282" s="4" t="s">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H366" s="4" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D284" s="4" t="s">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D368" s="4" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="D286" s="4" t="s">
+    <row r="370" spans="4:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D370" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="I286" s="4" t="s">
+      <c r="I370" s="4" t="s">
         <v>461</v>
       </c>
     </row>
@@ -9172,9 +10994,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57E4F1F-C950-4A27-AF75-D7439B97B581}">
   <dimension ref="A2:Q45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>1</v>
       </c>
@@ -9194,7 +11016,7 @@
         <v>0.38654923450307577</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>1.57</v>
       </c>
@@ -9210,7 +11032,7 @@
         <v>411.95</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>1.62</v>
       </c>
@@ -9226,7 +11048,7 @@
         <v>424.73</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1.6559999999999999</v>
       </c>
@@ -9242,7 +11064,7 @@
         <v>433.62</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="10">
         <v>1.7969999999999999</v>
       </c>
@@ -9258,7 +11080,7 @@
         <v>465.24</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>1.84</v>
       </c>
@@ -9274,7 +11096,7 @@
         <v>474.38</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>3</v>
       </c>
@@ -9301,7 +11123,7 @@
         <v>599.08872447978786</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>5</v>
       </c>
@@ -9321,7 +11143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>1.7820607373170305</v>
       </c>
@@ -9338,7 +11160,7 @@
         <v>456.00000740102411</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>1.6557005420069286</v>
       </c>
@@ -9355,12 +11177,12 @@
         <v>456.03979015218101</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>200</v>
       </c>
@@ -9371,7 +11193,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0</v>
       </c>
@@ -9390,7 +11212,7 @@
         <v>6.8841283483509805</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2</v>
       </c>
@@ -9409,7 +11231,7 @@
         <v>6.883196157481434</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>4</v>
       </c>
@@ -9428,7 +11250,7 @@
         <v>6.8840771516275598</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>8</v>
       </c>
@@ -9447,7 +11269,7 @@
         <v>6.8787589185405453</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>16</v>
       </c>
@@ -9466,7 +11288,7 @@
         <v>6.8377082806701024</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>32</v>
       </c>
@@ -9485,7 +11307,7 @@
         <v>6.5374739002084548</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>56</v>
       </c>
@@ -9504,7 +11326,7 @@
         <v>5.512460535664947</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>72</v>
       </c>
@@ -9523,7 +11345,7 @@
         <v>4.7502224576872303</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>128</v>
       </c>
@@ -9542,7 +11364,7 @@
         <v>1.4213718877325867</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>198</v>
       </c>
@@ -9550,7 +11372,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.9</v>
       </c>
@@ -9565,7 +11387,7 @@
         <v>89.295627373824047</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.7</v>
       </c>
@@ -9576,7 +11398,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.64700000000000002</v>
       </c>
@@ -9587,7 +11409,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.63</v>
       </c>
@@ -9598,7 +11420,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.62</v>
       </c>
@@ -9606,7 +11428,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <v>0.61499999999999999</v>
       </c>
@@ -9614,7 +11436,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.42</v>
       </c>
@@ -9622,7 +11444,7 @@
         <v>212.19</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.63935225868978396</v>
       </c>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF54DBE-6BF7-4250-A0BD-A9531A875905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D1267E-1BBA-4DB3-B27F-0EA1460A8A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="18672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0D" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Optical" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -88,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="714">
   <si>
     <t>A</t>
   </si>
@@ -2224,6 +2223,57 @@
   </si>
   <si>
     <t>diameter instead of length on h, removed</t>
+  </si>
+  <si>
+    <t>Cps  x2 + ks x2</t>
+  </si>
+  <si>
+    <t>7.16b</t>
+  </si>
+  <si>
+    <t>very good - July conference</t>
+  </si>
+  <si>
+    <t>revert to M97 no scaling</t>
+  </si>
+  <si>
+    <t>M_emis=0.8</t>
+  </si>
+  <si>
+    <t>all three E#</t>
+  </si>
+  <si>
+    <t>removed ThermalContact</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.solener.2017.04.002</t>
+  </si>
+  <si>
+    <t>added Rosseland approximation for k_z anisotropic (k_{eff, Z} = k_{SiC}(T) + \frac{16 \cdot \sigma \cdot T^3 \cdot d}{3} ; just R not hydraulic)</t>
+  </si>
+  <si>
+    <t>all I_factors to 1.0</t>
+  </si>
+  <si>
+    <t>activate surface-to-surface radiation</t>
+  </si>
+  <si>
+    <t>boundary layers 2-&gt;6, adj fact 5-&gt;1</t>
+  </si>
+  <si>
+    <t>changed to SS flow</t>
+  </si>
+  <si>
+    <t>ins_cp 1360 -&gt; 2360</t>
+  </si>
+  <si>
+    <t>Rosseland d--&gt; length</t>
+  </si>
+  <si>
+    <t>reduced flow to 80%</t>
+  </si>
+  <si>
+    <t>reduced irradiance to 90%</t>
   </si>
 </sst>
 </file>
@@ -2274,10 +2324,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2339,10 +2391,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2393,12 +2446,16 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5192,15 +5249,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>605790</xdr:colOff>
-      <xdr:row>361</xdr:row>
-      <xdr:rowOff>1905</xdr:rowOff>
+      <xdr:colOff>320040</xdr:colOff>
+      <xdr:row>367</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>361</xdr:row>
-      <xdr:rowOff>1905</xdr:rowOff>
+      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:row>367</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5215,8 +5272,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="605790" y="89978865"/>
-          <a:ext cx="14333220" cy="0"/>
+          <a:off x="320040" y="106119930"/>
+          <a:ext cx="13948410" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5713,12 +5770,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:P68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="16" max="16" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="46.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5765,7 +5822,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5812,7 +5869,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5835,7 +5892,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5861,7 +5918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5881,7 +5938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5904,7 +5961,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5924,7 +5981,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5944,7 +6001,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5967,7 +6024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -5990,7 +6047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -6013,7 +6070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -6024,7 +6081,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -6038,7 +6095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -6064,7 +6121,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -6075,7 +6132,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -6095,7 +6152,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -6103,7 +6160,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -6117,7 +6174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -6125,7 +6182,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -6142,7 +6199,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -6156,7 +6213,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -6179,7 +6236,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -6202,7 +6259,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -6225,7 +6282,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -6239,7 +6296,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -6259,7 +6316,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -6276,7 +6333,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -6290,7 +6347,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -6310,7 +6367,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -6330,7 +6387,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -6341,7 +6398,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -6361,7 +6418,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -6384,7 +6441,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -6404,7 +6461,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -6418,7 +6475,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -6429,15 +6486,15 @@
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="N38">
         <v>0</v>
       </c>
-      <c r="P38" s="21" t="s">
+      <c r="P38" s="20" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>35</v>
       </c>
@@ -6466,7 +6523,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>36</v>
       </c>
@@ -6489,7 +6546,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>37</v>
       </c>
@@ -6503,7 +6560,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>38</v>
       </c>
@@ -6529,7 +6586,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>39</v>
       </c>
@@ -6555,7 +6612,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>40</v>
       </c>
@@ -6578,7 +6635,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>41</v>
       </c>
@@ -6598,7 +6655,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>42</v>
       </c>
@@ -6618,7 +6675,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>43</v>
       </c>
@@ -6638,7 +6695,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>-0.59913658322029595</v>
       </c>
@@ -6655,7 +6712,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>-3.0218416280894E-2</v>
       </c>
@@ -6672,7 +6729,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>2.32366143478863</v>
       </c>
@@ -6692,7 +6749,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>-0.11531413827813</v>
       </c>
@@ -6712,7 +6769,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>-5.9825795140801101E-2</v>
       </c>
@@ -6729,7 +6786,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>0.163215104178386</v>
       </c>
@@ -6746,7 +6803,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>0.16620523432742201</v>
       </c>
@@ -6763,7 +6820,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>0.113337590003834</v>
       </c>
@@ -6780,7 +6837,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>0.115547627813837</v>
       </c>
@@ -6797,7 +6854,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>-3.3149389346669902E-2</v>
       </c>
@@ -6814,7 +6871,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="E58">
         <v>1</v>
       </c>
@@ -6822,7 +6879,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>0.250054010925023</v>
       </c>
@@ -6839,7 +6896,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>-1.44059076725918</v>
       </c>
@@ -6856,7 +6913,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>-1.21144890336943</v>
       </c>
@@ -6873,7 +6930,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>-1.2070813277479999</v>
       </c>
@@ -6893,7 +6950,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>-1.0012021396300801</v>
       </c>
@@ -6907,7 +6964,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>-4.4248727373665302</v>
       </c>
@@ -6924,7 +6981,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>-1.0608132419307801</v>
       </c>
@@ -6944,7 +7001,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>-1.1261289140861099</v>
       </c>
@@ -6964,7 +7021,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>-1.2035253749880399</v>
       </c>
@@ -6978,7 +7035,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>-1.44395477402174</v>
       </c>
@@ -7003,20 +7060,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B19FA9-A01B-4042-9995-5A31C36523E9}">
-  <dimension ref="A2:J370"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:J384"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.109375" style="4"/>
-    <col min="3" max="3" width="9.6640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="33.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="37.44140625" style="4" customWidth="1"/>
-    <col min="6" max="8" width="33.33203125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="55.109375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="29.88671875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="4"/>
+    <col min="1" max="2" width="9.140625" style="4"/>
+    <col min="3" max="3" width="9.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="37.42578125" style="4" customWidth="1"/>
+    <col min="6" max="8" width="33.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="55.140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="29.85546875" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>270</v>
       </c>
@@ -7045,7 +7102,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -7062,7 +7119,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -7073,7 +7130,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -7084,7 +7141,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -7098,7 +7155,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -7109,7 +7166,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -7123,7 +7180,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -7134,7 +7191,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -7142,7 +7199,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -7156,7 +7213,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -7167,7 +7224,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -7175,7 +7232,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -7186,7 +7243,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -7197,7 +7254,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -7208,7 +7265,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -7219,7 +7276,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -7230,7 +7287,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -7241,7 +7298,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -7252,7 +7309,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -7266,7 +7323,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -7277,7 +7334,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -7288,7 +7345,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -7299,7 +7356,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -7310,7 +7367,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -7321,7 +7378,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -7332,7 +7389,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -7343,7 +7400,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -7354,7 +7411,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -7362,7 +7419,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -7370,7 +7427,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -7378,7 +7435,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -7389,7 +7446,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -7403,7 +7460,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -7411,7 +7468,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -7419,7 +7476,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -7430,7 +7487,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -7444,7 +7501,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -7458,7 +7515,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -7469,7 +7526,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -7480,7 +7537,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -7488,7 +7545,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -7503,7 +7560,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -7517,7 +7574,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -7528,7 +7585,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -7539,7 +7596,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -7550,7 +7607,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -7561,7 +7618,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -7575,7 +7632,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -7589,7 +7646,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -7606,7 +7663,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -7617,7 +7674,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>51</v>
       </c>
@@ -7628,7 +7685,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>52</v>
       </c>
@@ -7642,7 +7699,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>53</v>
       </c>
@@ -7653,7 +7710,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>54</v>
       </c>
@@ -7667,7 +7724,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>55</v>
       </c>
@@ -7681,7 +7738,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>56</v>
       </c>
@@ -7692,7 +7749,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>57</v>
       </c>
@@ -7700,7 +7757,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>58</v>
       </c>
@@ -7711,7 +7768,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>59</v>
       </c>
@@ -7725,7 +7782,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>60</v>
       </c>
@@ -7736,7 +7793,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>61</v>
       </c>
@@ -7747,7 +7804,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>62</v>
       </c>
@@ -7758,7 +7815,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>63</v>
       </c>
@@ -7769,7 +7826,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>64</v>
       </c>
@@ -7780,7 +7837,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>65</v>
       </c>
@@ -7791,7 +7848,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>66</v>
       </c>
@@ -7802,7 +7859,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>67</v>
       </c>
@@ -7813,7 +7870,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>68</v>
       </c>
@@ -7827,7 +7884,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>69</v>
       </c>
@@ -7841,7 +7898,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>70</v>
       </c>
@@ -7849,7 +7906,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>71</v>
       </c>
@@ -7863,7 +7920,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>72</v>
       </c>
@@ -7877,7 +7934,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>73</v>
       </c>
@@ -7888,7 +7945,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>74</v>
       </c>
@@ -7899,7 +7956,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>75</v>
       </c>
@@ -7910,7 +7967,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>76</v>
       </c>
@@ -7924,7 +7981,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>77</v>
       </c>
@@ -7935,7 +7992,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>78</v>
       </c>
@@ -7946,7 +8003,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>79</v>
       </c>
@@ -7957,7 +8014,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>80</v>
       </c>
@@ -7971,7 +8028,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>81</v>
       </c>
@@ -7982,7 +8039,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>82</v>
       </c>
@@ -7990,7 +8047,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>83</v>
       </c>
@@ -8001,7 +8058,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>84</v>
       </c>
@@ -8015,7 +8072,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>85</v>
       </c>
@@ -8023,7 +8080,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>86</v>
       </c>
@@ -8034,7 +8091,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>87</v>
       </c>
@@ -8045,7 +8102,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>88</v>
       </c>
@@ -8056,7 +8113,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>89</v>
       </c>
@@ -8064,7 +8121,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>90</v>
       </c>
@@ -8072,7 +8129,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>91</v>
       </c>
@@ -8080,7 +8137,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>92</v>
       </c>
@@ -8088,7 +8145,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>93</v>
       </c>
@@ -8099,7 +8156,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>94</v>
       </c>
@@ -8110,7 +8167,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>95</v>
       </c>
@@ -8124,7 +8181,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>96</v>
       </c>
@@ -8135,7 +8192,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>97</v>
       </c>
@@ -8149,7 +8206,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>98</v>
       </c>
@@ -8163,7 +8220,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B101" s="14">
         <v>7.8</v>
       </c>
@@ -8180,7 +8237,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>99</v>
       </c>
@@ -8191,7 +8248,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>100</v>
       </c>
@@ -8199,7 +8256,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>101</v>
       </c>
@@ -8210,7 +8267,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>102</v>
       </c>
@@ -8221,7 +8278,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>103</v>
       </c>
@@ -8232,7 +8289,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>104</v>
       </c>
@@ -8243,7 +8300,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>105</v>
       </c>
@@ -8254,7 +8311,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>106</v>
       </c>
@@ -8265,7 +8322,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>107</v>
       </c>
@@ -8276,7 +8333,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>108</v>
       </c>
@@ -8287,7 +8344,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>109</v>
       </c>
@@ -8298,7 +8355,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>110</v>
       </c>
@@ -8309,7 +8366,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>111</v>
       </c>
@@ -8323,7 +8380,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>112</v>
       </c>
@@ -8334,7 +8391,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>113</v>
       </c>
@@ -8348,7 +8405,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>114</v>
       </c>
@@ -8359,7 +8416,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>115</v>
       </c>
@@ -8370,7 +8427,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>116</v>
       </c>
@@ -8378,7 +8435,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>117</v>
       </c>
@@ -8389,7 +8446,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>118</v>
       </c>
@@ -8397,7 +8454,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>119</v>
       </c>
@@ -8408,7 +8465,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>120</v>
       </c>
@@ -8425,7 +8482,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>121</v>
       </c>
@@ -8436,7 +8493,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>122</v>
       </c>
@@ -8447,7 +8504,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>123</v>
       </c>
@@ -8458,7 +8515,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>124</v>
       </c>
@@ -8469,7 +8526,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>125</v>
       </c>
@@ -8480,7 +8537,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>126</v>
       </c>
@@ -8491,7 +8548,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>127</v>
       </c>
@@ -8502,7 +8559,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>128</v>
       </c>
@@ -8513,7 +8570,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>129</v>
       </c>
@@ -8524,7 +8581,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>130</v>
       </c>
@@ -8535,7 +8592,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>131</v>
       </c>
@@ -8543,7 +8600,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>132</v>
       </c>
@@ -8551,7 +8608,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>133</v>
       </c>
@@ -8562,7 +8619,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>134</v>
       </c>
@@ -8570,7 +8627,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>135</v>
       </c>
@@ -8578,7 +8635,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>136</v>
       </c>
@@ -8589,7 +8646,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>137</v>
       </c>
@@ -8600,7 +8657,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>138</v>
       </c>
@@ -8611,7 +8668,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>139</v>
       </c>
@@ -8622,7 +8679,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>140</v>
       </c>
@@ -8633,7 +8690,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>141</v>
       </c>
@@ -8644,7 +8701,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>142</v>
       </c>
@@ -8655,7 +8712,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>143</v>
       </c>
@@ -8666,7 +8723,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>144</v>
       </c>
@@ -8677,7 +8734,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>145</v>
       </c>
@@ -8688,7 +8745,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>333</v>
       </c>
@@ -8705,7 +8762,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>146</v>
       </c>
@@ -8722,7 +8779,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>147</v>
       </c>
@@ -8733,7 +8790,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D154" s="4" t="s">
         <v>338</v>
       </c>
@@ -8741,7 +8798,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B155" s="9">
         <v>7.12</v>
       </c>
@@ -8755,7 +8812,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>148</v>
       </c>
@@ -8769,7 +8826,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>149</v>
       </c>
@@ -8780,7 +8837,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>150</v>
       </c>
@@ -8791,7 +8848,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>151</v>
       </c>
@@ -8802,7 +8859,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>152</v>
       </c>
@@ -8813,7 +8870,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>153</v>
       </c>
@@ -8824,7 +8881,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>154</v>
       </c>
@@ -8835,7 +8892,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>155</v>
       </c>
@@ -8849,7 +8906,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>156</v>
       </c>
@@ -8860,7 +8917,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>157</v>
       </c>
@@ -8871,7 +8928,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>158</v>
       </c>
@@ -8882,7 +8939,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>159</v>
       </c>
@@ -8893,7 +8950,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>160</v>
       </c>
@@ -8904,7 +8961,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>161</v>
       </c>
@@ -8915,7 +8972,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>162</v>
       </c>
@@ -8926,7 +8983,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>163</v>
       </c>
@@ -8940,7 +8997,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>164</v>
       </c>
@@ -8948,7 +9005,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>165</v>
       </c>
@@ -8956,7 +9013,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>166</v>
       </c>
@@ -8967,7 +9024,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>167</v>
       </c>
@@ -8975,7 +9032,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>168</v>
       </c>
@@ -8986,7 +9043,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>169</v>
       </c>
@@ -8997,7 +9054,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>170</v>
       </c>
@@ -9005,7 +9062,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>171</v>
       </c>
@@ -9016,7 +9073,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>172</v>
       </c>
@@ -9024,7 +9081,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>173</v>
       </c>
@@ -9035,7 +9092,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>174</v>
       </c>
@@ -9046,7 +9103,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>175</v>
       </c>
@@ -9057,7 +9114,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>176</v>
       </c>
@@ -9065,7 +9122,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>177</v>
       </c>
@@ -9073,7 +9130,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>178</v>
       </c>
@@ -9081,7 +9138,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>179</v>
       </c>
@@ -9092,7 +9149,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>180</v>
       </c>
@@ -9103,7 +9160,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>181</v>
       </c>
@@ -9114,7 +9171,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>182</v>
       </c>
@@ -9122,7 +9179,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>183</v>
       </c>
@@ -9130,7 +9187,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>184</v>
       </c>
@@ -9141,7 +9198,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>185</v>
       </c>
@@ -9149,7 +9206,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
         <v>186</v>
       </c>
@@ -9157,7 +9214,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>187</v>
       </c>
@@ -9168,7 +9225,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>188</v>
       </c>
@@ -9182,7 +9239,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>189</v>
       </c>
@@ -9193,7 +9250,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>190</v>
       </c>
@@ -9210,7 +9267,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>191</v>
       </c>
@@ -9227,7 +9284,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>333</v>
       </c>
@@ -9235,7 +9292,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>192</v>
       </c>
@@ -9249,7 +9306,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>193</v>
       </c>
@@ -9260,7 +9317,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>194</v>
       </c>
@@ -9277,7 +9334,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
         <v>195</v>
       </c>
@@ -9288,7 +9345,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>196</v>
       </c>
@@ -9299,7 +9356,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>333</v>
       </c>
@@ -9310,7 +9367,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>333</v>
       </c>
@@ -9324,7 +9381,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B208" s="12">
         <v>7.14</v>
       </c>
@@ -9335,7 +9392,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>198</v>
       </c>
@@ -9349,7 +9406,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
         <v>199</v>
       </c>
@@ -9357,7 +9414,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>200</v>
       </c>
@@ -9368,7 +9425,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
         <v>201</v>
       </c>
@@ -9379,7 +9436,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>202</v>
       </c>
@@ -9390,7 +9447,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
         <v>203</v>
       </c>
@@ -9398,7 +9455,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>204</v>
       </c>
@@ -9412,7 +9469,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>205</v>
       </c>
@@ -9423,7 +9480,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>206</v>
       </c>
@@ -9434,7 +9491,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>207</v>
       </c>
@@ -9445,7 +9502,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>208</v>
       </c>
@@ -9456,7 +9513,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
         <v>209</v>
       </c>
@@ -9467,7 +9524,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>210</v>
       </c>
@@ -9478,7 +9535,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
         <v>211</v>
       </c>
@@ -9492,7 +9549,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>212</v>
       </c>
@@ -9506,7 +9563,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>213</v>
       </c>
@@ -9517,7 +9574,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>333</v>
       </c>
@@ -9531,7 +9588,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>214</v>
       </c>
@@ -9545,7 +9602,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>215</v>
       </c>
@@ -9553,7 +9610,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>216</v>
       </c>
@@ -9561,7 +9618,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>217</v>
       </c>
@@ -9572,7 +9629,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
         <v>218</v>
       </c>
@@ -9580,7 +9637,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>219</v>
       </c>
@@ -9591,7 +9648,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
         <v>220</v>
       </c>
@@ -9602,7 +9659,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>221</v>
       </c>
@@ -9616,7 +9673,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>222</v>
       </c>
@@ -9630,7 +9687,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>223</v>
       </c>
@@ -9641,7 +9698,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
         <v>224</v>
       </c>
@@ -9652,7 +9709,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>225</v>
       </c>
@@ -9675,7 +9732,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>226</v>
       </c>
@@ -9686,7 +9743,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>227</v>
       </c>
@@ -9694,7 +9751,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
         <v>228</v>
       </c>
@@ -9702,7 +9759,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>229</v>
       </c>
@@ -9710,7 +9767,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
         <v>230</v>
       </c>
@@ -9718,7 +9775,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>231</v>
       </c>
@@ -9726,7 +9783,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>232</v>
       </c>
@@ -9749,7 +9806,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>233</v>
       </c>
@@ -9760,7 +9817,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>234</v>
       </c>
@@ -9774,7 +9831,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>235</v>
       </c>
@@ -9788,7 +9845,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>236</v>
       </c>
@@ -9799,7 +9856,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>237</v>
       </c>
@@ -9807,7 +9864,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>238</v>
       </c>
@@ -9818,7 +9875,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>239</v>
       </c>
@@ -9829,7 +9886,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>240</v>
       </c>
@@ -9840,7 +9897,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>241</v>
       </c>
@@ -9851,7 +9908,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
         <v>242</v>
       </c>
@@ -9859,12 +9916,12 @@
         <v>505</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F255" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>244</v>
       </c>
@@ -9875,7 +9932,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>245</v>
       </c>
@@ -9886,7 +9943,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>246</v>
       </c>
@@ -9897,7 +9954,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>247</v>
       </c>
@@ -9908,7 +9965,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>248</v>
       </c>
@@ -9919,7 +9976,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>249</v>
       </c>
@@ -9933,7 +9990,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>250</v>
       </c>
@@ -9944,7 +10001,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>251</v>
       </c>
@@ -9955,7 +10012,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
         <v>252</v>
       </c>
@@ -9972,7 +10029,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>253</v>
       </c>
@@ -9989,7 +10046,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
         <v>254</v>
       </c>
@@ -10000,7 +10057,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
         <v>255</v>
       </c>
@@ -10014,7 +10071,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
         <v>257</v>
       </c>
@@ -10022,12 +10079,12 @@
         <v>537</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="I270" s="4" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H271" s="13" t="s">
         <v>545</v>
       </c>
@@ -10035,7 +10092,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
         <v>258</v>
       </c>
@@ -10049,12 +10106,12 @@
         <v>542</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="I273" s="4" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
         <v>259</v>
       </c>
@@ -10065,7 +10122,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
         <v>260</v>
       </c>
@@ -10076,7 +10133,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
         <v>261</v>
       </c>
@@ -10090,7 +10147,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
         <v>262</v>
       </c>
@@ -10098,7 +10155,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
         <v>263</v>
       </c>
@@ -10106,12 +10163,12 @@
         <v>553</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D279" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
         <v>264</v>
       </c>
@@ -10125,7 +10182,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
         <v>265</v>
       </c>
@@ -10139,7 +10196,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
         <v>266</v>
       </c>
@@ -10150,7 +10207,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
         <v>267</v>
       </c>
@@ -10161,7 +10218,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
         <v>268</v>
       </c>
@@ -10172,7 +10229,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
         <v>269</v>
       </c>
@@ -10183,7 +10240,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
         <v>270</v>
       </c>
@@ -10194,7 +10251,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D287" s="4" t="s">
         <v>568</v>
       </c>
@@ -10202,7 +10259,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
         <v>271</v>
       </c>
@@ -10213,7 +10270,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
         <v>272</v>
       </c>
@@ -10224,7 +10281,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
         <v>273</v>
       </c>
@@ -10235,7 +10292,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
         <v>274</v>
       </c>
@@ -10243,7 +10300,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
         <v>275</v>
       </c>
@@ -10254,7 +10311,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
         <v>276</v>
       </c>
@@ -10262,7 +10319,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
         <v>277</v>
       </c>
@@ -10276,7 +10333,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
         <v>278</v>
       </c>
@@ -10287,7 +10344,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
         <v>279</v>
       </c>
@@ -10301,7 +10358,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
         <v>280</v>
       </c>
@@ -10309,7 +10366,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
         <v>281</v>
       </c>
@@ -10320,7 +10377,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
         <v>282</v>
       </c>
@@ -10331,7 +10388,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
         <v>283</v>
       </c>
@@ -10342,7 +10399,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
         <v>284</v>
       </c>
@@ -10356,7 +10413,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
         <v>285</v>
       </c>
@@ -10370,7 +10427,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
         <v>286</v>
       </c>
@@ -10381,7 +10438,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
         <v>287</v>
       </c>
@@ -10392,7 +10449,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
         <v>288</v>
       </c>
@@ -10403,7 +10460,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
         <v>289</v>
       </c>
@@ -10411,7 +10468,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
         <v>290</v>
       </c>
@@ -10422,7 +10479,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
         <v>291</v>
       </c>
@@ -10436,7 +10493,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
         <v>292</v>
       </c>
@@ -10447,7 +10504,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
         <v>293</v>
       </c>
@@ -10455,7 +10512,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
         <v>294</v>
       </c>
@@ -10463,7 +10520,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
         <v>295</v>
       </c>
@@ -10474,7 +10531,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
         <v>296</v>
       </c>
@@ -10482,7 +10539,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
         <v>297</v>
       </c>
@@ -10493,7 +10550,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
         <v>298</v>
       </c>
@@ -10507,7 +10564,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
         <v>299</v>
       </c>
@@ -10515,7 +10572,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A317" s="4">
         <v>300</v>
       </c>
@@ -10523,7 +10580,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A318" s="4">
         <v>301</v>
       </c>
@@ -10534,7 +10591,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
         <v>302</v>
       </c>
@@ -10542,7 +10599,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="4">
         <v>303</v>
       </c>
@@ -10550,7 +10607,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
         <v>304</v>
       </c>
@@ -10558,7 +10615,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
         <v>305</v>
       </c>
@@ -10566,7 +10623,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
         <v>306</v>
       </c>
@@ -10574,7 +10631,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" s="4">
         <v>307</v>
       </c>
@@ -10582,7 +10639,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
         <v>333</v>
       </c>
@@ -10590,7 +10647,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
         <v>308</v>
       </c>
@@ -10598,7 +10655,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
         <v>309</v>
       </c>
@@ -10609,7 +10666,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="4">
         <v>310</v>
       </c>
@@ -10620,7 +10677,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
         <v>311</v>
       </c>
@@ -10634,7 +10691,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
         <v>312</v>
       </c>
@@ -10645,7 +10702,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="12">
         <v>313</v>
       </c>
@@ -10656,8 +10713,8 @@
         <v>635</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A332" s="20">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="4">
         <v>314</v>
       </c>
       <c r="D332" s="4" t="s">
@@ -10667,8 +10724,8 @@
         <v>637</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A333" s="20">
+    <row r="333" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A333" s="4">
         <v>315</v>
       </c>
       <c r="D333" s="4" t="s">
@@ -10684,8 +10741,8 @@
         <v>639</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A334" s="20" t="s">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
         <v>333</v>
       </c>
       <c r="F334" s="4" t="s">
@@ -10695,24 +10752,24 @@
         <v>641</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A335" s="20">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="4">
         <v>316</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A336" s="20" t="s">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
         <v>644</v>
       </c>
       <c r="F336" s="4" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A337" s="20">
+    <row r="337" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A337" s="4">
         <v>318</v>
       </c>
       <c r="F337" s="4" t="s">
@@ -10722,8 +10779,8 @@
         <v>647</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A338" s="20">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="4">
         <v>319</v>
       </c>
       <c r="D338" s="4" t="s">
@@ -10733,8 +10790,8 @@
         <v>648</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A339" s="20">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="4">
         <v>320</v>
       </c>
       <c r="D339" s="4" t="s">
@@ -10744,8 +10801,8 @@
         <v>649</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A340" s="20">
+    <row r="340" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A340" s="4">
         <v>321</v>
       </c>
       <c r="G340" s="4" t="s">
@@ -10755,7 +10812,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
         <v>322</v>
       </c>
@@ -10766,7 +10823,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F342" s="4" t="s">
         <v>654</v>
       </c>
@@ -10774,7 +10831,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
         <v>324</v>
       </c>
@@ -10785,7 +10842,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
         <v>325</v>
       </c>
@@ -10793,7 +10850,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
         <v>326</v>
       </c>
@@ -10801,7 +10858,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
         <v>327</v>
       </c>
@@ -10809,7 +10866,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
         <v>328</v>
       </c>
@@ -10817,7 +10874,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="4">
         <v>329</v>
       </c>
@@ -10828,7 +10885,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
         <v>330</v>
       </c>
@@ -10836,7 +10893,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
         <v>331</v>
       </c>
@@ -10844,7 +10901,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
         <v>332</v>
       </c>
@@ -10852,7 +10909,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
         <v>333</v>
       </c>
@@ -10863,7 +10920,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
         <v>334</v>
       </c>
@@ -10874,7 +10931,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
         <v>335</v>
       </c>
@@ -10883,34 +10940,31 @@
       </c>
       <c r="I354" s="12"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
         <v>336</v>
       </c>
       <c r="F355" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="I355" s="20"/>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
         <v>337</v>
       </c>
       <c r="H356" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="I356" s="20"/>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
         <v>338</v>
       </c>
       <c r="F357" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="I357" s="20"/>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
         <v>339</v>
       </c>
@@ -10920,14 +10974,11 @@
       <c r="H358" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="I358" s="20" t="s">
+      <c r="I358" s="4" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I359" s="20"/>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
         <v>340</v>
       </c>
@@ -10941,62 +10992,183 @@
         <v>693</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" s="4">
+        <v>341</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>698</v>
+      </c>
       <c r="F361" s="4" t="s">
-        <v>677</v>
+        <v>697</v>
+      </c>
+      <c r="H361" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="I361" s="12" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" s="4">
+        <v>342</v>
+      </c>
+      <c r="I362" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" s="4">
+        <v>343</v>
+      </c>
+      <c r="B363" s="9">
+        <v>7.17</v>
+      </c>
+      <c r="F363" s="4" t="s">
+        <v>700</v>
+      </c>
       <c r="G363" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A364" s="4">
+        <v>344</v>
+      </c>
+      <c r="B364" s="21"/>
+      <c r="F364" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="G364" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="I364" s="22" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" s="4">
+        <v>345</v>
+      </c>
+      <c r="B365" s="21"/>
+      <c r="D365" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="E365" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="H365" s="4" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" s="4">
+        <v>346</v>
+      </c>
+      <c r="B366" s="21"/>
+      <c r="F366" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" s="4">
+        <v>347</v>
+      </c>
+      <c r="B367" s="21"/>
+      <c r="G367" s="4" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" s="4">
+        <v>348</v>
+      </c>
+      <c r="B368" s="21"/>
+      <c r="D368" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="H368" s="4" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="369" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B369" s="21"/>
+    </row>
+    <row r="370" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B370" s="21"/>
+    </row>
+    <row r="371" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B371" s="21"/>
+    </row>
+    <row r="372" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B372" s="21"/>
+      <c r="G372" s="4" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="373" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B373" s="21"/>
+    </row>
+    <row r="374" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B374" s="21"/>
+    </row>
+    <row r="375" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B375" s="21"/>
+    </row>
+    <row r="376" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B376" s="21"/>
+    </row>
+    <row r="377" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G377" s="4" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="D364" s="4" t="s">
+    <row r="378" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="D378" s="4" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D365" s="4" t="s">
+    <row r="379" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="D379" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="H365" s="4" t="s">
+      <c r="H379" s="4" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H366" s="4" t="s">
+    <row r="380" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H380" s="4" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D368" s="4" t="s">
+    <row r="382" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D382" s="4" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="370" spans="4:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D370" s="4" t="s">
+    <row r="384" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="D384" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="I370" s="4" t="s">
+      <c r="I384" s="4" t="s">
         <v>461</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I364" r:id="rId1" xr:uid="{05E58BA6-BA12-423C-9688-7F1AF41588C6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57E4F1F-C950-4A27-AF75-D7439B97B581}">
   <dimension ref="A2:Q45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>1</v>
       </c>
@@ -11016,7 +11188,7 @@
         <v>0.38654923450307577</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1.57</v>
       </c>
@@ -11032,7 +11204,7 @@
         <v>411.95</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1.62</v>
       </c>
@@ -11048,7 +11220,7 @@
         <v>424.73</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1.6559999999999999</v>
       </c>
@@ -11064,7 +11236,7 @@
         <v>433.62</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="10">
         <v>1.7969999999999999</v>
       </c>
@@ -11080,7 +11252,7 @@
         <v>465.24</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1.84</v>
       </c>
@@ -11096,7 +11268,7 @@
         <v>474.38</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>3</v>
       </c>
@@ -11123,7 +11295,7 @@
         <v>599.08872447978786</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -11143,7 +11315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1.7820607373170305</v>
       </c>
@@ -11160,7 +11332,7 @@
         <v>456.00000740102411</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1.6557005420069286</v>
       </c>
@@ -11177,12 +11349,12 @@
         <v>456.03979015218101</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>200</v>
       </c>
@@ -11193,7 +11365,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>0</v>
       </c>
@@ -11212,7 +11384,7 @@
         <v>6.8841283483509805</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2</v>
       </c>
@@ -11231,7 +11403,7 @@
         <v>6.883196157481434</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4</v>
       </c>
@@ -11250,7 +11422,7 @@
         <v>6.8840771516275598</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>8</v>
       </c>
@@ -11269,7 +11441,7 @@
         <v>6.8787589185405453</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>16</v>
       </c>
@@ -11288,7 +11460,7 @@
         <v>6.8377082806701024</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>32</v>
       </c>
@@ -11307,7 +11479,7 @@
         <v>6.5374739002084548</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>56</v>
       </c>
@@ -11326,7 +11498,7 @@
         <v>5.512460535664947</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>72</v>
       </c>
@@ -11345,7 +11517,7 @@
         <v>4.7502224576872303</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>128</v>
       </c>
@@ -11364,7 +11536,7 @@
         <v>1.4213718877325867</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>198</v>
       </c>
@@ -11372,7 +11544,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>0.9</v>
       </c>
@@ -11387,7 +11559,7 @@
         <v>89.295627373824047</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0.7</v>
       </c>
@@ -11398,7 +11570,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>0.64700000000000002</v>
       </c>
@@ -11409,7 +11581,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>0.63</v>
       </c>
@@ -11420,7 +11592,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>0.62</v>
       </c>
@@ -11428,7 +11600,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>0.61499999999999999</v>
       </c>
@@ -11436,7 +11608,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>0.42</v>
       </c>
@@ -11444,7 +11616,7 @@
         <v>212.19</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>0.63935225868978396</v>
       </c>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\tamuq-chen-secarelab-receiver\aysha\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D1267E-1BBA-4DB3-B27F-0EA1460A8A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D0A623-EE23-4B04-9243-D0BE180096B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="18672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0D" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="717">
   <si>
     <t>A</t>
   </si>
@@ -2274,6 +2274,15 @@
   </si>
   <si>
     <t>reduced irradiance to 90%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">converted model to 1.12 </t>
+  </si>
+  <si>
+    <t>and to COMSOL geometry with more thermal masses</t>
+  </si>
+  <si>
+    <t>T9 &amp; T10; removed I_factors</t>
   </si>
 </sst>
 </file>
@@ -2395,7 +2404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2447,9 +2456,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -5769,7 +5775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:P68"/>
+  <dimension ref="A2:P74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="16" max="16" width="46.85546875" bestFit="1" customWidth="1"/>
@@ -7050,6 +7056,74 @@
       </c>
       <c r="P68" t="s">
         <v>696</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B70">
+        <v>-1.2038</v>
+      </c>
+      <c r="C70">
+        <v>0.4929</v>
+      </c>
+      <c r="D70">
+        <v>-4.9325999999999999</v>
+      </c>
+      <c r="P70" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B71">
+        <v>-0.70223850678134803</v>
+      </c>
+      <c r="C71">
+        <v>0.25645673662077101</v>
+      </c>
+      <c r="D71">
+        <v>-4.9512972108205302</v>
+      </c>
+      <c r="P71" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="O72">
+        <v>1147</v>
+      </c>
+      <c r="P72" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>0.7</v>
+      </c>
+      <c r="O73">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="H74">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11035,14 +11109,13 @@
       <c r="A364" s="4">
         <v>344</v>
       </c>
-      <c r="B364" s="21"/>
       <c r="F364" s="4" t="s">
         <v>703</v>
       </c>
       <c r="G364" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="I364" s="22" t="s">
+      <c r="I364" s="21" t="s">
         <v>704</v>
       </c>
     </row>
@@ -11050,7 +11123,6 @@
       <c r="A365" s="4">
         <v>345</v>
       </c>
-      <c r="B365" s="21"/>
       <c r="D365" s="4" t="s">
         <v>709</v>
       </c>
@@ -11065,7 +11137,6 @@
       <c r="A366" s="4">
         <v>346</v>
       </c>
-      <c r="B366" s="21"/>
       <c r="F366" s="4" t="s">
         <v>710</v>
       </c>
@@ -11074,7 +11145,6 @@
       <c r="A367" s="4">
         <v>347</v>
       </c>
-      <c r="B367" s="21"/>
       <c r="G367" s="4" t="s">
         <v>711</v>
       </c>
@@ -11083,7 +11153,6 @@
       <c r="A368" s="4">
         <v>348</v>
       </c>
-      <c r="B368" s="21"/>
       <c r="D368" s="4" t="s">
         <v>712</v>
       </c>
@@ -11091,44 +11160,22 @@
         <v>713</v>
       </c>
     </row>
-    <row r="369" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B369" s="21"/>
-    </row>
-    <row r="370" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B370" s="21"/>
-    </row>
-    <row r="371" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B371" s="21"/>
-    </row>
-    <row r="372" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B372" s="21"/>
+    <row r="372" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G372" s="4" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="373" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B373" s="21"/>
-    </row>
-    <row r="374" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B374" s="21"/>
-    </row>
-    <row r="375" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B375" s="21"/>
-    </row>
-    <row r="376" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B376" s="21"/>
-    </row>
-    <row r="377" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G377" s="4" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="378" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D378" s="4" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="379" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D379" s="4" t="s">
         <v>538</v>
       </c>
@@ -11136,17 +11183,17 @@
         <v>373</v>
       </c>
     </row>
-    <row r="380" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H380" s="4" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="382" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D382" s="4" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="384" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D384" s="4" t="s">
         <v>475</v>
       </c>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D0A623-EE23-4B04-9243-D0BE180096B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C09ED1-ECE5-4F69-8C35-4BF2DDE8C751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="725">
   <si>
     <t>A</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>error</t>
-  </si>
-  <si>
-    <t>Comments</t>
   </si>
   <si>
     <t>same</t>
@@ -2283,6 +2280,33 @@
   </si>
   <si>
     <t>T9 &amp; T10; removed I_factors</t>
+  </si>
+  <si>
+    <t>low qlpm</t>
+  </si>
+  <si>
+    <t>Modification</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Solid temp scatter not bad, Gas shows flow independent behavior</t>
+  </si>
+  <si>
+    <t>I_factors too high</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>scatter plots are getting better</t>
+  </si>
+  <si>
+    <t>Cpinsulation=1360</t>
+  </si>
+  <si>
+    <t>very good scatter plots</t>
   </si>
 </sst>
 </file>
@@ -2404,7 +2428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2459,6 +2483,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5775,13 +5801,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:P74"/>
+  <dimension ref="A2:Q88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="16" max="16" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5804,31 +5831,34 @@
         <v>6</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>717</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5854,13 +5884,13 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -5872,10 +5902,10 @@
         <v>499.47699999999998</v>
       </c>
       <c r="P3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5895,10 +5925,10 @@
         <v>528.26599999999996</v>
       </c>
       <c r="P4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5921,10 +5951,10 @@
         <v>473.34</v>
       </c>
       <c r="P5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5941,10 +5971,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="P6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5964,10 +5994,10 @@
         <v>604.08600000000001</v>
       </c>
       <c r="P7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5984,10 +6014,10 @@
         <v>0.7</v>
       </c>
       <c r="P8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -6004,10 +6034,10 @@
         <v>0.63</v>
       </c>
       <c r="P9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -6027,12 +6057,12 @@
         <v>500</v>
       </c>
       <c r="P10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>17</v>
       </c>
       <c r="B11" s="3">
         <v>3.7125021077593002E-4</v>
@@ -6050,10 +6080,10 @@
         <v>480</v>
       </c>
       <c r="P11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -6067,41 +6097,41 @@
         <v>19.9997174906579</v>
       </c>
       <c r="I12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O12">
         <v>672</v>
       </c>
       <c r="P12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P13" t="s">
         <v>25</v>
       </c>
-      <c r="P13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="K14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O14">
         <v>25612</v>
       </c>
       <c r="P14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -6115,27 +6145,27 @@
         <v>20</v>
       </c>
       <c r="J15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O15">
         <v>469</v>
       </c>
       <c r="P15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="O16" t="s">
+        <v>53</v>
+      </c>
+      <c r="P16" t="s">
         <v>54</v>
-      </c>
-      <c r="P16" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -6155,7 +6185,7 @@
         <v>465</v>
       </c>
       <c r="P17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -6163,7 +6193,7 @@
         <v>15</v>
       </c>
       <c r="P18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -6177,7 +6207,7 @@
         <v>850</v>
       </c>
       <c r="P19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -6185,7 +6215,7 @@
         <v>17</v>
       </c>
       <c r="P20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -6202,7 +6232,7 @@
         <v>573</v>
       </c>
       <c r="P21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -6216,7 +6246,7 @@
         <v>607</v>
       </c>
       <c r="P22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -6239,7 +6269,7 @@
         <v>502</v>
       </c>
       <c r="P23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -6262,7 +6292,7 @@
         <v>1641</v>
       </c>
       <c r="P24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -6285,7 +6315,7 @@
         <v>1071</v>
       </c>
       <c r="P25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -6299,7 +6329,7 @@
         <v>1892</v>
       </c>
       <c r="P26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -6350,7 +6380,7 @@
         <v>502</v>
       </c>
       <c r="P29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -6370,7 +6400,7 @@
         <v>502</v>
       </c>
       <c r="P30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -6401,7 +6431,7 @@
         <v>522</v>
       </c>
       <c r="P32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -6461,7 +6491,7 @@
         <v>1.7341179006468701E-4</v>
       </c>
       <c r="K35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O35">
         <v>482</v>
@@ -6475,7 +6505,7 @@
         <v>0.64</v>
       </c>
       <c r="K36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O36">
         <v>586</v>
@@ -6497,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="20" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -6526,7 +6556,7 @@
         <v>1140</v>
       </c>
       <c r="P39" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -6549,7 +6579,7 @@
         <v>975</v>
       </c>
       <c r="P40" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -6563,7 +6593,7 @@
         <v>1140</v>
       </c>
       <c r="P41" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -6589,7 +6619,7 @@
         <v>975</v>
       </c>
       <c r="P42" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -6638,7 +6668,7 @@
         <v>1496</v>
       </c>
       <c r="P44" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -6698,7 +6728,7 @@
         <v>999</v>
       </c>
       <c r="P47" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
@@ -6715,7 +6745,7 @@
         <v>1050</v>
       </c>
       <c r="P48" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.25">
@@ -6729,7 +6759,7 @@
         <v>-5</v>
       </c>
       <c r="L49" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="O49">
         <v>996</v>
@@ -6746,13 +6776,13 @@
         <v>1.15176621671389</v>
       </c>
       <c r="L50" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O50">
         <v>1195</v>
       </c>
       <c r="P50" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.25">
@@ -6769,7 +6799,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="L51" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="O51">
         <v>1049</v>
@@ -6823,7 +6853,7 @@
         <v>1880</v>
       </c>
       <c r="P54" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.25">
@@ -6857,7 +6887,7 @@
         <v>1692</v>
       </c>
       <c r="P56" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.25">
@@ -6882,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.25">
@@ -6899,7 +6929,7 @@
         <v>1746</v>
       </c>
       <c r="P59" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.25">
@@ -6916,7 +6946,7 @@
         <v>1574</v>
       </c>
       <c r="P60" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.25">
@@ -6984,10 +7014,10 @@
         <v>1528</v>
       </c>
       <c r="P64" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>-1.0608132419307801</v>
       </c>
@@ -6998,16 +7028,16 @@
         <v>-4.9695269901766101</v>
       </c>
       <c r="L65" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="O65">
         <v>1167</v>
       </c>
       <c r="P65" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>-1.1261289140861099</v>
       </c>
@@ -7024,10 +7054,10 @@
         <v>1002</v>
       </c>
       <c r="P66" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>-1.2035253749880399</v>
       </c>
@@ -7041,7 +7071,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>-1.44395477402174</v>
       </c>
@@ -7055,11 +7085,11 @@
         <v>1121</v>
       </c>
       <c r="P68" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="69" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>-1.2038</v>
       </c>
@@ -7070,10 +7100,10 @@
         <v>-4.9325999999999999</v>
       </c>
       <c r="P70" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>-0.70223850678134803</v>
       </c>
@@ -7084,10 +7114,10 @@
         <v>-4.9512972108205302</v>
       </c>
       <c r="P71" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E72">
         <v>1</v>
       </c>
@@ -7104,10 +7134,19 @@
         <v>1147</v>
       </c>
       <c r="P72" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B73">
+        <v>-1.8904675242014499</v>
+      </c>
+      <c r="C73">
+        <v>0.78604681017162004</v>
+      </c>
+      <c r="D73">
+        <v>-4.8087781051542704</v>
+      </c>
       <c r="F73">
         <v>1.1499999999999999</v>
       </c>
@@ -7121,9 +7160,184 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="H74">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>4</v>
+      </c>
+      <c r="B74">
+        <v>-1.8904675242014499</v>
+      </c>
+      <c r="C74">
+        <v>0.78604681017162004</v>
+      </c>
+      <c r="D74">
+        <v>-4.8087781051542704</v>
+      </c>
+      <c r="G74">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="O74">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>-2.92555847278929</v>
+      </c>
+      <c r="C75">
+        <v>1.1553271728060299</v>
+      </c>
+      <c r="D75">
+        <v>-5</v>
+      </c>
+      <c r="O75">
+        <v>1110</v>
+      </c>
+      <c r="P75" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>6</v>
+      </c>
+      <c r="B76" s="23">
+        <v>-4.2861727192109598</v>
+      </c>
+      <c r="C76">
+        <v>1.98660254327817</v>
+      </c>
+      <c r="D76">
+        <v>-5</v>
+      </c>
+      <c r="O76">
+        <v>1613</v>
+      </c>
+      <c r="P76" t="s">
+        <v>716</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" s="22" t="s">
+        <v>721</v>
+      </c>
+      <c r="E77">
+        <v>0.7</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>7</v>
+      </c>
+      <c r="E78">
+        <v>0.8</v>
+      </c>
+      <c r="F78">
         <v>1</v>
+      </c>
+      <c r="O78">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E79">
+        <v>0.75</v>
+      </c>
+      <c r="O79">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E80">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="G80">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H81">
+        <v>0.9</v>
+      </c>
+      <c r="O81">
+        <v>1237</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P82" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <v>0.9</v>
+      </c>
+      <c r="O83">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H84">
+        <v>0.85</v>
+      </c>
+      <c r="O84">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E85">
+        <v>0.7</v>
+      </c>
+      <c r="O85">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H86">
+        <v>0.8</v>
+      </c>
+      <c r="O86">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H87">
+        <v>0.75</v>
+      </c>
+      <c r="O87">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>18</v>
+      </c>
+      <c r="F88">
+        <v>0.85</v>
+      </c>
+      <c r="G88">
+        <v>1.05</v>
+      </c>
+      <c r="O88">
+        <v>1463</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -7149,31 +7363,31 @@
   <sheetData>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -7181,16 +7395,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -7198,10 +7412,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7209,10 +7423,10 @@
         <v>3</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7220,13 +7434,13 @@
         <v>4</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -7234,10 +7448,10 @@
         <v>5</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -7245,13 +7459,13 @@
         <v>6</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -7259,10 +7473,10 @@
         <v>7</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7270,7 +7484,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7278,13 +7492,13 @@
         <v>9</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -7292,10 +7506,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -7303,7 +7517,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7311,10 +7525,10 @@
         <v>12</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7322,10 +7536,10 @@
         <v>13</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -7333,10 +7547,10 @@
         <v>14</v>
       </c>
       <c r="H16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -7344,10 +7558,10 @@
         <v>15</v>
       </c>
       <c r="H17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -7355,10 +7569,10 @@
         <v>16</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -7366,10 +7580,10 @@
         <v>17</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -7377,10 +7591,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7388,13 +7602,13 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7402,10 +7616,10 @@
         <v>20</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -7413,10 +7627,10 @@
         <v>21</v>
       </c>
       <c r="G23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -7424,10 +7638,10 @@
         <v>22</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -7435,10 +7649,10 @@
         <v>23</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -7446,10 +7660,10 @@
         <v>24</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7457,10 +7671,10 @@
         <v>25</v>
       </c>
       <c r="G27" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7468,10 +7682,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I28" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7479,10 +7693,10 @@
         <v>27</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -7490,7 +7704,7 @@
         <v>28</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -7498,7 +7712,7 @@
         <v>29</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -7506,7 +7720,7 @@
         <v>30</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -7514,10 +7728,10 @@
         <v>31</v>
       </c>
       <c r="F33" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -7525,13 +7739,13 @@
         <v>32</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -7539,7 +7753,7 @@
         <v>33</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -7547,7 +7761,7 @@
         <v>34</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -7555,10 +7769,10 @@
         <v>35</v>
       </c>
       <c r="H37" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I37" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -7566,13 +7780,13 @@
         <v>36</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="I38" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -7580,13 +7794,13 @@
         <v>37</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -7594,10 +7808,10 @@
         <v>38</v>
       </c>
       <c r="F40" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -7605,10 +7819,10 @@
         <v>39</v>
       </c>
       <c r="F41" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -7616,7 +7830,7 @@
         <v>40</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -7628,10 +7842,10 @@
       </c>
       <c r="E43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -7642,10 +7856,10 @@
         <v>7.3</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -7653,10 +7867,10 @@
         <v>43</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -7664,10 +7878,10 @@
         <v>44</v>
       </c>
       <c r="F46" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I46" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -7675,10 +7889,10 @@
         <v>45</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I47" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -7686,10 +7900,10 @@
         <v>46</v>
       </c>
       <c r="F48" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I48" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -7697,13 +7911,13 @@
         <v>47</v>
       </c>
       <c r="F49" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -7711,13 +7925,13 @@
         <v>48</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -7725,16 +7939,16 @@
         <v>49</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F51" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -7742,10 +7956,10 @@
         <v>50</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="60" x14ac:dyDescent="0.25">
@@ -7753,10 +7967,10 @@
         <v>51</v>
       </c>
       <c r="E53" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I53" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="60" x14ac:dyDescent="0.25">
@@ -7764,13 +7978,13 @@
         <v>52</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H54" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="H54" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="I54" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -7778,10 +7992,10 @@
         <v>53</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I55" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -7789,13 +8003,13 @@
         <v>54</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -7803,13 +8017,13 @@
         <v>55</v>
       </c>
       <c r="D57" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I57" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -7817,10 +8031,10 @@
         <v>56</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -7828,7 +8042,7 @@
         <v>57</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -7836,10 +8050,10 @@
         <v>58</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -7847,13 +8061,13 @@
         <v>59</v>
       </c>
       <c r="D61" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I61" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -7861,10 +8075,10 @@
         <v>60</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -7872,10 +8086,10 @@
         <v>61</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -7883,10 +8097,10 @@
         <v>62</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -7894,10 +8108,10 @@
         <v>63</v>
       </c>
       <c r="F65" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I65" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -7905,10 +8119,10 @@
         <v>64</v>
       </c>
       <c r="D66" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -7916,10 +8130,10 @@
         <v>65</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -7927,10 +8141,10 @@
         <v>66</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7938,10 +8152,10 @@
         <v>67</v>
       </c>
       <c r="F69" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I69" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7949,13 +8163,13 @@
         <v>68</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F70" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I70" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7963,13 +8177,13 @@
         <v>69</v>
       </c>
       <c r="D71" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="H71" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="H71" s="4" t="s">
+      <c r="I71" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -7977,7 +8191,7 @@
         <v>70</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7988,10 +8202,10 @@
         <v>7.6</v>
       </c>
       <c r="G73" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I73" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8002,10 +8216,10 @@
         <v>7.7</v>
       </c>
       <c r="G74" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I74" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -8013,10 +8227,10 @@
         <v>73</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -8024,10 +8238,10 @@
         <v>74</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8035,10 +8249,10 @@
         <v>75</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8046,13 +8260,13 @@
         <v>76</v>
       </c>
       <c r="F78" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="I78" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -8060,10 +8274,10 @@
         <v>77</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8071,10 +8285,10 @@
         <v>78</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -8082,10 +8296,10 @@
         <v>79</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8093,13 +8307,13 @@
         <v>80</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8107,10 +8321,10 @@
         <v>81</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -8118,7 +8332,7 @@
         <v>82</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -8126,10 +8340,10 @@
         <v>83</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -8137,13 +8351,13 @@
         <v>84</v>
       </c>
       <c r="F86" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -8151,7 +8365,7 @@
         <v>85</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -8159,10 +8373,10 @@
         <v>86</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -8170,10 +8384,10 @@
         <v>87</v>
       </c>
       <c r="H89" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="I89" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -8181,10 +8395,10 @@
         <v>88</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -8192,7 +8406,7 @@
         <v>89</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -8200,7 +8414,7 @@
         <v>90</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -8208,7 +8422,7 @@
         <v>91</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -8216,7 +8430,7 @@
         <v>92</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -8224,10 +8438,10 @@
         <v>93</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -8235,10 +8449,10 @@
         <v>94</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8246,13 +8460,13 @@
         <v>95</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -8260,10 +8474,10 @@
         <v>96</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8271,13 +8485,13 @@
         <v>97</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8285,13 +8499,13 @@
         <v>98</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -8299,16 +8513,16 @@
         <v>7.8</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8316,10 +8530,10 @@
         <v>99</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -8327,7 +8541,7 @@
         <v>100</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8335,10 +8549,10 @@
         <v>101</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -8346,10 +8560,10 @@
         <v>102</v>
       </c>
       <c r="H105" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I105" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="I105" s="4" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8357,10 +8571,10 @@
         <v>103</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -8368,10 +8582,10 @@
         <v>104</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -8379,10 +8593,10 @@
         <v>105</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8390,10 +8604,10 @@
         <v>106</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -8401,10 +8615,10 @@
         <v>107</v>
       </c>
       <c r="F110" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="I110" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="I110" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -8412,10 +8626,10 @@
         <v>108</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -8423,10 +8637,10 @@
         <v>109</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8434,10 +8648,10 @@
         <v>110</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -8445,13 +8659,13 @@
         <v>111</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -8462,7 +8676,7 @@
         <v>7.7</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -8470,13 +8684,13 @@
         <v>113</v>
       </c>
       <c r="E117" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I117" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="I117" s="4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -8484,10 +8698,10 @@
         <v>114</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -8495,10 +8709,10 @@
         <v>115</v>
       </c>
       <c r="H119" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I119" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="I119" s="4" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -8506,7 +8720,7 @@
         <v>116</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8514,10 +8728,10 @@
         <v>117</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -8525,7 +8739,7 @@
         <v>118</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -8533,10 +8747,10 @@
         <v>119</v>
       </c>
       <c r="F123" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="I123" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="I123" s="4" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -8547,13 +8761,13 @@
         <v>7.9</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I125" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -8561,10 +8775,10 @@
         <v>121</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -8572,10 +8786,10 @@
         <v>122</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -8583,10 +8797,10 @@
         <v>123</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8594,10 +8808,10 @@
         <v>124</v>
       </c>
       <c r="D129" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="I129" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="I129" s="4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -8605,10 +8819,10 @@
         <v>125</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8616,10 +8830,10 @@
         <v>126</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -8627,10 +8841,10 @@
         <v>127</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -8638,10 +8852,10 @@
         <v>128</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8649,10 +8863,10 @@
         <v>129</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -8660,10 +8874,10 @@
         <v>130</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
@@ -8671,7 +8885,7 @@
         <v>131</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -8679,7 +8893,7 @@
         <v>132</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8687,10 +8901,10 @@
         <v>133</v>
       </c>
       <c r="D138" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I138" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="I138" s="4" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -8698,7 +8912,7 @@
         <v>134</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -8706,7 +8920,7 @@
         <v>135</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -8714,10 +8928,10 @@
         <v>136</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8725,10 +8939,10 @@
         <v>137</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I142" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -8736,10 +8950,10 @@
         <v>138</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -8747,10 +8961,10 @@
         <v>139</v>
       </c>
       <c r="H144" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="I144" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="I144" s="4" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -8758,10 +8972,10 @@
         <v>140</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I145" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
@@ -8769,10 +8983,10 @@
         <v>141</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -8780,10 +8994,10 @@
         <v>142</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -8791,10 +9005,10 @@
         <v>143</v>
       </c>
       <c r="F148" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="I148" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="I148" s="4" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8802,10 +9016,10 @@
         <v>144</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8813,27 +9027,27 @@
         <v>145</v>
       </c>
       <c r="H150" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="I150" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="I150" s="4" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B151" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="I151" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="D151" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="H151" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="I151" s="4" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -8844,13 +9058,13 @@
         <v>7.11</v>
       </c>
       <c r="D152" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="H152" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="H152" s="4" t="s">
+      <c r="I152" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="I152" s="4" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -8858,18 +9072,18 @@
         <v>147</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D154" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -8877,13 +9091,13 @@
         <v>7.12</v>
       </c>
       <c r="D155" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="I155" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="F155" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="I155" s="4" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8891,13 +9105,13 @@
         <v>148</v>
       </c>
       <c r="D156" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="I156" s="16" t="s">
         <v>345</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="I156" s="16" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8905,10 +9119,10 @@
         <v>149</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I157" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8916,10 +9130,10 @@
         <v>150</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I158" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8927,10 +9141,10 @@
         <v>151</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I159" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -8938,10 +9152,10 @@
         <v>152</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I160" s="17" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -8949,10 +9163,10 @@
         <v>153</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I161" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -8960,10 +9174,10 @@
         <v>154</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I162" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -8971,13 +9185,13 @@
         <v>155</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I163" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
@@ -8985,10 +9199,10 @@
         <v>156</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I164" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
@@ -8996,10 +9210,10 @@
         <v>157</v>
       </c>
       <c r="H165" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="I165" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="I165" s="4" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9007,10 +9221,10 @@
         <v>158</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I166" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9018,10 +9232,10 @@
         <v>159</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I167" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -9029,10 +9243,10 @@
         <v>160</v>
       </c>
       <c r="F168" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="I168" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="I168" s="4" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
@@ -9040,10 +9254,10 @@
         <v>161</v>
       </c>
       <c r="D169" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="I169" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="I169" s="4" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -9051,10 +9265,10 @@
         <v>162</v>
       </c>
       <c r="H170" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="I170" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="I170" s="4" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -9062,13 +9276,13 @@
         <v>163</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I171" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -9076,7 +9290,7 @@
         <v>164</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
@@ -9084,7 +9298,7 @@
         <v>165</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
@@ -9092,10 +9306,10 @@
         <v>166</v>
       </c>
       <c r="H174" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="I174" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="I174" s="4" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9103,7 +9317,7 @@
         <v>167</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
@@ -9111,10 +9325,10 @@
         <v>168</v>
       </c>
       <c r="D176" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I176" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="I176" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9122,10 +9336,10 @@
         <v>169</v>
       </c>
       <c r="D177" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="H177" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="H177" s="4" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -9133,7 +9347,7 @@
         <v>170</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -9141,10 +9355,10 @@
         <v>171</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I179" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
@@ -9152,7 +9366,7 @@
         <v>172</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
@@ -9160,10 +9374,10 @@
         <v>173</v>
       </c>
       <c r="H181" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="I181" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="I181" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
@@ -9171,10 +9385,10 @@
         <v>174</v>
       </c>
       <c r="F182" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="I182" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="I182" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
@@ -9182,10 +9396,10 @@
         <v>175</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I183" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -9193,7 +9407,7 @@
         <v>176</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -9201,7 +9415,7 @@
         <v>177</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
@@ -9209,7 +9423,7 @@
         <v>178</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -9217,10 +9431,10 @@
         <v>179</v>
       </c>
       <c r="H187" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="I187" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="I187" s="4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
@@ -9228,10 +9442,10 @@
         <v>180</v>
       </c>
       <c r="F188" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="I188" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="I188" s="4" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
@@ -9239,10 +9453,10 @@
         <v>181</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -9250,7 +9464,7 @@
         <v>182</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
@@ -9258,7 +9472,7 @@
         <v>183</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -9266,10 +9480,10 @@
         <v>184</v>
       </c>
       <c r="F192" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="H192" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="H192" s="4" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -9277,7 +9491,7 @@
         <v>185</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
@@ -9285,7 +9499,7 @@
         <v>186</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9293,10 +9507,10 @@
         <v>187</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I195" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -9304,13 +9518,13 @@
         <v>188</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I196" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -9318,10 +9532,10 @@
         <v>189</v>
       </c>
       <c r="F197" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="I197" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="I197" s="4" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -9332,13 +9546,13 @@
         <v>7.13</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D198" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="I198" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="I198" s="4" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9349,21 +9563,21 @@
         <v>7.14</v>
       </c>
       <c r="C199" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="G199" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I199" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="G199" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="I199" s="4" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I200" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9371,13 +9585,13 @@
         <v>192</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I201" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9385,10 +9599,10 @@
         <v>193</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I202" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -9396,16 +9610,16 @@
         <v>194</v>
       </c>
       <c r="D203" s="18" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G203" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="H203" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="H203" s="4" t="s">
+      <c r="I203" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="I203" s="4" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -9413,10 +9627,10 @@
         <v>195</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I204" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="205" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9424,35 +9638,35 @@
         <v>196</v>
       </c>
       <c r="F205" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="I205" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="I205" s="4" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I206" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I207" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -9460,10 +9674,10 @@
         <v>7.14</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -9471,13 +9685,13 @@
         <v>198</v>
       </c>
       <c r="D209" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="H209" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="H209" s="4" t="s">
-        <v>434</v>
-      </c>
       <c r="I209" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -9485,7 +9699,7 @@
         <v>199</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -9493,10 +9707,10 @@
         <v>200</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -9504,10 +9718,10 @@
         <v>201</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -9515,10 +9729,10 @@
         <v>202</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="214" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9526,7 +9740,7 @@
         <v>203</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -9534,13 +9748,13 @@
         <v>204</v>
       </c>
       <c r="F215" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="H215" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="I215" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="H215" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="I215" s="4" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9548,10 +9762,10 @@
         <v>205</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I216" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -9559,10 +9773,10 @@
         <v>206</v>
       </c>
       <c r="H217" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I217" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="I217" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -9570,10 +9784,10 @@
         <v>207</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9581,10 +9795,10 @@
         <v>208</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I219" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9592,10 +9806,10 @@
         <v>209</v>
       </c>
       <c r="H220" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="I220" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="I220" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
@@ -9603,10 +9817,10 @@
         <v>210</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I221" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="222" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -9614,13 +9828,13 @@
         <v>211</v>
       </c>
       <c r="F222" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H222" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="I222" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="H222" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="I222" s="4" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -9628,13 +9842,13 @@
         <v>212</v>
       </c>
       <c r="F223" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="H223" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I223" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="H223" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="I223" s="4" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
@@ -9642,24 +9856,24 @@
         <v>213</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I224" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="225" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I225" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="226" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9667,13 +9881,13 @@
         <v>214</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I226" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -9681,7 +9895,7 @@
         <v>215</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
@@ -9689,7 +9903,7 @@
         <v>216</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
@@ -9697,10 +9911,10 @@
         <v>217</v>
       </c>
       <c r="F229" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="I229" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="I229" s="4" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
@@ -9708,7 +9922,7 @@
         <v>218</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="231" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9716,10 +9930,10 @@
         <v>219</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I231" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
@@ -9727,10 +9941,10 @@
         <v>220</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
@@ -9738,13 +9952,13 @@
         <v>221</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I233" s="19" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -9752,13 +9966,13 @@
         <v>222</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H234" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="I234" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="I234" s="4" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
@@ -9766,10 +9980,10 @@
         <v>223</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I235" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
@@ -9777,10 +9991,10 @@
         <v>224</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I236" s="19" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="237" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -9791,19 +10005,19 @@
         <v>7.15</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I237" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="238" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9811,10 +10025,10 @@
         <v>226</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I238" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
@@ -9822,7 +10036,7 @@
         <v>227</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -9830,7 +10044,7 @@
         <v>228</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9838,7 +10052,7 @@
         <v>229</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
@@ -9846,7 +10060,7 @@
         <v>230</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
@@ -9854,7 +10068,7 @@
         <v>231</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="244" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -9865,19 +10079,19 @@
         <v>7.16</v>
       </c>
       <c r="C244" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="D244" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="D244" s="4" t="s">
+      <c r="F244" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="H244" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="I244" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="F244" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="H244" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="I244" s="4" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="245" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9885,10 +10099,10 @@
         <v>233</v>
       </c>
       <c r="F245" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="I245" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="I245" s="4" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
@@ -9896,13 +10110,13 @@
         <v>234</v>
       </c>
       <c r="D246" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="I246" s="4" t="s">
         <v>493</v>
-      </c>
-      <c r="F246" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="I246" s="4" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="247" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9910,13 +10124,13 @@
         <v>235</v>
       </c>
       <c r="D247" s="13" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H247" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
@@ -9924,10 +10138,10 @@
         <v>236</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I248" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
@@ -9935,7 +10149,7 @@
         <v>237</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -9943,10 +10157,10 @@
         <v>238</v>
       </c>
       <c r="F250" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="I250" s="4" t="s">
         <v>497</v>
-      </c>
-      <c r="I250" s="4" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="251" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9954,10 +10168,10 @@
         <v>239</v>
       </c>
       <c r="F251" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="I251" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="I251" s="4" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="252" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9965,10 +10179,10 @@
         <v>240</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I252" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="253" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9976,10 +10190,10 @@
         <v>241</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="254" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -9987,12 +10201,12 @@
         <v>242</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F255" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
@@ -10000,10 +10214,10 @@
         <v>244</v>
       </c>
       <c r="G256" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="I256" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="I256" s="4" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10011,10 +10225,10 @@
         <v>245</v>
       </c>
       <c r="F257" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="I257" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="I257" s="4" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="258" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -10022,10 +10236,10 @@
         <v>246</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="259" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10033,10 +10247,10 @@
         <v>247</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I259" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -10044,10 +10258,10 @@
         <v>248</v>
       </c>
       <c r="G260" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="I260" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="I260" s="4" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="261" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10055,13 +10269,13 @@
         <v>249</v>
       </c>
       <c r="G261" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="H261" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="H261" s="4" t="s">
-        <v>518</v>
-      </c>
       <c r="I261" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="262" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10069,10 +10283,10 @@
         <v>250</v>
       </c>
       <c r="F262" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="I262" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="I262" s="4" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
@@ -10080,10 +10294,10 @@
         <v>251</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I263" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10091,16 +10305,16 @@
         <v>252</v>
       </c>
       <c r="F264" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="G264" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="G264" s="4" t="s">
-        <v>527</v>
-      </c>
       <c r="H264" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I264" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="265" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10108,16 +10322,16 @@
         <v>253</v>
       </c>
       <c r="F265" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="G265" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="G265" s="4" t="s">
+      <c r="H265" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="I265" s="4" t="s">
         <v>532</v>
-      </c>
-      <c r="H265" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="I265" s="4" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
@@ -10125,10 +10339,10 @@
         <v>254</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
@@ -10136,13 +10350,13 @@
         <v>255</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I267" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="269" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10150,20 +10364,20 @@
         <v>257</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="270" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="I270" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="271" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="H271" s="13" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I271" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="272" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10171,18 +10385,18 @@
         <v>258</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G272" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H272" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="273" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="I273" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
@@ -10190,10 +10404,10 @@
         <v>259</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I274" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
@@ -10201,10 +10415,10 @@
         <v>260</v>
       </c>
       <c r="D275" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="I275" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="I275" s="4" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
@@ -10212,13 +10426,13 @@
         <v>261</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H276" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I276" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
@@ -10226,7 +10440,7 @@
         <v>262</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
@@ -10234,12 +10448,12 @@
         <v>263</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D279" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="280" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10247,13 +10461,13 @@
         <v>264</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E280" s="12" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I280" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10261,13 +10475,13 @@
         <v>265</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I281" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="282" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -10275,10 +10489,10 @@
         <v>266</v>
       </c>
       <c r="H282" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="I282" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="I282" s="4" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="283" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10286,10 +10500,10 @@
         <v>267</v>
       </c>
       <c r="H283" s="12" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I283" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
@@ -10297,10 +10511,10 @@
         <v>268</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I284" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
@@ -10308,10 +10522,10 @@
         <v>269</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I285" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -10319,18 +10533,18 @@
         <v>270</v>
       </c>
       <c r="F286" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="I286" s="4" t="s">
         <v>566</v>
-      </c>
-      <c r="I286" s="4" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D287" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="I287" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="I287" s="4" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
@@ -10338,10 +10552,10 @@
         <v>271</v>
       </c>
       <c r="D288" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="I288" s="4" t="s">
         <v>570</v>
-      </c>
-      <c r="I288" s="4" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
@@ -10349,10 +10563,10 @@
         <v>272</v>
       </c>
       <c r="D289" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="I289" s="4" t="s">
         <v>572</v>
-      </c>
-      <c r="I289" s="4" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
@@ -10360,10 +10574,10 @@
         <v>273</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E290" s="12" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="291" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10371,7 +10585,7 @@
         <v>274</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="292" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10379,10 +10593,10 @@
         <v>275</v>
       </c>
       <c r="F292" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="I292" s="4" t="s">
         <v>576</v>
-      </c>
-      <c r="I292" s="4" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
@@ -10390,7 +10604,7 @@
         <v>276</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
@@ -10398,13 +10612,13 @@
         <v>277</v>
       </c>
       <c r="F294" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="H294" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="I294" s="4" t="s">
         <v>580</v>
-      </c>
-      <c r="H294" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="I294" s="4" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -10412,10 +10626,10 @@
         <v>278</v>
       </c>
       <c r="F295" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="I295" s="4" t="s">
         <v>582</v>
-      </c>
-      <c r="I295" s="4" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
@@ -10423,13 +10637,13 @@
         <v>279</v>
       </c>
       <c r="F296" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="I296" s="4" t="s">
         <v>585</v>
-      </c>
-      <c r="H296" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="I296" s="4" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
@@ -10437,7 +10651,7 @@
         <v>280</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="298" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10445,10 +10659,10 @@
         <v>281</v>
       </c>
       <c r="F298" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="I298" s="4" t="s">
         <v>588</v>
-      </c>
-      <c r="I298" s="4" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
@@ -10456,10 +10670,10 @@
         <v>282</v>
       </c>
       <c r="F299" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="I299" s="4" t="s">
         <v>590</v>
-      </c>
-      <c r="I299" s="4" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
@@ -10467,10 +10681,10 @@
         <v>283</v>
       </c>
       <c r="F300" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="I300" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="I300" s="4" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
@@ -10478,13 +10692,13 @@
         <v>284</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F301" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="I301" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="I301" s="4" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="302" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10492,13 +10706,13 @@
         <v>285</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H302" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="I302" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="I302" s="4" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="303" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10506,10 +10720,10 @@
         <v>286</v>
       </c>
       <c r="F303" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="I303" s="4" t="s">
         <v>599</v>
-      </c>
-      <c r="I303" s="4" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
@@ -10517,10 +10731,10 @@
         <v>287</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H304" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
@@ -10528,10 +10742,10 @@
         <v>288</v>
       </c>
       <c r="F305" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I305" s="4" t="s">
         <v>602</v>
-      </c>
-      <c r="I305" s="4" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
@@ -10539,7 +10753,7 @@
         <v>289</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
@@ -10547,10 +10761,10 @@
         <v>290</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="308" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10558,13 +10772,13 @@
         <v>291</v>
       </c>
       <c r="F308" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H308" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="H308" s="4" t="s">
+      <c r="I308" s="4" t="s">
         <v>608</v>
-      </c>
-      <c r="I308" s="4" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
@@ -10572,10 +10786,10 @@
         <v>292</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I309" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
@@ -10583,7 +10797,7 @@
         <v>293</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
@@ -10591,7 +10805,7 @@
         <v>294</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="312" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10599,10 +10813,10 @@
         <v>295</v>
       </c>
       <c r="F312" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="I312" s="4" t="s">
         <v>613</v>
-      </c>
-      <c r="I312" s="4" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
@@ -10610,7 +10824,7 @@
         <v>296</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
@@ -10618,10 +10832,10 @@
         <v>297</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I314" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="315" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10629,13 +10843,13 @@
         <v>298</v>
       </c>
       <c r="F315" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="G315" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="G315" s="4" t="s">
+      <c r="I315" s="4" t="s">
         <v>620</v>
-      </c>
-      <c r="I315" s="4" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
@@ -10643,7 +10857,7 @@
         <v>299</v>
       </c>
       <c r="H316" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="317" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10651,7 +10865,7 @@
         <v>300</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="318" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10659,10 +10873,10 @@
         <v>301</v>
       </c>
       <c r="F318" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G318" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
@@ -10670,7 +10884,7 @@
         <v>302</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
@@ -10678,7 +10892,7 @@
         <v>303</v>
       </c>
       <c r="G320" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
@@ -10686,7 +10900,7 @@
         <v>304</v>
       </c>
       <c r="H321" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
@@ -10694,7 +10908,7 @@
         <v>305</v>
       </c>
       <c r="G322" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
@@ -10702,7 +10916,7 @@
         <v>306</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
@@ -10710,15 +10924,15 @@
         <v>307</v>
       </c>
       <c r="F324" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F325" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
@@ -10726,7 +10940,7 @@
         <v>308</v>
       </c>
       <c r="F326" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
@@ -10734,10 +10948,10 @@
         <v>309</v>
       </c>
       <c r="H327" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I327" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
@@ -10745,10 +10959,10 @@
         <v>310</v>
       </c>
       <c r="H328" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I328" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
@@ -10756,13 +10970,13 @@
         <v>311</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H329" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="I329" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
@@ -10770,10 +10984,10 @@
         <v>312</v>
       </c>
       <c r="F330" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I330" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
@@ -10781,10 +10995,10 @@
         <v>313</v>
       </c>
       <c r="H331" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="I331" s="12" t="s">
         <v>634</v>
-      </c>
-      <c r="I331" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
@@ -10792,10 +11006,10 @@
         <v>314</v>
       </c>
       <c r="D332" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="I332" s="4" t="s">
         <v>636</v>
-      </c>
-      <c r="I332" s="4" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="333" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10803,27 +11017,27 @@
         <v>315</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F333" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="H333" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="I333" s="4" t="s">
         <v>638</v>
-      </c>
-      <c r="H333" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="I333" s="4" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F334" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="I334" s="4" t="s">
         <v>640</v>
-      </c>
-      <c r="I334" s="4" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
@@ -10831,15 +11045,15 @@
         <v>316</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F336" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="337" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10847,10 +11061,10 @@
         <v>318</v>
       </c>
       <c r="F337" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="I337" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
@@ -10858,10 +11072,10 @@
         <v>319</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I338" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
@@ -10869,10 +11083,10 @@
         <v>320</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="340" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10880,10 +11094,10 @@
         <v>321</v>
       </c>
       <c r="G340" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="I340" s="4" t="s">
         <v>650</v>
-      </c>
-      <c r="I340" s="4" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="341" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -10891,18 +11105,18 @@
         <v>322</v>
       </c>
       <c r="F341" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="I341" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="I341" s="4" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F342" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="I342" s="4" t="s">
         <v>654</v>
-      </c>
-      <c r="I342" s="4" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
@@ -10910,10 +11124,10 @@
         <v>324</v>
       </c>
       <c r="F343" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="I343" s="4" t="s">
         <v>656</v>
-      </c>
-      <c r="I343" s="4" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.25">
@@ -10921,7 +11135,7 @@
         <v>325</v>
       </c>
       <c r="F344" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
@@ -10929,7 +11143,7 @@
         <v>326</v>
       </c>
       <c r="F345" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
@@ -10937,7 +11151,7 @@
         <v>327</v>
       </c>
       <c r="F346" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.25">
@@ -10945,7 +11159,7 @@
         <v>328</v>
       </c>
       <c r="F347" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
@@ -10953,10 +11167,10 @@
         <v>329</v>
       </c>
       <c r="F348" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G348" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.25">
@@ -10964,7 +11178,7 @@
         <v>330</v>
       </c>
       <c r="F349" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.25">
@@ -10972,7 +11186,7 @@
         <v>331</v>
       </c>
       <c r="F350" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.25">
@@ -10980,7 +11194,7 @@
         <v>332</v>
       </c>
       <c r="F351" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.25">
@@ -10988,10 +11202,10 @@
         <v>333</v>
       </c>
       <c r="G352" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I352" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.25">
@@ -10999,10 +11213,10 @@
         <v>334</v>
       </c>
       <c r="H353" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="I353" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.25">
@@ -11010,7 +11224,7 @@
         <v>335</v>
       </c>
       <c r="F354" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="I354" s="12"/>
     </row>
@@ -11019,7 +11233,7 @@
         <v>336</v>
       </c>
       <c r="F355" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.25">
@@ -11027,7 +11241,7 @@
         <v>337</v>
       </c>
       <c r="H356" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.25">
@@ -11035,7 +11249,7 @@
         <v>338</v>
       </c>
       <c r="F357" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
@@ -11043,13 +11257,13 @@
         <v>339</v>
       </c>
       <c r="D358" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="H358" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="H358" s="4" t="s">
-        <v>688</v>
-      </c>
       <c r="I358" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.25">
@@ -11057,13 +11271,13 @@
         <v>340</v>
       </c>
       <c r="D360" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="H360" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="I360" s="12" t="s">
         <v>692</v>
-      </c>
-      <c r="H360" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="I360" s="12" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.25">
@@ -11071,16 +11285,16 @@
         <v>341</v>
       </c>
       <c r="B361" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="F361" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="H361" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="I361" s="12" t="s">
         <v>698</v>
-      </c>
-      <c r="F361" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="H361" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="I361" s="12" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.25">
@@ -11088,7 +11302,7 @@
         <v>342</v>
       </c>
       <c r="I362" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
@@ -11099,10 +11313,10 @@
         <v>7.17</v>
       </c>
       <c r="F363" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="G363" s="4" t="s">
         <v>700</v>
-      </c>
-      <c r="G363" s="4" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="364" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -11110,13 +11324,13 @@
         <v>344</v>
       </c>
       <c r="F364" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="G364" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="I364" s="21" t="s">
         <v>703</v>
-      </c>
-      <c r="G364" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="I364" s="21" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.25">
@@ -11124,13 +11338,13 @@
         <v>345</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E365" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H365" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.25">
@@ -11138,7 +11352,7 @@
         <v>346</v>
       </c>
       <c r="F366" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.25">
@@ -11146,7 +11360,7 @@
         <v>347</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.25">
@@ -11154,51 +11368,51 @@
         <v>348</v>
       </c>
       <c r="D368" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="H368" s="4" t="s">
         <v>712</v>
-      </c>
-      <c r="H368" s="4" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="372" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="G372" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="377" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G377" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="378" spans="4:9" ht="45" x14ac:dyDescent="0.25">
       <c r="D378" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="379" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D379" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H379" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="380" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H380" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="382" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D382" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="384" spans="4:9" ht="30" x14ac:dyDescent="0.25">
       <c r="D384" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I384" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -11398,18 +11612,18 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" t="s">
         <v>200</v>
       </c>
-      <c r="C23" t="s">
-        <v>201</v>
-      </c>
       <c r="D23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -11585,10 +11799,10 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" t="s">
         <v>198</v>
-      </c>
-      <c r="B35" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -11625,7 +11839,7 @@
         <v>503</v>
       </c>
       <c r="Q38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -11636,7 +11850,7 @@
         <v>477</v>
       </c>
       <c r="Q39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C09ED1-ECE5-4F69-8C35-4BF2DDE8C751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313BBE19-BC0E-4329-972F-E46C9E6B8E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="727">
   <si>
     <t>A</t>
   </si>
@@ -2307,6 +2307,12 @@
   </si>
   <si>
     <t>very good scatter plots</t>
+  </si>
+  <si>
+    <t>high qlpm</t>
+  </si>
+  <si>
+    <t>solid not bad, gas too cold and flat</t>
   </si>
 </sst>
 </file>
@@ -5801,7 +5807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Q88"/>
+  <dimension ref="A2:Q96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="16" max="16" width="46.85546875" bestFit="1" customWidth="1"/>
@@ -7338,6 +7344,94 @@
       </c>
       <c r="Q88" t="s">
         <v>724</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>19</v>
+      </c>
+      <c r="O89">
+        <v>2704</v>
+      </c>
+      <c r="P89" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>20</v>
+      </c>
+      <c r="E90">
+        <v>0.9</v>
+      </c>
+      <c r="O90">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>21</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H91">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>22</v>
+      </c>
+      <c r="E92">
+        <v>0.95</v>
+      </c>
+      <c r="O92">
+        <v>1439</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>23</v>
+      </c>
+      <c r="G93">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="O93">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>24</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="O94">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E95">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O95">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E96">
+        <v>1.05</v>
+      </c>
+      <c r="O96">
+        <v>1139</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313BBE19-BC0E-4329-972F-E46C9E6B8E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E4589E-5D37-4E7C-98A1-86DBA36470F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="735">
   <si>
     <t>A</t>
   </si>
@@ -2313,6 +2313,30 @@
   </si>
   <si>
     <t>solid not bad, gas too cold and flat</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>optical</t>
+  </si>
+  <si>
+    <t>ε=0.9, α=0.7</t>
+  </si>
+  <si>
+    <t>back to 0.85</t>
+  </si>
+  <si>
+    <t>0D_v1 instead of _v2</t>
+  </si>
+  <si>
+    <t>I_all needs reduction</t>
+  </si>
+  <si>
+    <t>back to _v2</t>
   </si>
 </sst>
 </file>
@@ -2434,7 +2458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2491,6 +2515,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5807,14 +5835,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Q96"/>
+  <dimension ref="A2:R104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="16" max="16" width="46.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.140625" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5854,17 +5883,20 @@
       <c r="N2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="24" t="s">
+        <v>729</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5904,14 +5936,14 @@
       <c r="N3">
         <v>0.4</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>499.47699999999998</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5927,14 +5959,14 @@
       <c r="E4">
         <v>0.66</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>528.26599999999996</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5953,14 +5985,14 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>473.34</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5976,11 +6008,11 @@
       <c r="G6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5996,14 +6028,14 @@
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>604.08600000000001</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6019,11 +6051,11 @@
       <c r="E8">
         <v>0.7</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -6039,11 +6071,11 @@
       <c r="E9">
         <v>0.63</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -6059,14 +6091,14 @@
       <c r="G10">
         <v>1.2</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>500</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6082,14 +6114,14 @@
       <c r="E11">
         <v>0.64</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>480</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -6105,39 +6137,39 @@
       <c r="I12" t="s">
         <v>20</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>672</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="J13" t="s">
         <v>24</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="K14" t="s">
         <v>28</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>25612</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -6156,25 +6188,25 @@
       <c r="K15" t="s">
         <v>27</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>469</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>53</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -6187,44 +6219,44 @@
       <c r="D17">
         <v>25.984272299692599</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>465</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="E19">
         <v>0.84</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>850</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -6234,28 +6266,28 @@
       <c r="F21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>573</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="E22">
         <v>0.64</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>607</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -6271,14 +6303,14 @@
       <c r="E23">
         <v>0.7</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>502</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -6294,14 +6326,14 @@
       <c r="L24">
         <v>4.4000000000000004</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>1641</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -6317,28 +6349,28 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>1071</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="L26">
         <v>1</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>1892</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -6354,11 +6386,11 @@
       <c r="E27">
         <v>0.9</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>1354</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -6375,21 +6407,21 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="E29">
         <v>0.7</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>502</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -6402,14 +6434,14 @@
       <c r="D30">
         <v>1.3738648256894E-4</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>502</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -6425,22 +6457,22 @@
       <c r="N31">
         <v>0.6</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>522</v>
       </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -6456,11 +6488,11 @@
       <c r="N33">
         <v>0</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>563</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -6479,11 +6511,11 @@
       <c r="G34">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>461</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -6499,11 +6531,11 @@
       <c r="K35" t="s">
         <v>72</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -6513,30 +6545,30 @@
       <c r="K36" t="s">
         <v>27</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>586</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="E37">
         <v>0.75</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N38">
         <v>0</v>
       </c>
-      <c r="P38" s="20" t="s">
+      <c r="Q38" s="20" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>35</v>
       </c>
@@ -6558,14 +6590,14 @@
       <c r="I39">
         <v>7.8E-2</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>1140</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>36</v>
       </c>
@@ -6581,28 +6613,28 @@
       <c r="L40">
         <v>3</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>975</v>
       </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>37</v>
       </c>
       <c r="L41">
         <v>1</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>1140</v>
       </c>
-      <c r="P41" t="s">
+      <c r="Q41" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>38</v>
       </c>
@@ -6621,14 +6653,14 @@
       <c r="M42">
         <v>3</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>975</v>
       </c>
-      <c r="P42" t="s">
+      <c r="Q42" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>39</v>
       </c>
@@ -6650,11 +6682,11 @@
       <c r="M43">
         <v>1</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>975</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>40</v>
       </c>
@@ -6670,14 +6702,14 @@
       <c r="E44">
         <v>1</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>1496</v>
       </c>
-      <c r="P44" t="s">
+      <c r="Q44" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>41</v>
       </c>
@@ -6693,11 +6725,11 @@
       <c r="E45">
         <v>0.7</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>1027</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>42</v>
       </c>
@@ -6713,11 +6745,11 @@
       <c r="L46">
         <v>2</v>
       </c>
-      <c r="O46">
+      <c r="P46">
         <v>999</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>43</v>
       </c>
@@ -6730,14 +6762,14 @@
       <c r="D47">
         <v>-3.85853069192695</v>
       </c>
-      <c r="O47">
+      <c r="P47">
         <v>999</v>
       </c>
-      <c r="P47" t="s">
+      <c r="Q47" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>-0.59913658322029595</v>
       </c>
@@ -6747,14 +6779,14 @@
       <c r="D48">
         <v>-4.54729113095385</v>
       </c>
-      <c r="O48">
+      <c r="P48">
         <v>1050</v>
       </c>
-      <c r="P48" t="s">
+      <c r="Q48" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>-3.0218416280894E-2</v>
       </c>
@@ -6767,11 +6799,11 @@
       <c r="L49" t="s">
         <v>678</v>
       </c>
-      <c r="O49">
+      <c r="P49">
         <v>996</v>
       </c>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>2.32366143478863</v>
       </c>
@@ -6784,14 +6816,14 @@
       <c r="L50" t="s">
         <v>679</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <v>1195</v>
       </c>
-      <c r="P50" t="s">
+      <c r="Q50" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>-0.11531413827813</v>
       </c>
@@ -6807,11 +6839,11 @@
       <c r="L51" t="s">
         <v>681</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <v>1049</v>
       </c>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>-5.9825795140801101E-2</v>
       </c>
@@ -6824,11 +6856,11 @@
       <c r="F52">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O52">
+      <c r="P52">
         <v>1016</v>
       </c>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>0.163215104178386</v>
       </c>
@@ -6841,11 +6873,11 @@
       <c r="E53">
         <v>1</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>1882</v>
       </c>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>0.16620523432742201</v>
       </c>
@@ -6855,14 +6887,14 @@
       <c r="D54">
         <v>-1.95188474207697</v>
       </c>
-      <c r="O54">
+      <c r="P54">
         <v>1880</v>
       </c>
-      <c r="P54" t="s">
+      <c r="Q54" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>0.113337590003834</v>
       </c>
@@ -6875,11 +6907,11 @@
       <c r="F55">
         <v>1</v>
       </c>
-      <c r="O55">
+      <c r="P55">
         <v>1692</v>
       </c>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>0.115547627813837</v>
       </c>
@@ -6889,14 +6921,14 @@
       <c r="D56">
         <v>-4.5277566109866303</v>
       </c>
-      <c r="O56">
+      <c r="P56">
         <v>1692</v>
       </c>
-      <c r="P56" t="s">
+      <c r="Q56" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>-3.3149389346669902E-2</v>
       </c>
@@ -6909,19 +6941,19 @@
       <c r="E57">
         <v>0.7</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <v>996</v>
       </c>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E58">
         <v>1</v>
       </c>
-      <c r="P58" t="s">
+      <c r="Q58" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>0.250054010925023</v>
       </c>
@@ -6931,14 +6963,14 @@
       <c r="D59">
         <v>-3.5197283757326399</v>
       </c>
-      <c r="O59">
+      <c r="P59">
         <v>1746</v>
       </c>
-      <c r="P59" t="s">
+      <c r="Q59" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>-1.44059076725918</v>
       </c>
@@ -6948,14 +6980,14 @@
       <c r="D60">
         <v>-4.8807740743608301</v>
       </c>
-      <c r="O60">
+      <c r="P60">
         <v>1574</v>
       </c>
-      <c r="P60" t="s">
+      <c r="Q60" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>-1.21144890336943</v>
       </c>
@@ -6968,11 +7000,11 @@
       <c r="H61">
         <v>1</v>
       </c>
-      <c r="O61">
+      <c r="P61">
         <v>2108</v>
       </c>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>-1.2070813277479999</v>
       </c>
@@ -6988,11 +7020,11 @@
       <c r="H62">
         <v>0.7</v>
       </c>
-      <c r="O62">
+      <c r="P62">
         <v>1309</v>
       </c>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>-1.0012021396300801</v>
       </c>
@@ -7002,11 +7034,11 @@
       <c r="D63">
         <v>-5</v>
       </c>
-      <c r="O63">
+      <c r="P63">
         <v>994</v>
       </c>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>-4.4248727373665302</v>
       </c>
@@ -7016,14 +7048,14 @@
       <c r="D64">
         <v>-0.92802622567503801</v>
       </c>
-      <c r="O64">
+      <c r="P64">
         <v>1528</v>
       </c>
-      <c r="P64" t="s">
+      <c r="Q64" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>-1.0608132419307801</v>
       </c>
@@ -7036,14 +7068,14 @@
       <c r="L65" t="s">
         <v>681</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <v>1167</v>
       </c>
-      <c r="P65" t="s">
+      <c r="Q65" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>-1.1261289140861099</v>
       </c>
@@ -7056,14 +7088,14 @@
       <c r="F66">
         <v>1.1499999999999999</v>
       </c>
-      <c r="O66">
+      <c r="P66">
         <v>1002</v>
       </c>
-      <c r="P66" t="s">
+      <c r="Q66" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>-1.2035253749880399</v>
       </c>
@@ -7073,11 +7105,11 @@
       <c r="D67">
         <v>-4.83529833670908</v>
       </c>
-      <c r="O67">
+      <c r="P67">
         <v>1121</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>-1.44395477402174</v>
       </c>
@@ -7087,15 +7119,17 @@
       <c r="D68">
         <v>-4.59924882828237</v>
       </c>
-      <c r="O68">
+      <c r="P68">
         <v>1121</v>
       </c>
-      <c r="P68" t="s">
+      <c r="Q68" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O69" s="25"/>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>-1.2038</v>
       </c>
@@ -7105,11 +7139,14 @@
       <c r="D70">
         <v>-4.9325999999999999</v>
       </c>
-      <c r="P70" t="s">
+      <c r="L70" t="s">
+        <v>727</v>
+      </c>
+      <c r="Q70" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>-0.70223850678134803</v>
       </c>
@@ -7119,11 +7156,11 @@
       <c r="D71">
         <v>-4.9512972108205302</v>
       </c>
-      <c r="P71" t="s">
+      <c r="Q71" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E72">
         <v>1</v>
       </c>
@@ -7136,14 +7173,14 @@
       <c r="H72">
         <v>1</v>
       </c>
-      <c r="O72">
+      <c r="P72">
         <v>1147</v>
       </c>
-      <c r="P72" t="s">
+      <c r="Q72" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>-1.8904675242014499</v>
       </c>
@@ -7162,11 +7199,11 @@
       <c r="H73">
         <v>0.7</v>
       </c>
-      <c r="O73">
+      <c r="P73">
         <v>1165</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>4</v>
       </c>
@@ -7182,11 +7219,11 @@
       <c r="G74">
         <v>1.1499999999999999</v>
       </c>
-      <c r="O74">
+      <c r="P74">
         <v>1165</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>5</v>
       </c>
@@ -7199,17 +7236,17 @@
       <c r="D75">
         <v>-5</v>
       </c>
-      <c r="O75">
+      <c r="P75">
         <v>1110</v>
       </c>
-      <c r="P75" t="s">
+      <c r="Q75" t="s">
         <v>688</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="R75" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>6</v>
       </c>
@@ -7222,28 +7259,28 @@
       <c r="D76">
         <v>-5</v>
       </c>
-      <c r="O76">
+      <c r="P76">
         <v>1613</v>
       </c>
-      <c r="P76" t="s">
+      <c r="Q76" t="s">
         <v>716</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="R76" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
         <v>721</v>
       </c>
       <c r="E77">
         <v>0.7</v>
       </c>
-      <c r="Q77" t="s">
+      <c r="R77" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>7</v>
       </c>
@@ -7253,19 +7290,19 @@
       <c r="F78">
         <v>1</v>
       </c>
-      <c r="O78">
+      <c r="P78">
         <v>1101</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E79">
         <v>0.75</v>
       </c>
-      <c r="O79">
+      <c r="P79">
         <v>1152</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E80">
         <v>0.72499999999999998</v>
       </c>
@@ -7273,63 +7310,63 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H81">
         <v>0.9</v>
       </c>
-      <c r="O81">
+      <c r="P81">
         <v>1237</v>
       </c>
-      <c r="Q81" t="s">
+      <c r="R81" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P82" t="s">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q82" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="F83">
         <v>0.9</v>
       </c>
-      <c r="O83">
+      <c r="P83">
         <v>1311</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H84">
         <v>0.85</v>
       </c>
-      <c r="O84">
+      <c r="P84">
         <v>1255</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E85">
         <v>0.7</v>
       </c>
-      <c r="O85">
+      <c r="P85">
         <v>1318</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H86">
         <v>0.8</v>
       </c>
-      <c r="O86">
+      <c r="P86">
         <v>1337</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H87">
         <v>0.75</v>
       </c>
-      <c r="O87">
+      <c r="P87">
         <v>1368</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>18</v>
       </c>
@@ -7339,36 +7376,36 @@
       <c r="G88">
         <v>1.05</v>
       </c>
-      <c r="O88">
+      <c r="P88">
         <v>1463</v>
       </c>
-      <c r="Q88" t="s">
+      <c r="R88" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>19</v>
       </c>
-      <c r="O89">
+      <c r="P89">
         <v>2704</v>
       </c>
-      <c r="P89" t="s">
+      <c r="Q89" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>20</v>
       </c>
       <c r="E90">
         <v>0.9</v>
       </c>
-      <c r="O90">
+      <c r="P90">
         <v>1939</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>21</v>
       </c>
@@ -7382,56 +7419,135 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>22</v>
       </c>
       <c r="E92">
         <v>0.95</v>
       </c>
-      <c r="O92">
+      <c r="P92">
         <v>1439</v>
       </c>
-      <c r="Q92" t="s">
+      <c r="R92" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>23</v>
       </c>
       <c r="G93">
         <v>1.1499999999999999</v>
       </c>
-      <c r="O93">
+      <c r="P93">
         <v>1399</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>24</v>
       </c>
       <c r="E94">
         <v>1</v>
       </c>
-      <c r="O94">
+      <c r="P94">
         <v>1256</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>25</v>
+      </c>
       <c r="E95">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O95">
+      <c r="P95">
         <v>1052</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>26</v>
+      </c>
       <c r="E96">
         <v>1.05</v>
       </c>
-      <c r="O96">
+      <c r="P96">
         <v>1139</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L97" t="s">
+        <v>728</v>
+      </c>
+      <c r="P97">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O98" s="23" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>29</v>
+      </c>
+      <c r="O99" s="23" t="s">
+        <v>731</v>
+      </c>
+      <c r="P99">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>30</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="P100">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>31</v>
+      </c>
+      <c r="H101">
+        <v>0.7</v>
+      </c>
+      <c r="P101">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>32</v>
+      </c>
+      <c r="P102">
+        <v>2033</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>732</v>
+      </c>
+      <c r="R102" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>33</v>
+      </c>
+      <c r="E103">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q104" t="s">
+        <v>734</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E4589E-5D37-4E7C-98A1-86DBA36470F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B232DB4F-D7CA-450A-BE3E-76900A4B5605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="736">
   <si>
     <t>A</t>
   </si>
@@ -2337,6 +2337,9 @@
   </si>
   <si>
     <t>back to _v2</t>
+  </si>
+  <si>
+    <t>CHENG GPT COMMENTS FOR MISTAKES</t>
   </si>
 </sst>
 </file>
@@ -5835,7 +5838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:R104"/>
+  <dimension ref="A2:R105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="15" max="15" width="11.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -7525,7 +7528,7 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="P102">
         <v>2033</v>
@@ -7539,15 +7542,41 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E103">
         <v>0.8</v>
       </c>
+      <c r="Q103" t="s">
+        <v>734</v>
+      </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="Q104" t="s">
+      <c r="A104">
+        <v>2</v>
+      </c>
+      <c r="P104">
+        <v>1322</v>
+      </c>
+      <c r="Q104" s="23" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>33</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="P105">
+        <v>938</v>
+      </c>
+      <c r="Q105" s="23" t="s">
         <v>734</v>
+      </c>
+      <c r="R105" t="s">
+        <v>735</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B232DB4F-D7CA-450A-BE3E-76900A4B5605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAA99D8-5149-4706-8C07-ABF60BEAB030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0D" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="740">
   <si>
     <t>A</t>
   </si>
@@ -2340,6 +2340,18 @@
   </si>
   <si>
     <t>CHENG GPT COMMENTS FOR MISTAKES</t>
+  </si>
+  <si>
+    <t>introduced hydraulic diameter for Re</t>
+  </si>
+  <si>
+    <t>was almost the same with the Lc</t>
+  </si>
+  <si>
+    <t>change convection area to A_frt_solid</t>
+  </si>
+  <si>
+    <t>0D_v3 with NTU gas temperature</t>
   </si>
 </sst>
 </file>
@@ -5838,7 +5850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:R105"/>
+  <dimension ref="A2:R108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="15" max="15" width="11.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -7575,8 +7587,44 @@
       <c r="Q105" s="23" t="s">
         <v>734</v>
       </c>
-      <c r="R105" t="s">
+      <c r="R105" s="25" t="s">
         <v>735</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>34</v>
+      </c>
+      <c r="P106">
+        <v>938</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>736</v>
+      </c>
+      <c r="R106" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>35</v>
+      </c>
+      <c r="P107">
+        <v>925</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>2</v>
+      </c>
+      <c r="P108">
+        <v>943</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>739</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAA99D8-5149-4706-8C07-ABF60BEAB030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC066E0-449C-4BEF-A319-5636E50E16A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0D" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <author>tc={1195A4A6-AC02-43B0-9B61-6F9ADFAE84CE}</author>
   </authors>
   <commentList>
-    <comment ref="B39" authorId="0" shapeId="0" xr:uid="{2C9673A5-534D-4FC2-A792-912F01D1091C}">
+    <comment ref="C39" authorId="0" shapeId="0" xr:uid="{2C9673A5-534D-4FC2-A792-912F01D1091C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -52,7 +52,7 @@
     10^A</t>
       </text>
     </comment>
-    <comment ref="D40" authorId="1" shapeId="0" xr:uid="{1195A4A6-AC02-43B0-9B61-6F9ADFAE84CE}">
+    <comment ref="E40" authorId="1" shapeId="0" xr:uid="{1195A4A6-AC02-43B0-9B61-6F9ADFAE84CE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="745">
   <si>
     <t>A</t>
   </si>
@@ -2352,6 +2352,21 @@
   </si>
   <si>
     <t>0D_v3 with NTU gas temperature</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>_v1</t>
+  </si>
+  <si>
+    <t>_v2</t>
+  </si>
+  <si>
+    <t>_v3</t>
+  </si>
+  <si>
+    <t>updated the objective function</t>
   </si>
 </sst>
 </file>
@@ -5839,10 +5854,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B39" dT="2025-07-23T05:22:20.02" personId="{276BCB23-7094-4A82-96C4-28630CE0F82D}" id="{2C9673A5-534D-4FC2-A792-912F01D1091C}">
+  <threadedComment ref="C39" dT="2025-07-23T05:22:20.02" personId="{276BCB23-7094-4A82-96C4-28630CE0F82D}" id="{2C9673A5-534D-4FC2-A792-912F01D1091C}">
     <text>10^A</text>
   </threadedComment>
-  <threadedComment ref="D40" dT="2025-07-23T05:38:31.92" personId="{276BCB23-7094-4A82-96C4-28630CE0F82D}" id="{1195A4A6-AC02-43B0-9B61-6F9ADFAE84CE}">
+  <threadedComment ref="E40" dT="2025-07-23T05:38:31.92" personId="{276BCB23-7094-4A82-96C4-28630CE0F82D}" id="{1195A4A6-AC02-43B0-9B61-6F9ADFAE84CE}">
     <text>10^</text>
   </threadedComment>
 </ThreadedComments>
@@ -5850,1335 +5865,1340 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:R108"/>
+  <dimension ref="A2:S110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="15" max="15" width="11.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="46.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="37.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="23"/>
+    <col min="16" max="16" width="11.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B2" s="23" t="s">
+        <v>740</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="P2" s="24" t="s">
         <v>729</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="C3" s="3">
         <v>1.24017003587548E-3</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1.3974854403316901</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1.6350743193202899</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.64</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1.2</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.8</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>27</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.4</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>499.47699999999998</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="C4" s="3">
         <v>9.7997522561352798E-4</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>1.4059359592048799</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>2.4349761382305499</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.66</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>528.26599999999996</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="C5" s="3">
         <v>1.00002800832326E-4</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>1.3282580903963901</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>16.077659504854701</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.64</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>473.34</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="C6" s="3">
         <v>3.0774692673678297E-5</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>1.4802745324312101</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>19.9517218966303</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="C7" s="3">
         <v>3.1142977666936498E-3</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>1.2623131975854101</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>2.7362624606074699E-3</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>604.08600000000001</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="C8" s="3">
         <v>2.7615114875290401E-3</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>1.2412550503592701</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1E-4</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.7</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="C9" s="3">
         <v>3.10648772630206E-3</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>1.2756696149129301</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>1E-4</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.63</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
+      <c r="C10" s="3">
         <v>8.6454867421348301E-5</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>1.64491004515391</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>12.0217117639568</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1.2</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>500</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="3">
+      <c r="C11" s="3">
         <v>3.7125021077593002E-4</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>1.3930651456031</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>8.3576305806791193</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.64</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>480</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" s="2">
+      <c r="C12" s="2">
         <v>2.6620817681730501E-5</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>1.4175004404023599</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>19.9997174906579</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>20</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>672</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>24</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>28</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>25612</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" s="2">
+      <c r="C15" s="2">
         <v>3.3035945380220997E-5</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>1.43770025274668</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>20</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>23</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>27</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>469</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>53</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
-      <c r="B17" s="2">
+      <c r="C17" s="2">
         <v>1.03191509408719E-5</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>1.4319313285872399</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>25.984272299692599</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>465</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.84</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>850</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.74</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>573</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.64</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>607</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23">
+      <c r="C23">
         <v>5.6058995390906102E-4</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>1.6106589591624401</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>9.910468968988089E-4</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.7</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>502</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
-      <c r="B24" s="2">
+      <c r="C24" s="2">
         <v>1.0024299213338499E-5</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>2.9323882617891202</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>1E-4</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>4.4000000000000004</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>1641</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
-      <c r="B25" s="2">
+      <c r="C25" s="2">
         <v>2.0887059774144901E-5</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>2.5052539496126101</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>1.8829968719792201E-2</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>1</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>1071</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>1</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>1892</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>2.1591196456141501E-4</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>1.7189995203791599</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>1.20209817420813</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.9</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>1354</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>3.0880065502844102E-4</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>1.7074022707650001</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>3.7186641941726502E-4</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.7</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>502</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>4.60311808037377E-4</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>1.66187478217667</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>1.3738648256894E-4</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>502</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>5.86247778425387E-4</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>1.6630696101604501</v>
       </c>
-      <c r="D31" s="2">
+      <c r="E31" s="2">
         <v>9.39537377217747E-5</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>0.6</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>522</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
-      <c r="B33">
+      <c r="C33">
         <v>2.8727643386340098E-4</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>1.5904189645704501</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>1.0263197679569199E-4</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>0</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>563</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>3.0928717643758302E-4</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>1.5965904733758101</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>2.4080124471630401E-4</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>1</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>461</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>2.4681495887314401E-4</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>1.6624759537039799</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>1.7341179006468701E-4</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>72</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.64</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
         <v>27</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>586</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.75</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N38">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O38">
         <v>0</v>
       </c>
-      <c r="Q38" s="20" t="s">
+      <c r="R38" s="20" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>35</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>-1.5880535011177801</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>0.65091494933399197</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>3.6666969736259901E-2</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>1</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>0.7</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>7.8E-2</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>1140</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>36</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>-1.62557011221157</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>0.64353970719628895</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>-5</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>3</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>975</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="R40" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>37</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>1</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>1140</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="R41" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>38</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>-1.62633085814944</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>0.64384726379398405</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>-4.2152141852378398</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>1.2</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>3</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>975</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>39</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>-1.62557011221157</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>0.64353970719628895</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>-5</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>1</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>3</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>1</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>975</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>40</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>-0.21738961927643199</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>0.224136849475497</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>-4.38627582837346</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>1</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>1496</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>41</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>-0.120453173998853</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>8.2527627411642504E-2</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>-5</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>0.7</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>1027</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>42</v>
       </c>
-      <c r="B46">
+      <c r="C46">
         <v>-6.3694404355623402E-2</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>6.9338798965457998E-2</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>-3.66322327238499</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>2</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>999</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>43</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>-5.6187532274797197E-2</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>6.7192097637876202E-2</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>-3.85853069192695</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>999</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="R47" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B48">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C48">
         <v>-0.59913658322029595</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>0.23267951536977999</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>-4.54729113095385</v>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <v>1050</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="R48" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B49">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C49">
         <v>-3.0218416280894E-2</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>5.6553370855678999E-2</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>-5</v>
       </c>
-      <c r="L49" t="s">
+      <c r="M49" t="s">
         <v>678</v>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <v>996</v>
       </c>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B50">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C50">
         <v>2.32366143478863</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>5.2381129172708499E-2</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>1.15176621671389</v>
       </c>
-      <c r="L50" t="s">
+      <c r="M50" t="s">
         <v>679</v>
       </c>
-      <c r="P50">
+      <c r="Q50">
         <v>1195</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="R50" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B51">
+    <row r="51" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C51">
         <v>-0.11531413827813</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>0.110780162848843</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>-5</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L51" t="s">
+      <c r="M51" t="s">
         <v>681</v>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>1049</v>
       </c>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B52">
+    <row r="52" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C52">
         <v>-5.9825795140801101E-2</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>8.3298389397967201E-2</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>-4.7822766948941098</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <v>1016</v>
       </c>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B53">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C53">
         <v>0.163215104178386</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>0.110019492778361</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>-5</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>1</v>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <v>1882</v>
       </c>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B54">
+    <row r="54" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C54">
         <v>0.16620523432742201</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>0.10949611407786</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>-1.95188474207697</v>
       </c>
-      <c r="P54">
+      <c r="Q54">
         <v>1880</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="R54" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B55">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C55">
         <v>0.113337590003834</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>0.113912815280584</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>-3.17711423761659</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>1</v>
       </c>
-      <c r="P55">
+      <c r="Q55">
         <v>1692</v>
       </c>
     </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B56">
+    <row r="56" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C56">
         <v>0.115547627813837</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>0.113073002583607</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>-4.5277566109866303</v>
       </c>
-      <c r="P56">
+      <c r="Q56">
         <v>1692</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="R56" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B57">
+    <row r="57" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C57">
         <v>-3.3149389346669902E-2</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>5.74856315526577E-2</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>-5</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>0.7</v>
       </c>
-      <c r="P57">
+      <c r="Q57">
         <v>996</v>
       </c>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="E58">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="F58">
         <v>1</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="R58" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B59">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C59">
         <v>0.250054010925023</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>9.0017378931107103E-2</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>-3.5197283757326399</v>
       </c>
-      <c r="P59">
+      <c r="Q59">
         <v>1746</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="R59" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B60">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C60">
         <v>-1.44059076725918</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>0.67522154899549303</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>-4.8807740743608301</v>
       </c>
-      <c r="P60">
+      <c r="Q60">
         <v>1574</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="R60" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B61">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C61">
         <v>-1.21144890336943</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>0.594262978875436</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>-5</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>1</v>
       </c>
-      <c r="P61">
+      <c r="Q61">
         <v>2108</v>
       </c>
     </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B62">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C62">
         <v>-1.2070813277479999</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>0.49223109727618702</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>-5</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>0.7</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>0.7</v>
       </c>
-      <c r="P62">
+      <c r="Q62">
         <v>1309</v>
       </c>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B63">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C63">
         <v>-1.0012021396300801</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>0.40143186621960603</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>-5</v>
       </c>
-      <c r="P63">
+      <c r="Q63">
         <v>994</v>
       </c>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B64">
+    <row r="64" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C64">
         <v>-4.4248727373665302</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>2.0054297178263898</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>-0.92802622567503801</v>
       </c>
-      <c r="P64">
+      <c r="Q64">
         <v>1528</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="R64" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B65">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C65">
         <v>-1.0608132419307801</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>0.415984490245218</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>-4.9695269901766101</v>
       </c>
-      <c r="L65" t="s">
+      <c r="M65" t="s">
         <v>681</v>
       </c>
-      <c r="P65">
+      <c r="Q65">
         <v>1167</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="R65" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B66">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C66">
         <v>-1.1261289140861099</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>0.47186731215250699</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>-4.5038498068435002</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>1.1499999999999999</v>
       </c>
-      <c r="P66">
+      <c r="Q66">
         <v>1002</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="R66" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B67">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C67">
         <v>-1.2035253749880399</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>0.49275278422355101</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>-4.83529833670908</v>
       </c>
-      <c r="P67">
+      <c r="Q67">
         <v>1121</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B68">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C68">
         <v>-1.44395477402174</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>0.49278508137217503</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>-4.59924882828237</v>
       </c>
-      <c r="P68">
+      <c r="Q68">
         <v>1121</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R68" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="O69" s="25"/>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B70">
+    <row r="69" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="25"/>
+      <c r="P69" s="25"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B70" s="23" t="s">
+        <v>742</v>
+      </c>
+      <c r="C70">
         <v>-1.2038</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>0.4929</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>-4.9325999999999999</v>
       </c>
-      <c r="L70" t="s">
+      <c r="M70" t="s">
         <v>727</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="R70" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B71">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C71">
         <v>-0.70223850678134803</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>0.25645673662077101</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>-4.9512972108205302</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="R71" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E72">
-        <v>1</v>
-      </c>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F72">
         <v>1</v>
       </c>
@@ -7188,443 +7208,479 @@
       <c r="H72">
         <v>1</v>
       </c>
-      <c r="P72">
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="Q72">
         <v>1147</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="R72" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B73">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C73">
         <v>-1.8904675242014499</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>0.78604681017162004</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>-4.8087781051542704</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>1.1499999999999999</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>1</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>0.7</v>
       </c>
-      <c r="P73">
+      <c r="Q73">
         <v>1165</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>4</v>
       </c>
-      <c r="B74">
+      <c r="C74">
         <v>-1.8904675242014499</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>0.78604681017162004</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>-4.8087781051542704</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>1.1499999999999999</v>
       </c>
-      <c r="P74">
+      <c r="Q74">
         <v>1165</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>5</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>-2.92555847278929</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>1.1553271728060299</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>-5</v>
       </c>
-      <c r="P75">
+      <c r="Q75">
         <v>1110</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="R75" t="s">
         <v>688</v>
       </c>
-      <c r="R75" t="s">
+      <c r="S75" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>6</v>
       </c>
-      <c r="B76" s="23">
+      <c r="C76" s="23">
         <v>-4.2861727192109598</v>
       </c>
-      <c r="C76">
+      <c r="D76">
         <v>1.98660254327817</v>
       </c>
-      <c r="D76">
+      <c r="E76">
         <v>-5</v>
       </c>
-      <c r="P76">
+      <c r="Q76">
         <v>1613</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="R76" t="s">
         <v>716</v>
       </c>
-      <c r="R76" t="s">
+      <c r="S76" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
         <v>721</v>
       </c>
-      <c r="E77">
+      <c r="B77" s="22"/>
+      <c r="F77">
         <v>0.7</v>
       </c>
-      <c r="R77" t="s">
+      <c r="S77" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>7</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>0.8</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>1</v>
       </c>
-      <c r="P78">
+      <c r="Q78">
         <v>1101</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E79">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F79">
         <v>0.75</v>
       </c>
-      <c r="P79">
+      <c r="Q79">
         <v>1152</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E80">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F80">
         <v>0.72499999999999998</v>
       </c>
-      <c r="G80">
+      <c r="H80">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H81">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I81">
         <v>0.9</v>
       </c>
-      <c r="P81">
+      <c r="Q81">
         <v>1237</v>
       </c>
-      <c r="R81" t="s">
+      <c r="S81" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="Q82" t="s">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R82" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="F83">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G83">
         <v>0.9</v>
       </c>
-      <c r="P83">
+      <c r="Q83">
         <v>1311</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H84">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I84">
         <v>0.85</v>
       </c>
-      <c r="P84">
+      <c r="Q84">
         <v>1255</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E85">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F85">
         <v>0.7</v>
       </c>
-      <c r="P85">
+      <c r="Q85">
         <v>1318</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H86">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I86">
         <v>0.8</v>
       </c>
-      <c r="P86">
+      <c r="Q86">
         <v>1337</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H87">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I87">
         <v>0.75</v>
       </c>
-      <c r="P87">
+      <c r="Q87">
         <v>1368</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>18</v>
       </c>
-      <c r="F88">
+      <c r="G88">
         <v>0.85</v>
       </c>
-      <c r="G88">
+      <c r="H88">
         <v>1.05</v>
       </c>
-      <c r="P88">
+      <c r="Q88">
         <v>1463</v>
       </c>
-      <c r="R88" t="s">
+      <c r="S88" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>19</v>
       </c>
-      <c r="P89">
+      <c r="Q89">
         <v>2704</v>
       </c>
-      <c r="Q89" t="s">
+      <c r="R89" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>20</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>0.9</v>
       </c>
-      <c r="P90">
+      <c r="Q90">
         <v>1939</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>21</v>
       </c>
-      <c r="F91">
+      <c r="G91">
         <v>1</v>
       </c>
-      <c r="G91">
+      <c r="H91">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H91">
+      <c r="I91">
         <v>0.8</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>22</v>
       </c>
-      <c r="E92">
+      <c r="F92">
         <v>0.95</v>
       </c>
-      <c r="P92">
+      <c r="Q92">
         <v>1439</v>
       </c>
-      <c r="R92" t="s">
+      <c r="S92" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>23</v>
       </c>
-      <c r="G93">
+      <c r="H93">
         <v>1.1499999999999999</v>
       </c>
-      <c r="P93">
+      <c r="Q93">
         <v>1399</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>24</v>
       </c>
-      <c r="E94">
+      <c r="F94">
         <v>1</v>
       </c>
-      <c r="P94">
+      <c r="Q94">
         <v>1256</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>25</v>
       </c>
-      <c r="E95">
+      <c r="F95">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P95">
+      <c r="Q95">
         <v>1052</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>26</v>
       </c>
-      <c r="E96">
+      <c r="F96">
         <v>1.05</v>
       </c>
-      <c r="P96">
+      <c r="Q96">
         <v>1139</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="L97" t="s">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M97" t="s">
         <v>728</v>
       </c>
-      <c r="P97">
+      <c r="Q97">
         <v>872</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="O98" s="23" t="s">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P98" s="23" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>29</v>
       </c>
-      <c r="O99" s="23" t="s">
+      <c r="P99" s="23" t="s">
         <v>731</v>
       </c>
-      <c r="P99">
+      <c r="Q99">
         <v>1216</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>30</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>1</v>
       </c>
-      <c r="P100">
+      <c r="Q100">
         <v>896</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>31</v>
       </c>
-      <c r="H101">
+      <c r="I101">
         <v>0.7</v>
       </c>
-      <c r="P101">
+      <c r="Q101">
         <v>938</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1</v>
       </c>
-      <c r="P102">
+      <c r="B102" s="23" t="s">
+        <v>741</v>
+      </c>
+      <c r="Q102">
         <v>2033</v>
       </c>
-      <c r="Q102" t="s">
+      <c r="R102" t="s">
         <v>732</v>
       </c>
-      <c r="R102" t="s">
+      <c r="S102" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>32</v>
       </c>
-      <c r="E103">
+      <c r="B103" s="23" t="s">
+        <v>742</v>
+      </c>
+      <c r="F103">
         <v>0.8</v>
       </c>
-      <c r="Q103" t="s">
+      <c r="R103" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2</v>
       </c>
-      <c r="P104">
+      <c r="B104" s="23" t="s">
+        <v>741</v>
+      </c>
+      <c r="Q104">
         <v>1322</v>
       </c>
-      <c r="Q104" s="23" t="s">
+      <c r="R104" s="23" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>33</v>
       </c>
-      <c r="E105">
+      <c r="B105" s="23" t="s">
+        <v>742</v>
+      </c>
+      <c r="F105">
         <v>1</v>
       </c>
-      <c r="P105">
+      <c r="Q105">
         <v>938</v>
       </c>
-      <c r="Q105" s="23" t="s">
+      <c r="R105" s="23" t="s">
         <v>734</v>
       </c>
-      <c r="R105" s="25" t="s">
+      <c r="S105" s="25" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>34</v>
       </c>
-      <c r="P106">
+      <c r="B106" s="23" t="s">
+        <v>742</v>
+      </c>
+      <c r="Q106">
         <v>938</v>
       </c>
-      <c r="Q106" t="s">
+      <c r="R106" t="s">
         <v>736</v>
       </c>
-      <c r="R106" t="s">
+      <c r="S106" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>35</v>
       </c>
-      <c r="P107">
+      <c r="B107" s="23" t="s">
+        <v>742</v>
+      </c>
+      <c r="Q107">
         <v>925</v>
       </c>
-      <c r="Q107" t="s">
+      <c r="R107" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2</v>
       </c>
-      <c r="P108">
+      <c r="B108" s="23" t="s">
+        <v>743</v>
+      </c>
+      <c r="Q108">
         <v>943</v>
       </c>
-      <c r="Q108" t="s">
+      <c r="R108" t="s">
         <v>739</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>4</v>
+      </c>
+      <c r="Q110">
+        <v>0.06</v>
+      </c>
+      <c r="R110" s="23" t="s">
+        <v>744</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC066E0-449C-4BEF-A319-5636E50E16A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F8773D-E160-4CBE-9BF5-BC99F7C3FA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="746">
   <si>
     <t>A</t>
   </si>
@@ -2367,6 +2367,9 @@
   </si>
   <si>
     <t>updated the objective function</t>
+  </si>
+  <si>
+    <t>Tfilm for Tgas and weighted Taveraged for the solid</t>
   </si>
 </sst>
 </file>
@@ -5865,7 +5868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:S110"/>
+  <dimension ref="A2:S111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" style="23"/>
@@ -7681,6 +7684,17 @@
       </c>
       <c r="R110" s="23" t="s">
         <v>744</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>5</v>
+      </c>
+      <c r="Q111">
+        <v>0.05</v>
+      </c>
+      <c r="R111" t="s">
+        <v>745</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F8773D-E160-4CBE-9BF5-BC99F7C3FA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B23D3CE-AE50-4D97-AFC6-605C5039AEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="750">
   <si>
     <t>A</t>
   </si>
@@ -2354,9 +2354,6 @@
     <t>0D_v3 with NTU gas temperature</t>
   </si>
   <si>
-    <t>mode</t>
-  </si>
-  <si>
     <t>_v1</t>
   </si>
   <si>
@@ -2366,10 +2363,25 @@
     <t>_v3</t>
   </si>
   <si>
+    <t>_v4</t>
+  </si>
+  <si>
     <t>updated the objective function</t>
   </si>
   <si>
     <t>Tfilm for Tgas and weighted Taveraged for the solid</t>
+  </si>
+  <si>
+    <t>include cooling, and focusing on the 0D parameters</t>
+  </si>
+  <si>
+    <t>solid profile not bad, but gas and time not good</t>
+  </si>
+  <si>
+    <t>similar plotting style with v4, included cooling output</t>
+  </si>
+  <si>
+    <t>model</t>
   </si>
 </sst>
 </file>
@@ -5868,18 +5880,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:S111"/>
+  <dimension ref="A2:S114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.140625" style="23"/>
+    <col min="1" max="1" width="9.140625" style="23"/>
     <col min="16" max="16" width="11.42578125" style="23" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
-        <v>740</v>
+      <c r="A2" s="23" t="s">
+        <v>749</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
@@ -5934,7 +5946,7 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" s="3">
@@ -5981,7 +5993,7 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" s="3">
@@ -6004,7 +6016,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" s="3">
@@ -6030,7 +6042,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" s="3">
@@ -6050,7 +6062,7 @@
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="B7">
         <v>5</v>
       </c>
       <c r="C7" s="3">
@@ -6073,7 +6085,7 @@
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" s="3">
@@ -6093,7 +6105,7 @@
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" s="3">
@@ -6113,7 +6125,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" s="3">
@@ -6136,7 +6148,7 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="3">
@@ -6159,7 +6171,7 @@
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="B12">
         <v>9</v>
       </c>
       <c r="C12" s="2">
@@ -6182,7 +6194,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="B13">
         <v>10</v>
       </c>
       <c r="K13" t="s">
@@ -6193,7 +6205,7 @@
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="B14">
         <v>11</v>
       </c>
       <c r="L14" t="s">
@@ -6207,7 +6219,7 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="B15">
         <v>12</v>
       </c>
       <c r="C15" s="2">
@@ -6233,7 +6245,7 @@
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="B16">
         <v>13</v>
       </c>
       <c r="Q16" t="s">
@@ -6243,8 +6255,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B17">
         <v>14</v>
       </c>
       <c r="C17" s="2">
@@ -6263,16 +6275,16 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B18">
         <v>15</v>
       </c>
       <c r="R18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B19">
         <v>16</v>
       </c>
       <c r="F19">
@@ -6285,16 +6297,16 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B20">
         <v>17</v>
       </c>
       <c r="R20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B21">
         <v>18</v>
       </c>
       <c r="F21">
@@ -6310,8 +6322,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B22">
         <v>19</v>
       </c>
       <c r="F22">
@@ -6324,8 +6336,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B23">
         <v>20</v>
       </c>
       <c r="C23">
@@ -6347,8 +6359,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B24">
         <v>21</v>
       </c>
       <c r="C24" s="2">
@@ -6370,8 +6382,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B25">
         <v>22</v>
       </c>
       <c r="C25" s="2">
@@ -6393,8 +6405,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B26">
         <v>23</v>
       </c>
       <c r="M26">
@@ -6407,8 +6419,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B27">
         <v>24</v>
       </c>
       <c r="C27">
@@ -6427,8 +6439,8 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B28">
         <v>25</v>
       </c>
       <c r="C28">
@@ -6444,8 +6456,8 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B29">
         <v>26</v>
       </c>
       <c r="F29">
@@ -6458,8 +6470,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B30">
         <v>27</v>
       </c>
       <c r="C30">
@@ -6478,8 +6490,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B31">
         <v>28</v>
       </c>
       <c r="C31">
@@ -6498,8 +6510,8 @@
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B32">
         <v>29</v>
       </c>
       <c r="Q32">
@@ -6509,8 +6521,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B33">
         <v>30</v>
       </c>
       <c r="C33">
@@ -6529,8 +6541,8 @@
         <v>563</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B34">
         <v>31</v>
       </c>
       <c r="C34">
@@ -6552,8 +6564,8 @@
         <v>461</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B35">
         <v>32</v>
       </c>
       <c r="C35">
@@ -6572,8 +6584,8 @@
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B36">
         <v>33</v>
       </c>
       <c r="F36">
@@ -6586,8 +6598,8 @@
         <v>586</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B37">
         <v>34</v>
       </c>
       <c r="F37">
@@ -6597,7 +6609,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="O38">
         <v>0</v>
       </c>
@@ -6605,8 +6617,8 @@
         <v>657</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B39">
         <v>35</v>
       </c>
       <c r="C39">
@@ -6634,8 +6646,8 @@
         <v>662</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B40">
         <v>36</v>
       </c>
       <c r="C40">
@@ -6657,8 +6669,8 @@
         <v>666</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B41">
         <v>37</v>
       </c>
       <c r="M41">
@@ -6671,8 +6683,8 @@
         <v>668</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B42">
         <v>38</v>
       </c>
       <c r="C42">
@@ -6697,8 +6709,8 @@
         <v>671</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B43">
         <v>39</v>
       </c>
       <c r="C43">
@@ -6723,8 +6735,8 @@
         <v>975</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B44">
         <v>40</v>
       </c>
       <c r="C44">
@@ -6746,8 +6758,8 @@
         <v>673</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B45">
         <v>41</v>
       </c>
       <c r="C45">
@@ -6766,8 +6778,8 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B46">
         <v>42</v>
       </c>
       <c r="C46">
@@ -6786,8 +6798,8 @@
         <v>999</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B47">
         <v>43</v>
       </c>
       <c r="C47">
@@ -6806,7 +6818,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C48">
         <v>-0.59913658322029595</v>
       </c>
@@ -7164,12 +7176,12 @@
       </c>
     </row>
     <row r="69" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="25"/>
+      <c r="A69" s="25"/>
       <c r="P69" s="25"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="23" t="s">
-        <v>742</v>
+      <c r="A70" s="23" t="s">
+        <v>741</v>
       </c>
       <c r="C70">
         <v>-1.2038</v>
@@ -7245,7 +7257,7 @@
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74">
+      <c r="B74">
         <v>4</v>
       </c>
       <c r="C74">
@@ -7265,7 +7277,7 @@
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A75">
+      <c r="B75">
         <v>5</v>
       </c>
       <c r="C75">
@@ -7288,7 +7300,7 @@
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A76">
+      <c r="B76">
         <v>6</v>
       </c>
       <c r="C76" s="23">
@@ -7311,10 +7323,10 @@
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A77" s="22" t="s">
+      <c r="A77" s="22"/>
+      <c r="B77" s="22" t="s">
         <v>721</v>
       </c>
-      <c r="B77" s="22"/>
       <c r="F77">
         <v>0.7</v>
       </c>
@@ -7323,7 +7335,7 @@
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78">
+      <c r="B78">
         <v>7</v>
       </c>
       <c r="F78">
@@ -7352,7 +7364,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:19" x14ac:dyDescent="0.25">
       <c r="I81">
         <v>0.9</v>
       </c>
@@ -7363,12 +7375,12 @@
         <v>722</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:19" x14ac:dyDescent="0.25">
       <c r="R82" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:19" x14ac:dyDescent="0.25">
       <c r="G83">
         <v>0.9</v>
       </c>
@@ -7376,7 +7388,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:19" x14ac:dyDescent="0.25">
       <c r="I84">
         <v>0.85</v>
       </c>
@@ -7384,7 +7396,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:19" x14ac:dyDescent="0.25">
       <c r="F85">
         <v>0.7</v>
       </c>
@@ -7392,7 +7404,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:19" x14ac:dyDescent="0.25">
       <c r="I86">
         <v>0.8</v>
       </c>
@@ -7400,7 +7412,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:19" x14ac:dyDescent="0.25">
       <c r="I87">
         <v>0.75</v>
       </c>
@@ -7408,8 +7420,8 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A88">
+    <row r="88" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B88">
         <v>18</v>
       </c>
       <c r="G88">
@@ -7425,8 +7437,8 @@
         <v>724</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A89">
+    <row r="89" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B89">
         <v>19</v>
       </c>
       <c r="Q89">
@@ -7436,8 +7448,8 @@
         <v>725</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A90">
+    <row r="90" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B90">
         <v>20</v>
       </c>
       <c r="F90">
@@ -7447,8 +7459,8 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91">
+    <row r="91" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B91">
         <v>21</v>
       </c>
       <c r="G91">
@@ -7461,8 +7473,8 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A92">
+    <row r="92" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B92">
         <v>22</v>
       </c>
       <c r="F92">
@@ -7475,8 +7487,8 @@
         <v>726</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A93">
+    <row r="93" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B93">
         <v>23</v>
       </c>
       <c r="H93">
@@ -7486,8 +7498,8 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A94">
+    <row r="94" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B94">
         <v>24</v>
       </c>
       <c r="F94">
@@ -7497,8 +7509,8 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A95">
+    <row r="95" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B95">
         <v>25</v>
       </c>
       <c r="F95">
@@ -7508,8 +7520,8 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A96">
+    <row r="96" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B96">
         <v>26</v>
       </c>
       <c r="F96">
@@ -7533,7 +7545,7 @@
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A99">
+      <c r="B99">
         <v>29</v>
       </c>
       <c r="P99" s="23" t="s">
@@ -7544,7 +7556,7 @@
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100">
+      <c r="B100">
         <v>30</v>
       </c>
       <c r="F100">
@@ -7555,7 +7567,7 @@
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A101">
+      <c r="B101">
         <v>31</v>
       </c>
       <c r="I101">
@@ -7566,11 +7578,11 @@
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A102">
+      <c r="A102" s="23" t="s">
+        <v>740</v>
+      </c>
+      <c r="B102">
         <v>1</v>
-      </c>
-      <c r="B102" s="23" t="s">
-        <v>741</v>
       </c>
       <c r="Q102">
         <v>2033</v>
@@ -7583,11 +7595,11 @@
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A103">
+      <c r="A103" s="23" t="s">
+        <v>741</v>
+      </c>
+      <c r="B103">
         <v>32</v>
-      </c>
-      <c r="B103" s="23" t="s">
-        <v>742</v>
       </c>
       <c r="F103">
         <v>0.8</v>
@@ -7597,11 +7609,11 @@
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A104">
+      <c r="A104" s="23" t="s">
+        <v>740</v>
+      </c>
+      <c r="B104">
         <v>2</v>
-      </c>
-      <c r="B104" s="23" t="s">
-        <v>741</v>
       </c>
       <c r="Q104">
         <v>1322</v>
@@ -7611,11 +7623,11 @@
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A105">
+      <c r="A105" s="23" t="s">
+        <v>741</v>
+      </c>
+      <c r="B105">
         <v>33</v>
-      </c>
-      <c r="B105" s="23" t="s">
-        <v>742</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -7631,11 +7643,11 @@
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A106">
+      <c r="A106" s="23" t="s">
+        <v>741</v>
+      </c>
+      <c r="B106">
         <v>34</v>
-      </c>
-      <c r="B106" s="23" t="s">
-        <v>742</v>
       </c>
       <c r="Q106">
         <v>938</v>
@@ -7648,11 +7660,11 @@
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A107">
+      <c r="A107" s="23" t="s">
+        <v>741</v>
+      </c>
+      <c r="B107">
         <v>35</v>
-      </c>
-      <c r="B107" s="23" t="s">
-        <v>742</v>
       </c>
       <c r="Q107">
         <v>925</v>
@@ -7662,11 +7674,11 @@
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A108">
+      <c r="A108" s="23" t="s">
+        <v>742</v>
+      </c>
+      <c r="B108">
         <v>2</v>
-      </c>
-      <c r="B108" s="23" t="s">
-        <v>743</v>
       </c>
       <c r="Q108">
         <v>943</v>
@@ -7676,7 +7688,7 @@
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A110">
+      <c r="B110">
         <v>4</v>
       </c>
       <c r="Q110">
@@ -7687,7 +7699,7 @@
       </c>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A111">
+      <c r="B111">
         <v>5</v>
       </c>
       <c r="Q111">
@@ -7695,6 +7707,54 @@
       </c>
       <c r="R111" t="s">
         <v>745</v>
+      </c>
+      <c r="S111" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A112" s="23" t="s">
+        <v>743</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="Q112">
+        <v>0.04</v>
+      </c>
+      <c r="R112" t="s">
+        <v>746</v>
+      </c>
+      <c r="S112" s="23" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A113" s="23" t="s">
+        <v>742</v>
+      </c>
+      <c r="B113">
+        <v>9</v>
+      </c>
+      <c r="C113">
+        <v>-3.1486202185996501</v>
+      </c>
+      <c r="D113">
+        <v>1.26914376889979</v>
+      </c>
+      <c r="E113">
+        <v>-4.8520029130770999</v>
+      </c>
+      <c r="Q113">
+        <v>5.5E-2</v>
+      </c>
+      <c r="R113" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A114" s="23" t="s">
+        <v>743</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B23D3CE-AE50-4D97-AFC6-605C5039AEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B5C9CF-77D3-496F-AD82-76D6606927CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="752">
   <si>
     <t>A</t>
   </si>
@@ -2382,6 +2382,12 @@
   </si>
   <si>
     <t>model</t>
+  </si>
+  <si>
+    <t>3 stages optimi\tion (heating, cooling, heating)</t>
+  </si>
+  <si>
+    <t>solid scatter plot, good but gas not</t>
   </si>
 </sst>
 </file>
@@ -5880,7 +5886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:S114"/>
+  <dimension ref="A2:S116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="23"/>
@@ -7729,7 +7735,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="23" t="s">
         <v>742</v>
       </c>
@@ -7752,9 +7758,34 @@
         <v>748</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="23" t="s">
         <v>743</v>
+      </c>
+      <c r="B114">
+        <v>3</v>
+      </c>
+      <c r="Q114">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B115">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B116">
+        <v>6</v>
+      </c>
+      <c r="Q116">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="R116" t="s">
+        <v>750</v>
+      </c>
+      <c r="S116" t="s">
+        <v>751</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B5C9CF-77D3-496F-AD82-76D6606927CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{F9B05BD3-6F93-43EB-89E4-4E1E10B2B816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Optical" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -87,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="755">
   <si>
     <t>A</t>
   </si>
@@ -2388,6 +2389,15 @@
   </si>
   <si>
     <t>solid scatter plot, good but gas not</t>
+  </si>
+  <si>
+    <t>1D_v3</t>
+  </si>
+  <si>
+    <t>1D_v6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tested </t>
   </si>
 </sst>
 </file>
@@ -2509,7 +2519,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2565,11 +2575,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5886,17 +5891,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:S116"/>
+  <dimension ref="A2:S123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="23"/>
-    <col min="16" max="16" width="11.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" t="s">
         <v>749</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5938,7 +5942,7 @@
       <c r="O2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="1" t="s">
         <v>729</v>
       </c>
       <c r="Q2" s="1" t="s">
@@ -7181,12 +7185,9 @@
         <v>695</v>
       </c>
     </row>
-    <row r="69" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="25"/>
-      <c r="P69" s="25"/>
-    </row>
+    <row r="69" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A70" s="23" t="s">
+      <c r="A70" t="s">
         <v>741</v>
       </c>
       <c r="C70">
@@ -7309,7 +7310,7 @@
       <c r="B76">
         <v>6</v>
       </c>
-      <c r="C76" s="23">
+      <c r="C76">
         <v>-4.2861727192109598</v>
       </c>
       <c r="D76">
@@ -7546,7 +7547,7 @@
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P98" s="23" t="s">
+      <c r="P98" t="s">
         <v>730</v>
       </c>
     </row>
@@ -7554,7 +7555,7 @@
       <c r="B99">
         <v>29</v>
       </c>
-      <c r="P99" s="23" t="s">
+      <c r="P99" t="s">
         <v>731</v>
       </c>
       <c r="Q99">
@@ -7584,7 +7585,7 @@
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A102" s="23" t="s">
+      <c r="A102" t="s">
         <v>740</v>
       </c>
       <c r="B102">
@@ -7601,7 +7602,7 @@
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A103" s="23" t="s">
+      <c r="A103" t="s">
         <v>741</v>
       </c>
       <c r="B103">
@@ -7615,7 +7616,7 @@
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A104" s="23" t="s">
+      <c r="A104" t="s">
         <v>740</v>
       </c>
       <c r="B104">
@@ -7624,12 +7625,12 @@
       <c r="Q104">
         <v>1322</v>
       </c>
-      <c r="R104" s="23" t="s">
+      <c r="R104" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A105" s="23" t="s">
+      <c r="A105" t="s">
         <v>741</v>
       </c>
       <c r="B105">
@@ -7641,15 +7642,15 @@
       <c r="Q105">
         <v>938</v>
       </c>
-      <c r="R105" s="23" t="s">
+      <c r="R105" t="s">
         <v>734</v>
       </c>
-      <c r="S105" s="25" t="s">
+      <c r="S105" s="11" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A106" s="23" t="s">
+      <c r="A106" t="s">
         <v>741</v>
       </c>
       <c r="B106">
@@ -7666,7 +7667,7 @@
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A107" s="23" t="s">
+      <c r="A107" t="s">
         <v>741</v>
       </c>
       <c r="B107">
@@ -7680,7 +7681,7 @@
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A108" s="23" t="s">
+      <c r="A108" t="s">
         <v>742</v>
       </c>
       <c r="B108">
@@ -7700,7 +7701,7 @@
       <c r="Q110">
         <v>0.06</v>
       </c>
-      <c r="R110" s="23" t="s">
+      <c r="R110" t="s">
         <v>744</v>
       </c>
     </row>
@@ -7719,7 +7720,7 @@
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A112" s="23" t="s">
+      <c r="A112" t="s">
         <v>743</v>
       </c>
       <c r="B112">
@@ -7731,12 +7732,12 @@
       <c r="R112" t="s">
         <v>746</v>
       </c>
-      <c r="S112" s="23" t="s">
+      <c r="S112" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A113" s="23" t="s">
+      <c r="A113" t="s">
         <v>742</v>
       </c>
       <c r="B113">
@@ -7759,7 +7760,7 @@
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A114" s="23" t="s">
+      <c r="A114" t="s">
         <v>743</v>
       </c>
       <c r="B114">
@@ -7786,6 +7787,19 @@
       </c>
       <c r="S116" t="s">
         <v>751</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>753</v>
+      </c>
+      <c r="R123" t="s">
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -12335,7 +12349,7 @@
       </c>
     </row>
   </sheetData>
-  <dataConsolidate link="1"/>
+  <dataConsolidate/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{F9B05BD3-6F93-43EB-89E4-4E1E10B2B816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2D2087-D4D8-42D0-BFB2-EAFB2FDD3BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0D" sheetId="1" r:id="rId1"/>
     <sheet name="3D" sheetId="2" r:id="rId2"/>
     <sheet name="Optical" sheetId="3" r:id="rId3"/>
+    <sheet name="MFC_t0" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="831">
   <si>
     <t>A</t>
   </si>
@@ -2398,6 +2398,234 @@
   </si>
   <si>
     <t xml:space="preserve">tested </t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Clock Time</t>
+  </si>
+  <si>
+    <t>Time (s)</t>
+  </si>
+  <si>
+    <t>MFC H2 SP (lpm)</t>
+  </si>
+  <si>
+    <t>MFC CH4 SP (lpm)</t>
+  </si>
+  <si>
+    <t>MFC CO2 SP (lpm)</t>
+  </si>
+  <si>
+    <t>MFC He SP (lpm)</t>
+  </si>
+  <si>
+    <t>MFC H2 (lpm)</t>
+  </si>
+  <si>
+    <t>MFC CH4 (lpm)</t>
+  </si>
+  <si>
+    <t>MFC CO2 (lpm)</t>
+  </si>
+  <si>
+    <t>MFC He (lpm)</t>
+  </si>
+  <si>
+    <t>P1 Limit (mbarg)</t>
+  </si>
+  <si>
+    <t>P2 Limit (mbarg)</t>
+  </si>
+  <si>
+    <t>DP1 Limit (mbar)</t>
+  </si>
+  <si>
+    <t>DP2 Limit (mbar)</t>
+  </si>
+  <si>
+    <t>P1 (mbarg)</t>
+  </si>
+  <si>
+    <t>P2 (mbarg)</t>
+  </si>
+  <si>
+    <t>DP1 (mbar)</t>
+  </si>
+  <si>
+    <t>DP2 (mbar)</t>
+  </si>
+  <si>
+    <t>T1 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T2 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T3 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T4 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T5 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T6 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T7 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T8 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T9 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T10 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T11 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T12 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T13 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T14 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T15 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T16 Limit (°C)</t>
+  </si>
+  <si>
+    <t>T1 (°C)</t>
+  </si>
+  <si>
+    <t>T2 (°C)</t>
+  </si>
+  <si>
+    <t>T3 (°C)</t>
+  </si>
+  <si>
+    <t>T4 (°C)</t>
+  </si>
+  <si>
+    <t>T5 (°C)</t>
+  </si>
+  <si>
+    <t>T6 (°C)</t>
+  </si>
+  <si>
+    <t>T7 (°C)</t>
+  </si>
+  <si>
+    <t>T8 (°C)</t>
+  </si>
+  <si>
+    <t>T09 (°C)</t>
+  </si>
+  <si>
+    <t>T10 (°C)</t>
+  </si>
+  <si>
+    <t>T11 (°C)</t>
+  </si>
+  <si>
+    <t>T12 (°C)</t>
+  </si>
+  <si>
+    <t>T13 (°C)</t>
+  </si>
+  <si>
+    <t>T14 (°C)</t>
+  </si>
+  <si>
+    <t>T15 (°C)</t>
+  </si>
+  <si>
+    <t>T16 (°C)</t>
+  </si>
+  <si>
+    <t>Flow Module</t>
+  </si>
+  <si>
+    <t>Pressure Module</t>
+  </si>
+  <si>
+    <t>Temperature Module</t>
+  </si>
+  <si>
+    <t>Program Started</t>
+  </si>
+  <si>
+    <t>MFCs Manual</t>
+  </si>
+  <si>
+    <t>Alarm Triggered</t>
+  </si>
+  <si>
+    <t>Overpressure</t>
+  </si>
+  <si>
+    <t>Overtemperature</t>
+  </si>
+  <si>
+    <t>Emergency User Input</t>
+  </si>
+  <si>
+    <t>Flows Emergency Stop</t>
+  </si>
+  <si>
+    <t>Flow Module Comm Error</t>
+  </si>
+  <si>
+    <t>Pressure Module Comm Error</t>
+  </si>
+  <si>
+    <t>Temperature Module Comm Error</t>
+  </si>
+  <si>
+    <t>E69</t>
+  </si>
+  <si>
+    <t>E70</t>
+  </si>
+  <si>
+    <t>E71</t>
+  </si>
+  <si>
+    <t>E72</t>
+  </si>
+  <si>
+    <t>E73</t>
+  </si>
+  <si>
+    <t>E74</t>
+  </si>
+  <si>
+    <t>E75</t>
+  </si>
+  <si>
+    <t>E76</t>
+  </si>
+  <si>
+    <t>E77</t>
+  </si>
+  <si>
+    <t>E79</t>
+  </si>
+  <si>
+    <t>E80</t>
+  </si>
+  <si>
+    <t>E81</t>
   </si>
 </sst>
 </file>
@@ -2519,7 +2747,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2575,6 +2803,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4189,6 +4418,433 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.0665354330708661E-2"/>
+                  <c:y val="-4.2117964421114026E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>MFC_t0!$L$2:$L$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>15.273</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.496</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.509</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.097999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.104000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19.488</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13.169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.016</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.9399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.5149999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.844999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.007000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.0109999999999992</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.5990000000000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.5110000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>MFC_t0!$S$2:$S$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.14299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.222</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.29499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.26600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.23300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.29899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.38700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.13900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.22600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.29899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.36799999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C448-4EFE-96A5-25781AA5A6D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2130121920"/>
+        <c:axId val="2130123360"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2130121920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2130123360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2130123360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2130121920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4230,6 +4886,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5301,6 +5997,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -5575,6 +6787,47 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>138112</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C5FD98D-454C-CD33-865A-BE1644303320}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -12353,4 +13606,3179 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FCA6E0-29A7-4D5D-82E5-A39A92764F1E}">
+  <dimension ref="A1:BM16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B1" t="s">
+        <v>756</v>
+      </c>
+      <c r="C1" t="s">
+        <v>757</v>
+      </c>
+      <c r="D1" t="s">
+        <v>758</v>
+      </c>
+      <c r="E1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1" t="s">
+        <v>760</v>
+      </c>
+      <c r="G1" t="s">
+        <v>761</v>
+      </c>
+      <c r="H1" t="s">
+        <v>762</v>
+      </c>
+      <c r="I1" t="s">
+        <v>763</v>
+      </c>
+      <c r="J1" t="s">
+        <v>764</v>
+      </c>
+      <c r="K1" t="s">
+        <v>765</v>
+      </c>
+      <c r="M1" t="s">
+        <v>766</v>
+      </c>
+      <c r="N1" t="s">
+        <v>767</v>
+      </c>
+      <c r="O1" t="s">
+        <v>768</v>
+      </c>
+      <c r="P1" t="s">
+        <v>769</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>770</v>
+      </c>
+      <c r="R1" t="s">
+        <v>771</v>
+      </c>
+      <c r="S1" t="s">
+        <v>772</v>
+      </c>
+      <c r="T1" t="s">
+        <v>773</v>
+      </c>
+      <c r="U1" t="s">
+        <v>774</v>
+      </c>
+      <c r="V1" t="s">
+        <v>775</v>
+      </c>
+      <c r="W1" t="s">
+        <v>776</v>
+      </c>
+      <c r="X1" t="s">
+        <v>777</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>778</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>779</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>780</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>781</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>782</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>783</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>784</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>785</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>786</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>787</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>788</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>789</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>790</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>791</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>792</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>793</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>794</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>795</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>796</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>797</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>798</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>799</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>800</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>801</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>802</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>803</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>804</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>805</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>806</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>807</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>808</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>809</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>810</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>811</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>812</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>813</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>814</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>815</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>816</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>817</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B2" s="23">
+        <v>0.67929398148148146</v>
+      </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <v>3.7</v>
+      </c>
+      <c r="E2">
+        <v>3.7</v>
+      </c>
+      <c r="F2">
+        <v>3.7</v>
+      </c>
+      <c r="G2">
+        <v>1.7</v>
+      </c>
+      <c r="H2">
+        <v>3.669</v>
+      </c>
+      <c r="I2">
+        <v>5.2889999999999997</v>
+      </c>
+      <c r="J2">
+        <v>5.1429999999999998</v>
+      </c>
+      <c r="K2">
+        <v>1.1719999999999999</v>
+      </c>
+      <c r="L2">
+        <f>SUM(H2:K2)</f>
+        <v>15.273</v>
+      </c>
+      <c r="M2">
+        <v>500</v>
+      </c>
+      <c r="N2">
+        <v>200</v>
+      </c>
+      <c r="O2">
+        <v>200</v>
+      </c>
+      <c r="P2">
+        <v>100</v>
+      </c>
+      <c r="Q2">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="R2">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="S2">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="T2">
+        <v>-0.28899999999999998</v>
+      </c>
+      <c r="U2">
+        <v>1500</v>
+      </c>
+      <c r="V2">
+        <v>1500</v>
+      </c>
+      <c r="W2">
+        <v>1500</v>
+      </c>
+      <c r="X2">
+        <v>1500</v>
+      </c>
+      <c r="Y2">
+        <v>1500</v>
+      </c>
+      <c r="Z2">
+        <v>1500</v>
+      </c>
+      <c r="AA2">
+        <v>1500</v>
+      </c>
+      <c r="AB2">
+        <v>1500</v>
+      </c>
+      <c r="AC2">
+        <v>1500</v>
+      </c>
+      <c r="AD2">
+        <v>1500</v>
+      </c>
+      <c r="AE2">
+        <v>1500</v>
+      </c>
+      <c r="AF2">
+        <v>1500</v>
+      </c>
+      <c r="AG2">
+        <v>1500</v>
+      </c>
+      <c r="AH2">
+        <v>1500</v>
+      </c>
+      <c r="AI2">
+        <v>1500</v>
+      </c>
+      <c r="AJ2">
+        <v>1500</v>
+      </c>
+      <c r="AK2">
+        <v>22.277999999999999</v>
+      </c>
+      <c r="AL2">
+        <v>20.251999999999999</v>
+      </c>
+      <c r="AM2">
+        <v>23.46</v>
+      </c>
+      <c r="AN2">
+        <v>22.001999999999999</v>
+      </c>
+      <c r="AO2">
+        <v>18.645</v>
+      </c>
+      <c r="AP2">
+        <v>25.114000000000001</v>
+      </c>
+      <c r="AQ2">
+        <v>24.907</v>
+      </c>
+      <c r="AR2">
+        <v>23.423999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>23.01</v>
+      </c>
+      <c r="AT2">
+        <v>23.207000000000001</v>
+      </c>
+      <c r="AU2">
+        <v>23.143000000000001</v>
+      </c>
+      <c r="AV2">
+        <v>23.05</v>
+      </c>
+      <c r="AW2">
+        <v>20.27</v>
+      </c>
+      <c r="AX2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="AY2">
+        <v>20.289000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>20.157</v>
+      </c>
+      <c r="BA2">
+        <v>1</v>
+      </c>
+      <c r="BB2">
+        <v>1</v>
+      </c>
+      <c r="BC2">
+        <v>1</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>1</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B3" s="23">
+        <v>0.49829861111111112</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>3.7</v>
+      </c>
+      <c r="E3">
+        <v>3.7</v>
+      </c>
+      <c r="F3">
+        <v>1.7</v>
+      </c>
+      <c r="G3">
+        <v>1.7</v>
+      </c>
+      <c r="H3">
+        <v>3.665</v>
+      </c>
+      <c r="I3">
+        <v>5.2939999999999996</v>
+      </c>
+      <c r="J3">
+        <v>2.3639999999999999</v>
+      </c>
+      <c r="K3">
+        <v>1.173</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L16" si="0">SUM(H3:K3)</f>
+        <v>12.496</v>
+      </c>
+      <c r="M3">
+        <v>500</v>
+      </c>
+      <c r="N3">
+        <v>200</v>
+      </c>
+      <c r="O3">
+        <v>200</v>
+      </c>
+      <c r="P3">
+        <v>100</v>
+      </c>
+      <c r="Q3">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="R3">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="S3">
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="T3">
+        <v>-0.313</v>
+      </c>
+      <c r="U3">
+        <v>1500</v>
+      </c>
+      <c r="V3">
+        <v>1500</v>
+      </c>
+      <c r="W3">
+        <v>1500</v>
+      </c>
+      <c r="X3">
+        <v>1500</v>
+      </c>
+      <c r="Y3">
+        <v>1500</v>
+      </c>
+      <c r="Z3">
+        <v>1500</v>
+      </c>
+      <c r="AA3">
+        <v>1500</v>
+      </c>
+      <c r="AB3">
+        <v>1500</v>
+      </c>
+      <c r="AC3">
+        <v>1500</v>
+      </c>
+      <c r="AD3">
+        <v>1500</v>
+      </c>
+      <c r="AE3">
+        <v>1500</v>
+      </c>
+      <c r="AF3">
+        <v>1500</v>
+      </c>
+      <c r="AG3">
+        <v>1500</v>
+      </c>
+      <c r="AH3">
+        <v>1500</v>
+      </c>
+      <c r="AI3">
+        <v>1500</v>
+      </c>
+      <c r="AJ3">
+        <v>1500</v>
+      </c>
+      <c r="AK3">
+        <v>20.167999999999999</v>
+      </c>
+      <c r="AL3">
+        <v>20.321999999999999</v>
+      </c>
+      <c r="AM3">
+        <v>20.523</v>
+      </c>
+      <c r="AN3">
+        <v>20.370999999999999</v>
+      </c>
+      <c r="AO3">
+        <v>18.364000000000001</v>
+      </c>
+      <c r="AP3">
+        <v>25.265000000000001</v>
+      </c>
+      <c r="AQ3">
+        <v>25.013999999999999</v>
+      </c>
+      <c r="AR3">
+        <v>21.701000000000001</v>
+      </c>
+      <c r="AS3">
+        <v>20.433</v>
+      </c>
+      <c r="AT3">
+        <v>20.498999999999999</v>
+      </c>
+      <c r="AU3">
+        <v>20.335999999999999</v>
+      </c>
+      <c r="AV3">
+        <v>20.420999999999999</v>
+      </c>
+      <c r="AW3">
+        <v>20.341999999999999</v>
+      </c>
+      <c r="AX3">
+        <v>20.135999999999999</v>
+      </c>
+      <c r="AY3">
+        <v>20.353000000000002</v>
+      </c>
+      <c r="AZ3">
+        <v>20.222999999999999</v>
+      </c>
+      <c r="BA3">
+        <v>1</v>
+      </c>
+      <c r="BB3">
+        <v>1</v>
+      </c>
+      <c r="BC3">
+        <v>1</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>1</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>819</v>
+      </c>
+      <c r="B4" s="23">
+        <v>0.5847106481481481</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>3.7</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1.7</v>
+      </c>
+      <c r="H4">
+        <v>3.67</v>
+      </c>
+      <c r="I4">
+        <v>2.8690000000000002</v>
+      </c>
+      <c r="J4">
+        <v>2.794</v>
+      </c>
+      <c r="K4">
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>10.509</v>
+      </c>
+      <c r="M4">
+        <v>500</v>
+      </c>
+      <c r="N4">
+        <v>200</v>
+      </c>
+      <c r="O4">
+        <v>200</v>
+      </c>
+      <c r="P4">
+        <v>100</v>
+      </c>
+      <c r="Q4">
+        <v>0.69</v>
+      </c>
+      <c r="R4">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="S4">
+        <v>-3.9E-2</v>
+      </c>
+      <c r="T4">
+        <v>-0.27600000000000002</v>
+      </c>
+      <c r="U4">
+        <v>1500</v>
+      </c>
+      <c r="V4">
+        <v>1500</v>
+      </c>
+      <c r="W4">
+        <v>1500</v>
+      </c>
+      <c r="X4">
+        <v>1500</v>
+      </c>
+      <c r="Y4">
+        <v>1500</v>
+      </c>
+      <c r="Z4">
+        <v>1500</v>
+      </c>
+      <c r="AA4">
+        <v>1500</v>
+      </c>
+      <c r="AB4">
+        <v>1500</v>
+      </c>
+      <c r="AC4">
+        <v>1500</v>
+      </c>
+      <c r="AD4">
+        <v>1500</v>
+      </c>
+      <c r="AE4">
+        <v>1500</v>
+      </c>
+      <c r="AF4">
+        <v>1500</v>
+      </c>
+      <c r="AG4">
+        <v>1500</v>
+      </c>
+      <c r="AH4">
+        <v>1500</v>
+      </c>
+      <c r="AI4">
+        <v>1500</v>
+      </c>
+      <c r="AJ4">
+        <v>1500</v>
+      </c>
+      <c r="AK4">
+        <v>59.156999999999996</v>
+      </c>
+      <c r="AL4">
+        <v>53.396999999999998</v>
+      </c>
+      <c r="AM4">
+        <v>107.42100000000001</v>
+      </c>
+      <c r="AN4">
+        <v>38.183999999999997</v>
+      </c>
+      <c r="AO4">
+        <v>23.056000000000001</v>
+      </c>
+      <c r="AP4">
+        <v>25.128</v>
+      </c>
+      <c r="AQ4">
+        <v>24.975000000000001</v>
+      </c>
+      <c r="AR4">
+        <v>44.439</v>
+      </c>
+      <c r="AS4">
+        <v>71.262</v>
+      </c>
+      <c r="AT4">
+        <v>98.691000000000003</v>
+      </c>
+      <c r="AU4">
+        <v>87.981999999999999</v>
+      </c>
+      <c r="AV4">
+        <v>64.507000000000005</v>
+      </c>
+      <c r="AW4">
+        <v>24.576000000000001</v>
+      </c>
+      <c r="AX4">
+        <v>24.337</v>
+      </c>
+      <c r="AY4">
+        <v>24.14</v>
+      </c>
+      <c r="AZ4">
+        <v>24.15</v>
+      </c>
+      <c r="BA4">
+        <v>1</v>
+      </c>
+      <c r="BB4">
+        <v>1</v>
+      </c>
+      <c r="BC4">
+        <v>1</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>1</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>820</v>
+      </c>
+      <c r="B5" s="23">
+        <v>0.37761574074074072</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>3.7</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1.7</v>
+      </c>
+      <c r="H5">
+        <v>3.6640000000000001</v>
+      </c>
+      <c r="I5">
+        <v>2.8650000000000002</v>
+      </c>
+      <c r="J5">
+        <v>1.3979999999999999</v>
+      </c>
+      <c r="K5">
+        <v>1.171</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>9.097999999999999</v>
+      </c>
+      <c r="M5">
+        <v>500</v>
+      </c>
+      <c r="N5">
+        <v>200</v>
+      </c>
+      <c r="O5">
+        <v>200</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="R5">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="S5">
+        <v>-0.222</v>
+      </c>
+      <c r="T5">
+        <v>-0.309</v>
+      </c>
+      <c r="U5">
+        <v>1500</v>
+      </c>
+      <c r="V5">
+        <v>1500</v>
+      </c>
+      <c r="W5">
+        <v>1500</v>
+      </c>
+      <c r="X5">
+        <v>1500</v>
+      </c>
+      <c r="Y5">
+        <v>1500</v>
+      </c>
+      <c r="Z5">
+        <v>1500</v>
+      </c>
+      <c r="AA5">
+        <v>1500</v>
+      </c>
+      <c r="AB5">
+        <v>1500</v>
+      </c>
+      <c r="AC5">
+        <v>1500</v>
+      </c>
+      <c r="AD5">
+        <v>1500</v>
+      </c>
+      <c r="AE5">
+        <v>1500</v>
+      </c>
+      <c r="AF5">
+        <v>1500</v>
+      </c>
+      <c r="AG5">
+        <v>1500</v>
+      </c>
+      <c r="AH5">
+        <v>1500</v>
+      </c>
+      <c r="AI5">
+        <v>1500</v>
+      </c>
+      <c r="AJ5">
+        <v>1500</v>
+      </c>
+      <c r="AK5">
+        <v>20.518000000000001</v>
+      </c>
+      <c r="AL5">
+        <v>20.356000000000002</v>
+      </c>
+      <c r="AM5">
+        <v>20.603999999999999</v>
+      </c>
+      <c r="AN5">
+        <v>20.399000000000001</v>
+      </c>
+      <c r="AO5">
+        <v>18.347999999999999</v>
+      </c>
+      <c r="AP5">
+        <v>24.672999999999998</v>
+      </c>
+      <c r="AQ5">
+        <v>24.448</v>
+      </c>
+      <c r="AR5">
+        <v>21.797999999999998</v>
+      </c>
+      <c r="AS5">
+        <v>20.5</v>
+      </c>
+      <c r="AT5">
+        <v>20.605</v>
+      </c>
+      <c r="AU5">
+        <v>20.408000000000001</v>
+      </c>
+      <c r="AV5">
+        <v>20.515999999999998</v>
+      </c>
+      <c r="AW5">
+        <v>20.355</v>
+      </c>
+      <c r="AX5">
+        <v>20.138999999999999</v>
+      </c>
+      <c r="AY5">
+        <v>20.420000000000002</v>
+      </c>
+      <c r="AZ5">
+        <v>20.266999999999999</v>
+      </c>
+      <c r="BA5">
+        <v>1</v>
+      </c>
+      <c r="BB5">
+        <v>1</v>
+      </c>
+      <c r="BC5">
+        <v>1</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>1</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>821</v>
+      </c>
+      <c r="B6" s="23">
+        <v>0.43559027777777776</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>1.7</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1.7</v>
+      </c>
+      <c r="H6">
+        <v>1.6819999999999999</v>
+      </c>
+      <c r="I6">
+        <v>2.859</v>
+      </c>
+      <c r="J6">
+        <v>1.389</v>
+      </c>
+      <c r="K6">
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>7.104000000000001</v>
+      </c>
+      <c r="M6">
+        <v>500</v>
+      </c>
+      <c r="N6">
+        <v>200</v>
+      </c>
+      <c r="O6">
+        <v>200</v>
+      </c>
+      <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>0.68</v>
+      </c>
+      <c r="R6">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="S6">
+        <v>-0.29499999999999998</v>
+      </c>
+      <c r="T6">
+        <v>-0.311</v>
+      </c>
+      <c r="U6">
+        <v>1500</v>
+      </c>
+      <c r="V6">
+        <v>1500</v>
+      </c>
+      <c r="W6">
+        <v>1500</v>
+      </c>
+      <c r="X6">
+        <v>1500</v>
+      </c>
+      <c r="Y6">
+        <v>1500</v>
+      </c>
+      <c r="Z6">
+        <v>1500</v>
+      </c>
+      <c r="AA6">
+        <v>1500</v>
+      </c>
+      <c r="AB6">
+        <v>1500</v>
+      </c>
+      <c r="AC6">
+        <v>1500</v>
+      </c>
+      <c r="AD6">
+        <v>1500</v>
+      </c>
+      <c r="AE6">
+        <v>1500</v>
+      </c>
+      <c r="AF6">
+        <v>1500</v>
+      </c>
+      <c r="AG6">
+        <v>1500</v>
+      </c>
+      <c r="AH6">
+        <v>1500</v>
+      </c>
+      <c r="AI6">
+        <v>1500</v>
+      </c>
+      <c r="AJ6">
+        <v>1500</v>
+      </c>
+      <c r="AK6">
+        <v>29.655999999999999</v>
+      </c>
+      <c r="AL6">
+        <v>20.463999999999999</v>
+      </c>
+      <c r="AM6">
+        <v>29.902999999999999</v>
+      </c>
+      <c r="AN6">
+        <v>21.088999999999999</v>
+      </c>
+      <c r="AO6">
+        <v>18.655000000000001</v>
+      </c>
+      <c r="AP6">
+        <v>25.138000000000002</v>
+      </c>
+      <c r="AQ6">
+        <v>24.934000000000001</v>
+      </c>
+      <c r="AR6">
+        <v>30.361000000000001</v>
+      </c>
+      <c r="AS6">
+        <v>33.777999999999999</v>
+      </c>
+      <c r="AT6">
+        <v>30.849</v>
+      </c>
+      <c r="AU6">
+        <v>32.182000000000002</v>
+      </c>
+      <c r="AV6">
+        <v>34.082999999999998</v>
+      </c>
+      <c r="AW6">
+        <v>20.681000000000001</v>
+      </c>
+      <c r="AX6">
+        <v>20.489000000000001</v>
+      </c>
+      <c r="AY6">
+        <v>20.672000000000001</v>
+      </c>
+      <c r="AZ6">
+        <v>20.545999999999999</v>
+      </c>
+      <c r="BA6">
+        <v>1</v>
+      </c>
+      <c r="BB6">
+        <v>1</v>
+      </c>
+      <c r="BC6">
+        <v>1</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>1</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>822</v>
+      </c>
+      <c r="B7" s="23">
+        <v>0.44568287037037035</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>4.4969999999999999</v>
+      </c>
+      <c r="I7">
+        <v>6.0190000000000001</v>
+      </c>
+      <c r="J7">
+        <v>5.524</v>
+      </c>
+      <c r="K7">
+        <v>3.448</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>19.488</v>
+      </c>
+      <c r="M7">
+        <v>500</v>
+      </c>
+      <c r="N7">
+        <v>200</v>
+      </c>
+      <c r="O7">
+        <v>200</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="R7">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="S7">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="T7">
+        <v>-0.29699999999999999</v>
+      </c>
+      <c r="U7">
+        <v>1500</v>
+      </c>
+      <c r="V7">
+        <v>1500</v>
+      </c>
+      <c r="W7">
+        <v>1500</v>
+      </c>
+      <c r="X7">
+        <v>1500</v>
+      </c>
+      <c r="Y7">
+        <v>1500</v>
+      </c>
+      <c r="Z7">
+        <v>1500</v>
+      </c>
+      <c r="AA7">
+        <v>1500</v>
+      </c>
+      <c r="AB7">
+        <v>1500</v>
+      </c>
+      <c r="AC7">
+        <v>1500</v>
+      </c>
+      <c r="AD7">
+        <v>1500</v>
+      </c>
+      <c r="AE7">
+        <v>1500</v>
+      </c>
+      <c r="AF7">
+        <v>1500</v>
+      </c>
+      <c r="AG7">
+        <v>1500</v>
+      </c>
+      <c r="AH7">
+        <v>1500</v>
+      </c>
+      <c r="AI7">
+        <v>1500</v>
+      </c>
+      <c r="AJ7">
+        <v>1500</v>
+      </c>
+      <c r="AK7">
+        <v>20.873999999999999</v>
+      </c>
+      <c r="AL7">
+        <v>20.925000000000001</v>
+      </c>
+      <c r="AM7">
+        <v>21.018000000000001</v>
+      </c>
+      <c r="AN7">
+        <v>21.010999999999999</v>
+      </c>
+      <c r="AO7">
+        <v>18.86</v>
+      </c>
+      <c r="AP7">
+        <v>24.832999999999998</v>
+      </c>
+      <c r="AQ7">
+        <v>24.591000000000001</v>
+      </c>
+      <c r="AR7">
+        <v>22.391999999999999</v>
+      </c>
+      <c r="AS7">
+        <v>21.065999999999999</v>
+      </c>
+      <c r="AT7">
+        <v>21.045999999999999</v>
+      </c>
+      <c r="AU7">
+        <v>20.85</v>
+      </c>
+      <c r="AV7">
+        <v>20.928999999999998</v>
+      </c>
+      <c r="AW7">
+        <v>21.023</v>
+      </c>
+      <c r="AX7">
+        <v>20.815000000000001</v>
+      </c>
+      <c r="AY7">
+        <v>20.962</v>
+      </c>
+      <c r="AZ7">
+        <v>20.86</v>
+      </c>
+      <c r="BA7">
+        <v>1</v>
+      </c>
+      <c r="BB7">
+        <v>1</v>
+      </c>
+      <c r="BC7">
+        <v>1</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>1</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B8" s="23">
+        <v>0.56099537037037039</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>1.9830000000000001</v>
+      </c>
+      <c r="I8">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="J8">
+        <v>5.556</v>
+      </c>
+      <c r="K8">
+        <v>2.758</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>13.169999999999998</v>
+      </c>
+      <c r="M8">
+        <v>500</v>
+      </c>
+      <c r="N8">
+        <v>200</v>
+      </c>
+      <c r="O8">
+        <v>200</v>
+      </c>
+      <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="R8">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="S8">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="T8">
+        <v>-0.29299999999999998</v>
+      </c>
+      <c r="U8">
+        <v>1500</v>
+      </c>
+      <c r="V8">
+        <v>1500</v>
+      </c>
+      <c r="W8">
+        <v>1500</v>
+      </c>
+      <c r="X8">
+        <v>1500</v>
+      </c>
+      <c r="Y8">
+        <v>1500</v>
+      </c>
+      <c r="Z8">
+        <v>1500</v>
+      </c>
+      <c r="AA8">
+        <v>1500</v>
+      </c>
+      <c r="AB8">
+        <v>1500</v>
+      </c>
+      <c r="AC8">
+        <v>1500</v>
+      </c>
+      <c r="AD8">
+        <v>1500</v>
+      </c>
+      <c r="AE8">
+        <v>1500</v>
+      </c>
+      <c r="AF8">
+        <v>1500</v>
+      </c>
+      <c r="AG8">
+        <v>1500</v>
+      </c>
+      <c r="AH8">
+        <v>1500</v>
+      </c>
+      <c r="AI8">
+        <v>1500</v>
+      </c>
+      <c r="AJ8">
+        <v>1500</v>
+      </c>
+      <c r="AK8">
+        <v>33.274000000000001</v>
+      </c>
+      <c r="AL8">
+        <v>32.514000000000003</v>
+      </c>
+      <c r="AM8">
+        <v>43.92</v>
+      </c>
+      <c r="AN8">
+        <v>24.234000000000002</v>
+      </c>
+      <c r="AO8">
+        <v>19.815999999999999</v>
+      </c>
+      <c r="AP8">
+        <v>24.739000000000001</v>
+      </c>
+      <c r="AQ8">
+        <v>24.603999999999999</v>
+      </c>
+      <c r="AR8">
+        <v>30.073</v>
+      </c>
+      <c r="AS8">
+        <v>36.981000000000002</v>
+      </c>
+      <c r="AT8">
+        <v>42.470999999999997</v>
+      </c>
+      <c r="AU8">
+        <v>39.097000000000001</v>
+      </c>
+      <c r="AV8">
+        <v>33.854999999999997</v>
+      </c>
+      <c r="AW8">
+        <v>22.873999999999999</v>
+      </c>
+      <c r="AX8">
+        <v>22.6</v>
+      </c>
+      <c r="AY8">
+        <v>22.196999999999999</v>
+      </c>
+      <c r="AZ8">
+        <v>22.402000000000001</v>
+      </c>
+      <c r="BA8">
+        <v>1</v>
+      </c>
+      <c r="BB8">
+        <v>1</v>
+      </c>
+      <c r="BC8">
+        <v>1</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>1</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>824</v>
+      </c>
+      <c r="B9" s="23">
+        <v>0.52262731481481484</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>1.9810000000000001</v>
+      </c>
+      <c r="I9">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="J9">
+        <v>2.7810000000000001</v>
+      </c>
+      <c r="K9">
+        <v>1.381</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>9.016</v>
+      </c>
+      <c r="M9">
+        <v>500</v>
+      </c>
+      <c r="N9">
+        <v>200</v>
+      </c>
+      <c r="O9">
+        <v>200</v>
+      </c>
+      <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="R9">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="S9">
+        <v>-0.23300000000000001</v>
+      </c>
+      <c r="T9">
+        <v>-0.317</v>
+      </c>
+      <c r="U9">
+        <v>1500</v>
+      </c>
+      <c r="V9">
+        <v>1500</v>
+      </c>
+      <c r="W9">
+        <v>1500</v>
+      </c>
+      <c r="X9">
+        <v>1500</v>
+      </c>
+      <c r="Y9">
+        <v>1500</v>
+      </c>
+      <c r="Z9">
+        <v>1500</v>
+      </c>
+      <c r="AA9">
+        <v>1500</v>
+      </c>
+      <c r="AB9">
+        <v>1500</v>
+      </c>
+      <c r="AC9">
+        <v>1500</v>
+      </c>
+      <c r="AD9">
+        <v>1500</v>
+      </c>
+      <c r="AE9">
+        <v>1500</v>
+      </c>
+      <c r="AF9">
+        <v>1500</v>
+      </c>
+      <c r="AG9">
+        <v>1500</v>
+      </c>
+      <c r="AH9">
+        <v>1500</v>
+      </c>
+      <c r="AI9">
+        <v>1500</v>
+      </c>
+      <c r="AJ9">
+        <v>1500</v>
+      </c>
+      <c r="AK9">
+        <v>20.971</v>
+      </c>
+      <c r="AL9">
+        <v>20.718</v>
+      </c>
+      <c r="AM9">
+        <v>20.951000000000001</v>
+      </c>
+      <c r="AN9">
+        <v>20.83</v>
+      </c>
+      <c r="AO9">
+        <v>18.888999999999999</v>
+      </c>
+      <c r="AP9">
+        <v>24.991</v>
+      </c>
+      <c r="AQ9">
+        <v>24.759</v>
+      </c>
+      <c r="AR9">
+        <v>22.398</v>
+      </c>
+      <c r="AS9">
+        <v>21.032</v>
+      </c>
+      <c r="AT9">
+        <v>20.963000000000001</v>
+      </c>
+      <c r="AU9">
+        <v>20.91</v>
+      </c>
+      <c r="AV9">
+        <v>21.073</v>
+      </c>
+      <c r="AW9">
+        <v>20.884</v>
+      </c>
+      <c r="AX9">
+        <v>20.704000000000001</v>
+      </c>
+      <c r="AY9">
+        <v>20.826000000000001</v>
+      </c>
+      <c r="AZ9">
+        <v>20.736000000000001</v>
+      </c>
+      <c r="BA9">
+        <v>1</v>
+      </c>
+      <c r="BB9">
+        <v>1</v>
+      </c>
+      <c r="BC9">
+        <v>1</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>1</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>825</v>
+      </c>
+      <c r="B10" s="23">
+        <v>0.68175925925925929</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1.982</v>
+      </c>
+      <c r="I10">
+        <v>2.8690000000000002</v>
+      </c>
+      <c r="J10">
+        <v>1.399</v>
+      </c>
+      <c r="K10">
+        <v>0.69</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>6.9399999999999995</v>
+      </c>
+      <c r="M10">
+        <v>500</v>
+      </c>
+      <c r="N10">
+        <v>200</v>
+      </c>
+      <c r="O10">
+        <v>200</v>
+      </c>
+      <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>0.70099999999999996</v>
+      </c>
+      <c r="R10">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="S10">
+        <v>-0.29899999999999999</v>
+      </c>
+      <c r="T10">
+        <v>-0.30099999999999999</v>
+      </c>
+      <c r="U10">
+        <v>1500</v>
+      </c>
+      <c r="V10">
+        <v>1500</v>
+      </c>
+      <c r="W10">
+        <v>1500</v>
+      </c>
+      <c r="X10">
+        <v>1500</v>
+      </c>
+      <c r="Y10">
+        <v>1500</v>
+      </c>
+      <c r="Z10">
+        <v>1500</v>
+      </c>
+      <c r="AA10">
+        <v>1500</v>
+      </c>
+      <c r="AB10">
+        <v>1500</v>
+      </c>
+      <c r="AC10">
+        <v>1500</v>
+      </c>
+      <c r="AD10">
+        <v>1500</v>
+      </c>
+      <c r="AE10">
+        <v>1500</v>
+      </c>
+      <c r="AF10">
+        <v>1500</v>
+      </c>
+      <c r="AG10">
+        <v>1500</v>
+      </c>
+      <c r="AH10">
+        <v>1500</v>
+      </c>
+      <c r="AI10">
+        <v>1500</v>
+      </c>
+      <c r="AJ10">
+        <v>1500</v>
+      </c>
+      <c r="AK10">
+        <v>20.853000000000002</v>
+      </c>
+      <c r="AL10">
+        <v>20.786000000000001</v>
+      </c>
+      <c r="AM10">
+        <v>20.949000000000002</v>
+      </c>
+      <c r="AN10">
+        <v>20.873999999999999</v>
+      </c>
+      <c r="AO10">
+        <v>18.873000000000001</v>
+      </c>
+      <c r="AP10">
+        <v>25.024000000000001</v>
+      </c>
+      <c r="AQ10">
+        <v>24.71</v>
+      </c>
+      <c r="AR10">
+        <v>22.398</v>
+      </c>
+      <c r="AS10">
+        <v>21.036000000000001</v>
+      </c>
+      <c r="AT10">
+        <v>20.966999999999999</v>
+      </c>
+      <c r="AU10">
+        <v>20.88</v>
+      </c>
+      <c r="AV10">
+        <v>21.052</v>
+      </c>
+      <c r="AW10">
+        <v>20.933</v>
+      </c>
+      <c r="AX10">
+        <v>20.748999999999999</v>
+      </c>
+      <c r="AY10">
+        <v>20.890999999999998</v>
+      </c>
+      <c r="AZ10">
+        <v>20.785</v>
+      </c>
+      <c r="BA10">
+        <v>1</v>
+      </c>
+      <c r="BB10">
+        <v>1</v>
+      </c>
+      <c r="BC10">
+        <v>1</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>1</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>826</v>
+      </c>
+      <c r="B11" s="23">
+        <v>0.5037962962962963</v>
+      </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0.995</v>
+      </c>
+      <c r="I11">
+        <v>1.4339999999999999</v>
+      </c>
+      <c r="J11">
+        <v>1.395</v>
+      </c>
+      <c r="K11">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>4.5149999999999997</v>
+      </c>
+      <c r="M11">
+        <v>500</v>
+      </c>
+      <c r="N11">
+        <v>200</v>
+      </c>
+      <c r="O11">
+        <v>200</v>
+      </c>
+      <c r="P11">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="R11">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="S11">
+        <v>-0.38700000000000001</v>
+      </c>
+      <c r="T11">
+        <v>-0.29899999999999999</v>
+      </c>
+      <c r="U11">
+        <v>1500</v>
+      </c>
+      <c r="V11">
+        <v>1500</v>
+      </c>
+      <c r="W11">
+        <v>1500</v>
+      </c>
+      <c r="X11">
+        <v>1500</v>
+      </c>
+      <c r="Y11">
+        <v>1500</v>
+      </c>
+      <c r="Z11">
+        <v>1500</v>
+      </c>
+      <c r="AA11">
+        <v>1500</v>
+      </c>
+      <c r="AB11">
+        <v>1500</v>
+      </c>
+      <c r="AC11">
+        <v>1500</v>
+      </c>
+      <c r="AD11">
+        <v>1500</v>
+      </c>
+      <c r="AE11">
+        <v>1500</v>
+      </c>
+      <c r="AF11">
+        <v>1500</v>
+      </c>
+      <c r="AG11">
+        <v>1500</v>
+      </c>
+      <c r="AH11">
+        <v>1500</v>
+      </c>
+      <c r="AI11">
+        <v>1500</v>
+      </c>
+      <c r="AJ11">
+        <v>1500</v>
+      </c>
+      <c r="AK11">
+        <v>20.855</v>
+      </c>
+      <c r="AL11">
+        <v>20.702000000000002</v>
+      </c>
+      <c r="AM11">
+        <v>20.902999999999999</v>
+      </c>
+      <c r="AN11">
+        <v>20.754000000000001</v>
+      </c>
+      <c r="AO11">
+        <v>18.815000000000001</v>
+      </c>
+      <c r="AP11">
+        <v>23.187999999999999</v>
+      </c>
+      <c r="AQ11">
+        <v>22.864000000000001</v>
+      </c>
+      <c r="AR11">
+        <v>22.387</v>
+      </c>
+      <c r="AS11">
+        <v>20.905999999999999</v>
+      </c>
+      <c r="AT11">
+        <v>20.934999999999999</v>
+      </c>
+      <c r="AU11">
+        <v>20.835999999999999</v>
+      </c>
+      <c r="AV11">
+        <v>21.026</v>
+      </c>
+      <c r="AW11">
+        <v>20.809000000000001</v>
+      </c>
+      <c r="AX11">
+        <v>20.652999999999999</v>
+      </c>
+      <c r="AY11">
+        <v>20.815999999999999</v>
+      </c>
+      <c r="AZ11">
+        <v>20.710999999999999</v>
+      </c>
+      <c r="BA11">
+        <v>1</v>
+      </c>
+      <c r="BB11">
+        <v>1</v>
+      </c>
+      <c r="BC11">
+        <v>1</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>1</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>827</v>
+      </c>
+      <c r="B12" s="23">
+        <v>0.67587962962962966</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>3.9590000000000001</v>
+      </c>
+      <c r="I12">
+        <v>5.718</v>
+      </c>
+      <c r="J12">
+        <v>2.786</v>
+      </c>
+      <c r="K12">
+        <v>1.3819999999999999</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>13.844999999999999</v>
+      </c>
+      <c r="M12">
+        <v>500</v>
+      </c>
+      <c r="N12">
+        <v>200</v>
+      </c>
+      <c r="O12">
+        <v>200</v>
+      </c>
+      <c r="P12">
+        <v>100</v>
+      </c>
+      <c r="Q12">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="R12">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="S12">
+        <v>6.2E-2</v>
+      </c>
+      <c r="T12">
+        <v>-0.29299999999999998</v>
+      </c>
+      <c r="U12">
+        <v>1500</v>
+      </c>
+      <c r="V12">
+        <v>1500</v>
+      </c>
+      <c r="W12">
+        <v>1500</v>
+      </c>
+      <c r="X12">
+        <v>1500</v>
+      </c>
+      <c r="Y12">
+        <v>1500</v>
+      </c>
+      <c r="Z12">
+        <v>1500</v>
+      </c>
+      <c r="AA12">
+        <v>1500</v>
+      </c>
+      <c r="AB12">
+        <v>1500</v>
+      </c>
+      <c r="AC12">
+        <v>1500</v>
+      </c>
+      <c r="AD12">
+        <v>1500</v>
+      </c>
+      <c r="AE12">
+        <v>1500</v>
+      </c>
+      <c r="AF12">
+        <v>1500</v>
+      </c>
+      <c r="AG12">
+        <v>1500</v>
+      </c>
+      <c r="AH12">
+        <v>1500</v>
+      </c>
+      <c r="AI12">
+        <v>1500</v>
+      </c>
+      <c r="AJ12">
+        <v>1500</v>
+      </c>
+      <c r="AK12">
+        <v>38.015000000000001</v>
+      </c>
+      <c r="AL12">
+        <v>34.933999999999997</v>
+      </c>
+      <c r="AM12">
+        <v>49.42</v>
+      </c>
+      <c r="AN12">
+        <v>23.440999999999999</v>
+      </c>
+      <c r="AO12">
+        <v>19.760000000000002</v>
+      </c>
+      <c r="AP12">
+        <v>24.747</v>
+      </c>
+      <c r="AQ12">
+        <v>24.574000000000002</v>
+      </c>
+      <c r="AR12">
+        <v>37.11</v>
+      </c>
+      <c r="AS12">
+        <v>45.844000000000001</v>
+      </c>
+      <c r="AT12">
+        <v>48.715000000000003</v>
+      </c>
+      <c r="AU12">
+        <v>46.834000000000003</v>
+      </c>
+      <c r="AV12">
+        <v>44.712000000000003</v>
+      </c>
+      <c r="AW12">
+        <v>22.701000000000001</v>
+      </c>
+      <c r="AX12">
+        <v>22.417999999999999</v>
+      </c>
+      <c r="AY12">
+        <v>22.122</v>
+      </c>
+      <c r="AZ12">
+        <v>22.291</v>
+      </c>
+      <c r="BA12">
+        <v>1</v>
+      </c>
+      <c r="BB12">
+        <v>1</v>
+      </c>
+      <c r="BC12">
+        <v>1</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>1</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>686</v>
+      </c>
+      <c r="B13" s="23">
+        <v>0.55775462962962963</v>
+      </c>
+      <c r="C13">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>2.9670000000000001</v>
+      </c>
+      <c r="I13">
+        <v>2.871</v>
+      </c>
+      <c r="J13">
+        <v>2.7890000000000001</v>
+      </c>
+      <c r="K13">
+        <v>1.38</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="0"/>
+        <v>10.007000000000001</v>
+      </c>
+      <c r="M13">
+        <v>500</v>
+      </c>
+      <c r="N13">
+        <v>200</v>
+      </c>
+      <c r="O13">
+        <v>200</v>
+      </c>
+      <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="R13">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="S13">
+        <v>-0.13900000000000001</v>
+      </c>
+      <c r="T13">
+        <v>-0.314</v>
+      </c>
+      <c r="U13">
+        <v>1500</v>
+      </c>
+      <c r="V13">
+        <v>1500</v>
+      </c>
+      <c r="W13">
+        <v>1500</v>
+      </c>
+      <c r="X13">
+        <v>1500</v>
+      </c>
+      <c r="Y13">
+        <v>1500</v>
+      </c>
+      <c r="Z13">
+        <v>1500</v>
+      </c>
+      <c r="AA13">
+        <v>1500</v>
+      </c>
+      <c r="AB13">
+        <v>1500</v>
+      </c>
+      <c r="AC13">
+        <v>1500</v>
+      </c>
+      <c r="AD13">
+        <v>1500</v>
+      </c>
+      <c r="AE13">
+        <v>1500</v>
+      </c>
+      <c r="AF13">
+        <v>1500</v>
+      </c>
+      <c r="AG13">
+        <v>1500</v>
+      </c>
+      <c r="AH13">
+        <v>1500</v>
+      </c>
+      <c r="AI13">
+        <v>1500</v>
+      </c>
+      <c r="AJ13">
+        <v>1500</v>
+      </c>
+      <c r="AK13">
+        <v>27.007999999999999</v>
+      </c>
+      <c r="AL13">
+        <v>21.03</v>
+      </c>
+      <c r="AM13">
+        <v>21.693000000000001</v>
+      </c>
+      <c r="AN13">
+        <v>21.242999999999999</v>
+      </c>
+      <c r="AO13">
+        <v>19.3</v>
+      </c>
+      <c r="AP13">
+        <v>24.405999999999999</v>
+      </c>
+      <c r="AQ13">
+        <v>24.085999999999999</v>
+      </c>
+      <c r="AR13">
+        <v>29.126000000000001</v>
+      </c>
+      <c r="AS13">
+        <v>21.548999999999999</v>
+      </c>
+      <c r="AT13">
+        <v>21.38</v>
+      </c>
+      <c r="AU13">
+        <v>22.134</v>
+      </c>
+      <c r="AV13">
+        <v>23.260999999999999</v>
+      </c>
+      <c r="AW13">
+        <v>21.247</v>
+      </c>
+      <c r="AX13">
+        <v>21.058</v>
+      </c>
+      <c r="AY13">
+        <v>21.236999999999998</v>
+      </c>
+      <c r="AZ13">
+        <v>21.102</v>
+      </c>
+      <c r="BA13">
+        <v>1</v>
+      </c>
+      <c r="BB13">
+        <v>1</v>
+      </c>
+      <c r="BC13">
+        <v>1</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>1</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>828</v>
+      </c>
+      <c r="B14" s="23">
+        <v>0.72422453703703704</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>0.99</v>
+      </c>
+      <c r="I14">
+        <v>2.86</v>
+      </c>
+      <c r="J14">
+        <v>2.778</v>
+      </c>
+      <c r="K14">
+        <v>1.383</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>8.0109999999999992</v>
+      </c>
+      <c r="M14">
+        <v>500</v>
+      </c>
+      <c r="N14">
+        <v>200</v>
+      </c>
+      <c r="O14">
+        <v>200</v>
+      </c>
+      <c r="P14">
+        <v>100</v>
+      </c>
+      <c r="Q14">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="R14">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="S14">
+        <v>-0.22600000000000001</v>
+      </c>
+      <c r="T14">
+        <v>-0.28199999999999997</v>
+      </c>
+      <c r="U14">
+        <v>1500</v>
+      </c>
+      <c r="V14">
+        <v>1500</v>
+      </c>
+      <c r="W14">
+        <v>1500</v>
+      </c>
+      <c r="X14">
+        <v>1500</v>
+      </c>
+      <c r="Y14">
+        <v>1500</v>
+      </c>
+      <c r="Z14">
+        <v>1500</v>
+      </c>
+      <c r="AA14">
+        <v>1500</v>
+      </c>
+      <c r="AB14">
+        <v>1500</v>
+      </c>
+      <c r="AC14">
+        <v>1500</v>
+      </c>
+      <c r="AD14">
+        <v>1500</v>
+      </c>
+      <c r="AE14">
+        <v>1500</v>
+      </c>
+      <c r="AF14">
+        <v>1500</v>
+      </c>
+      <c r="AG14">
+        <v>1500</v>
+      </c>
+      <c r="AH14">
+        <v>1500</v>
+      </c>
+      <c r="AI14">
+        <v>1500</v>
+      </c>
+      <c r="AJ14">
+        <v>1500</v>
+      </c>
+      <c r="AK14">
+        <v>27.495000000000001</v>
+      </c>
+      <c r="AL14">
+        <v>27.335000000000001</v>
+      </c>
+      <c r="AM14">
+        <v>30.024000000000001</v>
+      </c>
+      <c r="AN14">
+        <v>22.646999999999998</v>
+      </c>
+      <c r="AO14">
+        <v>20.405999999999999</v>
+      </c>
+      <c r="AP14">
+        <v>24.966000000000001</v>
+      </c>
+      <c r="AQ14">
+        <v>24.79</v>
+      </c>
+      <c r="AR14">
+        <v>26.724</v>
+      </c>
+      <c r="AS14">
+        <v>28.539000000000001</v>
+      </c>
+      <c r="AT14">
+        <v>29.795999999999999</v>
+      </c>
+      <c r="AU14">
+        <v>29.161000000000001</v>
+      </c>
+      <c r="AV14">
+        <v>27.957000000000001</v>
+      </c>
+      <c r="AW14">
+        <v>23.061</v>
+      </c>
+      <c r="AX14">
+        <v>22.806000000000001</v>
+      </c>
+      <c r="AY14">
+        <v>22.652000000000001</v>
+      </c>
+      <c r="AZ14">
+        <v>22.73</v>
+      </c>
+      <c r="BA14">
+        <v>1</v>
+      </c>
+      <c r="BB14">
+        <v>1</v>
+      </c>
+      <c r="BC14">
+        <v>1</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>1</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>829</v>
+      </c>
+      <c r="B15" s="23">
+        <v>0.41075231481481483</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>0.99</v>
+      </c>
+      <c r="I15">
+        <v>1.4419999999999999</v>
+      </c>
+      <c r="J15">
+        <v>2.786</v>
+      </c>
+      <c r="K15">
+        <v>1.381</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="0"/>
+        <v>6.5990000000000002</v>
+      </c>
+      <c r="M15">
+        <v>500</v>
+      </c>
+      <c r="N15">
+        <v>200</v>
+      </c>
+      <c r="O15">
+        <v>200</v>
+      </c>
+      <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="R15">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="S15">
+        <v>-0.29899999999999999</v>
+      </c>
+      <c r="T15">
+        <v>-0.30299999999999999</v>
+      </c>
+      <c r="U15">
+        <v>1500</v>
+      </c>
+      <c r="V15">
+        <v>1500</v>
+      </c>
+      <c r="W15">
+        <v>1500</v>
+      </c>
+      <c r="X15">
+        <v>1500</v>
+      </c>
+      <c r="Y15">
+        <v>1500</v>
+      </c>
+      <c r="Z15">
+        <v>1500</v>
+      </c>
+      <c r="AA15">
+        <v>1500</v>
+      </c>
+      <c r="AB15">
+        <v>1500</v>
+      </c>
+      <c r="AC15">
+        <v>1500</v>
+      </c>
+      <c r="AD15">
+        <v>1500</v>
+      </c>
+      <c r="AE15">
+        <v>1500</v>
+      </c>
+      <c r="AF15">
+        <v>1500</v>
+      </c>
+      <c r="AG15">
+        <v>1500</v>
+      </c>
+      <c r="AH15">
+        <v>1500</v>
+      </c>
+      <c r="AI15">
+        <v>1500</v>
+      </c>
+      <c r="AJ15">
+        <v>1500</v>
+      </c>
+      <c r="AK15">
+        <v>21.375</v>
+      </c>
+      <c r="AL15">
+        <v>21.209</v>
+      </c>
+      <c r="AM15">
+        <v>21.423999999999999</v>
+      </c>
+      <c r="AN15">
+        <v>21.198</v>
+      </c>
+      <c r="AO15">
+        <v>19.128</v>
+      </c>
+      <c r="AP15">
+        <v>24.588999999999999</v>
+      </c>
+      <c r="AQ15">
+        <v>24.321000000000002</v>
+      </c>
+      <c r="AR15">
+        <v>22.806999999999999</v>
+      </c>
+      <c r="AS15">
+        <v>21.539000000000001</v>
+      </c>
+      <c r="AT15">
+        <v>21.484000000000002</v>
+      </c>
+      <c r="AU15">
+        <v>21.379000000000001</v>
+      </c>
+      <c r="AV15">
+        <v>21.475000000000001</v>
+      </c>
+      <c r="AW15">
+        <v>21.298999999999999</v>
+      </c>
+      <c r="AX15">
+        <v>21.097000000000001</v>
+      </c>
+      <c r="AY15">
+        <v>21.177</v>
+      </c>
+      <c r="AZ15">
+        <v>21.087</v>
+      </c>
+      <c r="BA15">
+        <v>1</v>
+      </c>
+      <c r="BB15">
+        <v>1</v>
+      </c>
+      <c r="BC15">
+        <v>1</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>1</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>830</v>
+      </c>
+      <c r="B16" s="23">
+        <v>0.57916666666666672</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>0.99</v>
+      </c>
+      <c r="I16">
+        <v>1.4379999999999999</v>
+      </c>
+      <c r="J16">
+        <v>1.3919999999999999</v>
+      </c>
+      <c r="K16">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="0"/>
+        <v>4.5110000000000001</v>
+      </c>
+      <c r="M16">
+        <v>500</v>
+      </c>
+      <c r="N16">
+        <v>200</v>
+      </c>
+      <c r="O16">
+        <v>200</v>
+      </c>
+      <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>0.70399999999999996</v>
+      </c>
+      <c r="R16">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="S16">
+        <v>-0.36799999999999999</v>
+      </c>
+      <c r="T16">
+        <v>-0.29799999999999999</v>
+      </c>
+      <c r="U16">
+        <v>1500</v>
+      </c>
+      <c r="V16">
+        <v>1500</v>
+      </c>
+      <c r="W16">
+        <v>1500</v>
+      </c>
+      <c r="X16">
+        <v>1500</v>
+      </c>
+      <c r="Y16">
+        <v>1500</v>
+      </c>
+      <c r="Z16">
+        <v>1500</v>
+      </c>
+      <c r="AA16">
+        <v>1500</v>
+      </c>
+      <c r="AB16">
+        <v>1500</v>
+      </c>
+      <c r="AC16">
+        <v>1500</v>
+      </c>
+      <c r="AD16">
+        <v>1500</v>
+      </c>
+      <c r="AE16">
+        <v>1500</v>
+      </c>
+      <c r="AF16">
+        <v>1500</v>
+      </c>
+      <c r="AG16">
+        <v>1500</v>
+      </c>
+      <c r="AH16">
+        <v>1500</v>
+      </c>
+      <c r="AI16">
+        <v>1500</v>
+      </c>
+      <c r="AJ16">
+        <v>1500</v>
+      </c>
+      <c r="AK16">
+        <v>27.341000000000001</v>
+      </c>
+      <c r="AL16">
+        <v>26.523</v>
+      </c>
+      <c r="AM16">
+        <v>30.777000000000001</v>
+      </c>
+      <c r="AN16">
+        <v>21.861999999999998</v>
+      </c>
+      <c r="AO16">
+        <v>20.027999999999999</v>
+      </c>
+      <c r="AP16">
+        <v>25.474</v>
+      </c>
+      <c r="AQ16">
+        <v>25.346</v>
+      </c>
+      <c r="AR16">
+        <v>27.632999999999999</v>
+      </c>
+      <c r="AS16">
+        <v>29.855</v>
+      </c>
+      <c r="AT16">
+        <v>30.751000000000001</v>
+      </c>
+      <c r="AU16">
+        <v>30.462</v>
+      </c>
+      <c r="AV16">
+        <v>29.603000000000002</v>
+      </c>
+      <c r="AW16">
+        <v>22.361999999999998</v>
+      </c>
+      <c r="AX16">
+        <v>22.137</v>
+      </c>
+      <c r="AY16">
+        <v>22.135999999999999</v>
+      </c>
+      <c r="AZ16">
+        <v>22.14</v>
+      </c>
+      <c r="BA16">
+        <v>1</v>
+      </c>
+      <c r="BB16">
+        <v>1</v>
+      </c>
+      <c r="BC16">
+        <v>1</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>1</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/aysha/FittingTests v3.xlsx
+++ b/aysha/FittingTests v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2D2087-D4D8-42D0-BFB2-EAFB2FDD3BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7FFA0E-7A51-405F-94D8-C3C9D9F8C563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
